--- a/Financial Analysis/CRM.xlsx
+++ b/Financial Analysis/CRM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B73733A-37F7-4BDA-AE94-81898D771748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705CF378-A7F3-42FE-A931-8AE09E7C6C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{A12E68CC-70F9-45A5-9F33-23BEFCB58B54}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A12E68CC-70F9-45A5-9F33-23BEFCB58B54}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -860,14 +860,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="11">
-        <v>253.63</v>
+        <v>277.49</v>
       </c>
       <c r="E3" s="4">
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45805</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>243738.43</v>
+        <v>266667.89</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -932,7 +932,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>233287.43</v>
+        <v>256216.89</v>
       </c>
     </row>
   </sheetData>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="BM36" s="11">
         <f>Main!D3</f>
-        <v>253.63</v>
+        <v>277.49</v>
       </c>
     </row>
     <row r="37" spans="2:65" x14ac:dyDescent="0.3">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="BM37" s="10">
         <f>BM35/BM36-1</f>
-        <v>-0.42844692622181901</v>
+        <v>-0.47759196330548825</v>
       </c>
     </row>
     <row r="38" spans="2:65" x14ac:dyDescent="0.3">

--- a/Financial Analysis/CRM.xlsx
+++ b/Financial Analysis/CRM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705CF378-A7F3-42FE-A931-8AE09E7C6C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA365E78-2AF7-4F26-BFD5-DB3E6C7A0273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A12E68CC-70F9-45A5-9F33-23BEFCB58B54}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{A12E68CC-70F9-45A5-9F33-23BEFCB58B54}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -320,7 +320,7 @@
     <t>Service Margin</t>
   </si>
   <si>
-    <t>seems quite overvalued even with optimistic forecasts, maybe cash flow is better</t>
+    <t>Net Margin</t>
   </si>
 </sst>
 </file>
@@ -487,14 +487,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -511,8 +511,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25450800" y="15240"/>
-          <a:ext cx="0" cy="7040880"/>
+          <a:off x="26974800" y="15240"/>
+          <a:ext cx="0" cy="7772400"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -860,17 +860,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="11">
-        <v>277.49</v>
+        <v>252.92</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45909</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45909</v>
       </c>
       <c r="G3" s="4">
-        <v>45805</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -878,10 +878,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -890,7 +890,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>266667.89</v>
+        <v>240779.84</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -898,11 +898,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>8848+5184+4852</f>
-        <v>18884</v>
+        <f>10365+5007+5085</f>
+        <v>20457</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -910,11 +910,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>8433</f>
-        <v>8433</v>
+        <f>8436</f>
+        <v>8436</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>10451</v>
+        <v>12021</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -932,7 +932,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>256216.89</v>
+        <v>228758.84</v>
       </c>
     </row>
   </sheetData>
@@ -943,7 +943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00AFFAC9-910F-4EBF-A355-640842B8D7D8}">
-  <dimension ref="B1:GN40"/>
+  <dimension ref="B1:GN38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
@@ -1366,20 +1366,18 @@
         <v>9451</v>
       </c>
       <c r="AI3" s="12">
-        <f>AE3*1.08</f>
-        <v>9271.8000000000011</v>
+        <v>9297</v>
       </c>
       <c r="AJ3" s="12">
-        <f>AF3*1.07</f>
-        <v>9377.4800000000014</v>
+        <v>9690</v>
       </c>
       <c r="AK3" s="12">
-        <f>AG3*1.06</f>
-        <v>9411.74</v>
+        <f>AG3*1.1</f>
+        <v>9766.9000000000015</v>
       </c>
       <c r="AL3" s="12">
-        <f>AH3*1.04</f>
-        <v>9829.0400000000009</v>
+        <f>AH3*1.07</f>
+        <v>10112.57</v>
       </c>
       <c r="AM3" s="6"/>
       <c r="AN3" s="6"/>
@@ -1403,47 +1401,47 @@
       </c>
       <c r="AZ3" s="5">
         <f>SUM(AI3:AL3)</f>
-        <v>37890.060000000005</v>
+        <v>38866.47</v>
       </c>
       <c r="BA3" s="5">
-        <f>AZ3*1.04</f>
-        <v>39405.662400000008</v>
+        <f>AZ3*1.06</f>
+        <v>41198.458200000001</v>
       </c>
       <c r="BB3" s="5">
-        <f>BA3*1.03</f>
-        <v>40587.832272000007</v>
+        <f>BA3*1.05</f>
+        <v>43258.381110000002</v>
       </c>
       <c r="BC3" s="5">
-        <f>BB3*1.02</f>
-        <v>41399.588917440007</v>
+        <f>BB3*1.03</f>
+        <v>44556.132543300002</v>
       </c>
       <c r="BD3" s="5">
-        <f t="shared" ref="BD3:BE3" si="0">BC3*1.02</f>
-        <v>42227.580695788805</v>
+        <f t="shared" ref="BD3" si="0">BC3*1.02</f>
+        <v>45447.255194166006</v>
       </c>
       <c r="BE3" s="5">
-        <f t="shared" si="0"/>
-        <v>43072.132309704582</v>
+        <f t="shared" ref="BE3" si="1">BD3*1.02</f>
+        <v>46356.200298049327</v>
       </c>
       <c r="BF3" s="5">
-        <f>BE3*1.01</f>
-        <v>43502.853632801627</v>
+        <f t="shared" ref="BF3" si="2">BE3*1.02</f>
+        <v>47283.324304010312</v>
       </c>
       <c r="BG3" s="5">
-        <f t="shared" ref="BG3:BJ3" si="1">BF3*1.01</f>
-        <v>43937.882169129647</v>
+        <f t="shared" ref="BG3" si="3">BF3*1.02</f>
+        <v>48228.990790090516</v>
       </c>
       <c r="BH3" s="5">
-        <f t="shared" si="1"/>
-        <v>44377.260990820942</v>
+        <f t="shared" ref="BH3" si="4">BG3*1.02</f>
+        <v>49193.570605892324</v>
       </c>
       <c r="BI3" s="5">
-        <f t="shared" si="1"/>
-        <v>44821.033600729148</v>
+        <f t="shared" ref="BI3" si="5">BH3*1.02</f>
+        <v>50177.442018010173</v>
       </c>
       <c r="BJ3" s="5">
-        <f t="shared" si="1"/>
-        <v>45269.243936736442</v>
+        <f t="shared" ref="BJ3" si="6">BI3*1.02</f>
+        <v>51180.99085837038</v>
       </c>
     </row>
     <row r="4" spans="2:62" x14ac:dyDescent="0.3">
@@ -1517,19 +1515,17 @@
         <v>542</v>
       </c>
       <c r="AI4" s="12">
-        <f>AE4*1.01</f>
-        <v>553.48</v>
+        <v>532</v>
       </c>
       <c r="AJ4" s="12">
-        <f t="shared" ref="AJ4:AL4" si="2">AF4*1.01</f>
-        <v>566.61</v>
+        <v>546</v>
       </c>
       <c r="AK4" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AK4:AL4" si="7">AG4*1.01</f>
         <v>570.65</v>
       </c>
       <c r="AL4" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>547.41999999999996</v>
       </c>
       <c r="AM4" s="6"/>
@@ -1554,47 +1550,47 @@
       </c>
       <c r="AZ4" s="5">
         <f>SUM(AI4:AL4)</f>
-        <v>2238.1600000000003</v>
+        <v>2196.0700000000002</v>
       </c>
       <c r="BA4" s="5">
         <f>AZ4*1.01</f>
-        <v>2260.5416000000005</v>
+        <v>2218.0307000000003</v>
       </c>
       <c r="BB4" s="5">
-        <f t="shared" ref="BB4:BJ4" si="3">BA4*1.01</f>
-        <v>2283.1470160000003</v>
+        <f t="shared" ref="BB4:BJ4" si="8">BA4*1.01</f>
+        <v>2240.2110070000003</v>
       </c>
       <c r="BC4" s="5">
-        <f t="shared" si="3"/>
-        <v>2305.9784861600006</v>
+        <f t="shared" si="8"/>
+        <v>2262.6131170700005</v>
       </c>
       <c r="BD4" s="5">
-        <f t="shared" si="3"/>
-        <v>2329.0382710216004</v>
+        <f t="shared" si="8"/>
+        <v>2285.2392482407004</v>
       </c>
       <c r="BE4" s="5">
-        <f t="shared" si="3"/>
-        <v>2352.3286537318163</v>
+        <f t="shared" si="8"/>
+        <v>2308.0916407231075</v>
       </c>
       <c r="BF4" s="5">
-        <f t="shared" si="3"/>
-        <v>2375.8519402691345</v>
+        <f t="shared" si="8"/>
+        <v>2331.1725571303386</v>
       </c>
       <c r="BG4" s="5">
-        <f t="shared" si="3"/>
-        <v>2399.610459671826</v>
+        <f t="shared" si="8"/>
+        <v>2354.4842827016419</v>
       </c>
       <c r="BH4" s="5">
-        <f t="shared" si="3"/>
-        <v>2423.6065642685444</v>
+        <f t="shared" si="8"/>
+        <v>2378.0291255286584</v>
       </c>
       <c r="BI4" s="5">
-        <f t="shared" si="3"/>
-        <v>2447.8426299112298</v>
+        <f t="shared" si="8"/>
+        <v>2401.8094167839449</v>
       </c>
       <c r="BJ4" s="5">
-        <f t="shared" si="3"/>
-        <v>2472.3210562103422</v>
+        <f t="shared" si="8"/>
+        <v>2425.8275109517845</v>
       </c>
     </row>
     <row r="5" spans="2:62" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1651,84 +1647,84 @@
         <v>5817</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" ref="S5:AH5" si="4">S3+S4</f>
+        <f t="shared" ref="S5:AH5" si="9">S3+S4</f>
         <v>5963</v>
       </c>
       <c r="T5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>6340</v>
       </c>
       <c r="U5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>6863</v>
       </c>
       <c r="V5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>7326</v>
       </c>
       <c r="W5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>7411</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>7720</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>7837</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8384</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8247</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8603</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8720</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9287</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9133</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9325</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9444</v>
       </c>
       <c r="AH5" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9993</v>
       </c>
       <c r="AI5" s="9">
-        <f t="shared" ref="AI5:AL5" si="5">AI3+AI4</f>
-        <v>9825.2800000000007</v>
+        <f t="shared" ref="AI5:AL5" si="10">AI3+AI4</f>
+        <v>9829</v>
       </c>
       <c r="AJ5" s="9">
-        <f t="shared" si="5"/>
-        <v>9944.090000000002</v>
+        <f t="shared" si="10"/>
+        <v>10236</v>
       </c>
       <c r="AK5" s="9">
-        <f t="shared" si="5"/>
-        <v>9982.39</v>
+        <f t="shared" si="10"/>
+        <v>10337.550000000001</v>
       </c>
       <c r="AL5" s="9">
-        <f t="shared" si="5"/>
-        <v>10376.460000000001</v>
+        <f t="shared" si="10"/>
+        <v>10659.99</v>
       </c>
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
@@ -1751,11 +1747,11 @@
         <v>21252</v>
       </c>
       <c r="AV5" s="9">
-        <f t="shared" ref="AV5:AW5" si="6">AV3+AV4</f>
+        <f t="shared" ref="AV5:AW5" si="11">AV3+AV4</f>
         <v>26492</v>
       </c>
       <c r="AW5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>31352</v>
       </c>
       <c r="AX5" s="9">
@@ -1783,11 +1779,11 @@
         <v>45180.147012000016</v>
       </c>
       <c r="BD5" s="9">
-        <f t="shared" ref="BD5:BE5" si="7">BC5*1.03</f>
+        <f t="shared" ref="BD5:BE5" si="12">BC5*1.03</f>
         <v>46535.551422360018</v>
       </c>
       <c r="BE5" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>47931.617965030819</v>
       </c>
       <c r="BF5" s="9">
@@ -1795,19 +1791,19 @@
         <v>48890.250324331435</v>
       </c>
       <c r="BG5" s="9">
-        <f t="shared" ref="BG5:BJ5" si="8">BF5*1.02</f>
+        <f t="shared" ref="BG5:BJ5" si="13">BF5*1.02</f>
         <v>49868.055330818068</v>
       </c>
       <c r="BH5" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>50865.416437434433</v>
       </c>
       <c r="BI5" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>51882.724766183121</v>
       </c>
       <c r="BJ5" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>52920.379261506787</v>
       </c>
     </row>
@@ -1882,20 +1878,18 @@
         <v>1581</v>
       </c>
       <c r="AI6" s="5">
-        <f>AI3*0.17</f>
-        <v>1576.2060000000004</v>
+        <v>1611</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" ref="AJ6:AL6" si="9">AJ3*0.17</f>
-        <v>1594.1716000000004</v>
+        <v>1645</v>
       </c>
       <c r="AK6" s="5">
-        <f t="shared" si="9"/>
-        <v>1599.9958000000001</v>
+        <f t="shared" ref="AK6:AL6" si="14">AK3*0.17</f>
+        <v>1660.3730000000003</v>
       </c>
       <c r="AL6" s="5">
-        <f t="shared" si="9"/>
-        <v>1670.9368000000002</v>
+        <f t="shared" si="14"/>
+        <v>1719.1369</v>
       </c>
       <c r="AM6" s="9"/>
       <c r="AN6" s="9"/>
@@ -1923,7 +1917,7 @@
       </c>
       <c r="AZ6" s="5">
         <f>SUM(AI6:AL6)</f>
-        <v>6441.3102000000008</v>
+        <v>6635.5099000000009</v>
       </c>
       <c r="BA6" s="9"/>
       <c r="BB6" s="9"/>
@@ -2007,19 +2001,17 @@
         <v>636</v>
       </c>
       <c r="AI7" s="5">
-        <f>AI4*1.15</f>
-        <v>636.50199999999995</v>
+        <v>654</v>
       </c>
       <c r="AJ7" s="5">
-        <f t="shared" ref="AJ7:AL7" si="10">AJ4*1.15</f>
-        <v>651.60149999999999</v>
+        <v>597</v>
       </c>
       <c r="AK7" s="5">
-        <f t="shared" si="10"/>
-        <v>656.24749999999995</v>
+        <f>AK4*1.08</f>
+        <v>616.30200000000002</v>
       </c>
       <c r="AL7" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="AL7" si="15">AL4*1.15</f>
         <v>629.5329999999999</v>
       </c>
       <c r="AM7" s="9"/>
@@ -2048,7 +2040,7 @@
       </c>
       <c r="AZ7" s="5">
         <f>SUM(AI7:AL7)</f>
-        <v>2573.884</v>
+        <v>2496.835</v>
       </c>
       <c r="BA7" s="9"/>
       <c r="BB7" s="9"/>
@@ -2115,84 +2107,84 @@
         <v>1479</v>
       </c>
       <c r="S8" s="5">
-        <f t="shared" ref="S8:AH8" si="11">S6+S7</f>
+        <f t="shared" ref="S8:AH8" si="16">S6+S7</f>
         <v>1555</v>
       </c>
       <c r="T8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>1613</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>1844</v>
       </c>
       <c r="V8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2014</v>
       </c>
       <c r="W8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2045</v>
       </c>
       <c r="X8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2127</v>
       </c>
       <c r="Y8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2088</v>
       </c>
       <c r="Z8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2100</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2125</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2113</v>
       </c>
       <c r="AC8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2155</v>
       </c>
       <c r="AD8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2148</v>
       </c>
       <c r="AE8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2162</v>
       </c>
       <c r="AF8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2159</v>
       </c>
       <c r="AG8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2105</v>
       </c>
       <c r="AH8" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>2217</v>
       </c>
       <c r="AI8" s="5">
-        <f t="shared" ref="AI8:AL8" si="12">AI6+AI7</f>
-        <v>2212.7080000000005</v>
+        <f t="shared" ref="AI8:AL8" si="17">AI6+AI7</f>
+        <v>2265</v>
       </c>
       <c r="AJ8" s="5">
-        <f t="shared" si="12"/>
-        <v>2245.7731000000003</v>
+        <f t="shared" si="17"/>
+        <v>2242</v>
       </c>
       <c r="AK8" s="5">
-        <f t="shared" si="12"/>
-        <v>2256.2433000000001</v>
+        <f t="shared" si="17"/>
+        <v>2276.6750000000002</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" si="12"/>
-        <v>2300.4697999999999</v>
+        <f t="shared" si="17"/>
+        <v>2348.6698999999999</v>
       </c>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
@@ -2232,46 +2224,46 @@
       </c>
       <c r="AZ8" s="5">
         <f>AZ6+AZ7</f>
-        <v>9015.1942000000017</v>
+        <v>9132.3449000000001</v>
       </c>
       <c r="BA8" s="5">
-        <f t="shared" ref="BA8:BE8" si="13">BA5-BA9</f>
+        <f t="shared" ref="BA8:BE8" si="18">BA5-BA9</f>
         <v>9278.9697000000015</v>
       </c>
       <c r="BB8" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>9650.1284880000021</v>
       </c>
       <c r="BC8" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>9939.6323426400049</v>
       </c>
       <c r="BD8" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>10237.821312919201</v>
       </c>
       <c r="BE8" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>10544.95595230678</v>
       </c>
       <c r="BF8" s="5">
-        <f t="shared" ref="BF8:BJ8" si="14">BF5-BF9</f>
+        <f t="shared" ref="BF8:BJ8" si="19">BF5-BF9</f>
         <v>10755.855071352911</v>
       </c>
       <c r="BG8" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>10970.972172779977</v>
       </c>
       <c r="BH8" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>11190.391616235574</v>
       </c>
       <c r="BI8" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>11414.199448560285</v>
       </c>
       <c r="BJ8" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>11642.483437531489</v>
       </c>
     </row>
@@ -2280,59 +2272,59 @@
         <v>24</v>
       </c>
       <c r="C9" s="9">
-        <f t="shared" ref="C9:S9" si="15">C5-C8</f>
+        <f t="shared" ref="C9:S9" si="20">C5-C8</f>
         <v>1746</v>
       </c>
       <c r="D9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>1907</v>
       </c>
       <c r="E9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>1987</v>
       </c>
       <c r="F9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>2127</v>
       </c>
       <c r="G9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>2239</v>
       </c>
       <c r="H9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>2432</v>
       </c>
       <c r="I9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>2503</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>2657</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>2823</v>
       </c>
       <c r="L9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>3030</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>3379</v>
       </c>
       <c r="N9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>3631</v>
       </c>
       <c r="O9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>3611</v>
       </c>
       <c r="P9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>3840</v>
       </c>
       <c r="Q9" s="9">
@@ -2340,88 +2332,88 @@
         <v>4064.25</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>4338</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>4408</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" ref="T9" si="16">T5-T8</f>
+        <f t="shared" ref="T9" si="21">T5-T8</f>
         <v>4727</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" ref="U9" si="17">U5-U8</f>
+        <f t="shared" ref="U9" si="22">U5-U8</f>
         <v>5019</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" ref="V9:W9" si="18">V5-V8</f>
+        <f t="shared" ref="V9:W9" si="23">V5-V8</f>
         <v>5312</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>5366</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" ref="X9" si="19">X5-X8</f>
+        <f t="shared" ref="X9" si="24">X5-X8</f>
         <v>5593</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" ref="Y9" si="20">Y5-Y8</f>
+        <f t="shared" ref="Y9" si="25">Y5-Y8</f>
         <v>5749</v>
       </c>
       <c r="Z9" s="9">
-        <f t="shared" ref="Z9:AA9" si="21">Z5-Z8</f>
+        <f t="shared" ref="Z9:AA9" si="26">Z5-Z8</f>
         <v>6284</v>
       </c>
       <c r="AA9" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>6122</v>
       </c>
       <c r="AB9" s="9">
-        <f t="shared" ref="AB9" si="22">AB5-AB8</f>
+        <f t="shared" ref="AB9" si="27">AB5-AB8</f>
         <v>6490</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" ref="AC9" si="23">AC5-AC8</f>
+        <f t="shared" ref="AC9" si="28">AC5-AC8</f>
         <v>6565</v>
       </c>
       <c r="AD9" s="9">
-        <f t="shared" ref="AD9:AE9" si="24">AD5-AD8</f>
+        <f t="shared" ref="AD9:AE9" si="29">AD5-AD8</f>
         <v>7139</v>
       </c>
       <c r="AE9" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>6971</v>
       </c>
       <c r="AF9" s="9">
-        <f t="shared" ref="AF9" si="25">AF5-AF8</f>
+        <f t="shared" ref="AF9" si="30">AF5-AF8</f>
         <v>7166</v>
       </c>
       <c r="AG9" s="9">
-        <f t="shared" ref="AG9" si="26">AG5-AG8</f>
+        <f t="shared" ref="AG9" si="31">AG5-AG8</f>
         <v>7339</v>
       </c>
       <c r="AH9" s="9">
-        <f t="shared" ref="AH9:AL9" si="27">AH5-AH8</f>
+        <f t="shared" ref="AH9:AL9" si="32">AH5-AH8</f>
         <v>7776</v>
       </c>
       <c r="AI9" s="9">
-        <f t="shared" si="27"/>
-        <v>7612.5720000000001</v>
+        <f t="shared" si="32"/>
+        <v>7564</v>
       </c>
       <c r="AJ9" s="9">
-        <f t="shared" si="27"/>
-        <v>7698.3169000000016</v>
+        <f t="shared" si="32"/>
+        <v>7994</v>
       </c>
       <c r="AK9" s="9">
-        <f t="shared" si="27"/>
-        <v>7726.1466999999993</v>
+        <f t="shared" si="32"/>
+        <v>8060.8750000000009</v>
       </c>
       <c r="AL9" s="9">
-        <f t="shared" si="27"/>
-        <v>8075.9902000000011</v>
+        <f t="shared" si="32"/>
+        <v>8311.3201000000008</v>
       </c>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
@@ -2460,47 +2452,47 @@
         <v>29252</v>
       </c>
       <c r="AZ9" s="9">
-        <f t="shared" ref="AZ9" si="28">AZ5-AZ8</f>
-        <v>31153.505800000003</v>
+        <f t="shared" ref="AZ9" si="33">AZ5-AZ8</f>
+        <v>31036.355100000004</v>
       </c>
       <c r="BA9" s="9">
         <f>BA5*0.78</f>
         <v>32898.165300000008</v>
       </c>
       <c r="BB9" s="9">
-        <f t="shared" ref="BB9:BJ9" si="29">BB5*0.78</f>
+        <f t="shared" ref="BB9:BJ9" si="34">BB5*0.78</f>
         <v>34214.091912000011</v>
       </c>
       <c r="BC9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>35240.514669360011</v>
       </c>
       <c r="BD9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>36297.730109440818</v>
       </c>
       <c r="BE9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>37386.662012724039</v>
       </c>
       <c r="BF9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>38134.395252978524</v>
       </c>
       <c r="BG9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>38897.083158038091</v>
       </c>
       <c r="BH9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>39675.024821198858</v>
       </c>
       <c r="BI9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>40468.525317622836</v>
       </c>
       <c r="BJ9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>41277.895823975297</v>
       </c>
     </row>
@@ -2605,12 +2597,10 @@
         <v>1420</v>
       </c>
       <c r="AI10" s="5">
-        <f>AE10*1.11</f>
-        <v>1518.4800000000002</v>
+        <v>1460</v>
       </c>
       <c r="AJ10" s="5">
-        <f>AF10*1.12</f>
-        <v>1510.88</v>
+        <v>1481</v>
       </c>
       <c r="AK10" s="5">
         <f>AG10*1.11</f>
@@ -2658,47 +2648,47 @@
       </c>
       <c r="AZ10" s="5">
         <f>SUM(AI10:AL10)</f>
-        <v>6053.92</v>
+        <v>5965.5599999999995</v>
       </c>
       <c r="BA10" s="5">
         <f>AZ10*1.06</f>
-        <v>6417.1552000000001</v>
+        <v>6323.4935999999998</v>
       </c>
       <c r="BB10" s="5">
         <f>BA10*1.04</f>
-        <v>6673.8414080000002</v>
+        <v>6576.433344</v>
       </c>
       <c r="BC10" s="5">
-        <f t="shared" ref="BC10" si="30">BB10*1.03</f>
-        <v>6874.0566502400006</v>
+        <f t="shared" ref="BC10" si="35">BB10*1.03</f>
+        <v>6773.72634432</v>
       </c>
       <c r="BD10" s="5">
         <f>BC10*1.02</f>
-        <v>7011.5377832448012</v>
+        <v>6909.2008712063998</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10*1.02</f>
-        <v>7151.7685389096969</v>
+        <v>7047.3848886305277</v>
       </c>
       <c r="BF10" s="5">
         <f>BE10*1.01</f>
-        <v>7223.286224298794</v>
+        <v>7117.8587375168327</v>
       </c>
       <c r="BG10" s="5">
-        <f t="shared" ref="BG10:BJ10" si="31">BF10*1.01</f>
-        <v>7295.5190865417817</v>
+        <f t="shared" ref="BG10:BJ10" si="36">BF10*1.01</f>
+        <v>7189.0373248920014</v>
       </c>
       <c r="BH10" s="5">
-        <f t="shared" si="31"/>
-        <v>7368.4742774071992</v>
+        <f t="shared" si="36"/>
+        <v>7260.9276981409212</v>
       </c>
       <c r="BI10" s="5">
-        <f t="shared" si="31"/>
-        <v>7442.1590201812714</v>
+        <f t="shared" si="36"/>
+        <v>7333.5369751223307</v>
       </c>
       <c r="BJ10" s="5">
-        <f t="shared" si="31"/>
-        <v>7516.5806103830846</v>
+        <f t="shared" si="36"/>
+        <v>7406.8723448735536</v>
       </c>
     </row>
     <row r="11" spans="2:62" x14ac:dyDescent="0.3">
@@ -2803,20 +2793,18 @@
         <v>3471</v>
       </c>
       <c r="AI11" s="5">
-        <f>AI5*0.34</f>
-        <v>3340.5952000000007</v>
+        <v>3429</v>
       </c>
       <c r="AJ11" s="5">
-        <f t="shared" ref="AJ11:AL11" si="32">AJ5*0.34</f>
-        <v>3380.990600000001</v>
+        <v>3443</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" si="32"/>
-        <v>3394.0126</v>
+        <f t="shared" ref="AK11:AL11" si="37">AK5*0.34</f>
+        <v>3514.7670000000007</v>
       </c>
       <c r="AL11" s="5">
-        <f t="shared" si="32"/>
-        <v>3527.9964000000004</v>
+        <f t="shared" si="37"/>
+        <v>3624.3966</v>
       </c>
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
@@ -2856,7 +2844,7 @@
       </c>
       <c r="AZ11" s="5">
         <f>SUM(AI11:AL11)</f>
-        <v>13643.594800000003</v>
+        <v>14011.1636</v>
       </c>
       <c r="BA11" s="5">
         <f>BA5*0.33</f>
@@ -2871,31 +2859,31 @@
         <v>14457.647043840005</v>
       </c>
       <c r="BD11" s="5">
-        <f t="shared" ref="BD11:BJ11" si="33">BD5*0.32</f>
+        <f t="shared" ref="BD11:BJ11" si="38">BD5*0.32</f>
         <v>14891.376455155207</v>
       </c>
       <c r="BE11" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>15338.117748809862</v>
       </c>
       <c r="BF11" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>15644.880103786059</v>
       </c>
       <c r="BG11" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>15957.777705861781</v>
       </c>
       <c r="BH11" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>16276.93325997902</v>
       </c>
       <c r="BI11" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>16602.471925178597</v>
       </c>
       <c r="BJ11" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>16934.521363682172</v>
       </c>
     </row>
@@ -3000,20 +2988,18 @@
         <v>767</v>
       </c>
       <c r="AI12" s="5">
-        <f>AE12*1.25</f>
-        <v>808.75</v>
+        <v>697</v>
       </c>
       <c r="AJ12" s="5">
-        <f>AF12*1.15</f>
-        <v>817.65</v>
+        <v>734</v>
       </c>
       <c r="AK12" s="5">
-        <f>AG12*1.16</f>
-        <v>824.76</v>
+        <f>AG12*1.07</f>
+        <v>760.7700000000001</v>
       </c>
       <c r="AL12" s="5">
-        <f>AH12*1.12</f>
-        <v>859.04000000000008</v>
+        <f>AH12*1.05</f>
+        <v>805.35</v>
       </c>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
@@ -3053,47 +3039,47 @@
       </c>
       <c r="AZ12" s="5">
         <f>SUM(AI12:AL12)</f>
-        <v>3310.2</v>
+        <v>2997.12</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" ref="BA12" si="34">AZ12*1.03</f>
-        <v>3409.5059999999999</v>
+        <f t="shared" ref="BA12" si="39">AZ12*1.03</f>
+        <v>3087.0335999999998</v>
       </c>
       <c r="BB12" s="5">
         <f>BA12*1.02</f>
-        <v>3477.6961200000001</v>
+        <v>3148.7742719999997</v>
       </c>
       <c r="BC12" s="5">
         <f>BB12*1.02</f>
-        <v>3547.2500424</v>
+        <v>3211.7497574399995</v>
       </c>
       <c r="BD12" s="5">
-        <f t="shared" ref="BD12:BE12" si="35">BC12*1.02</f>
-        <v>3618.1950432479998</v>
+        <f t="shared" ref="BD12:BE12" si="40">BC12*1.02</f>
+        <v>3275.9847525887994</v>
       </c>
       <c r="BE12" s="5">
-        <f t="shared" si="35"/>
-        <v>3690.55894411296</v>
+        <f t="shared" si="40"/>
+        <v>3341.5044476405756</v>
       </c>
       <c r="BF12" s="5">
-        <f t="shared" ref="BF12" si="36">BE12*1.02</f>
-        <v>3764.3701229952194</v>
+        <f t="shared" ref="BF12" si="41">BE12*1.02</f>
+        <v>3408.3345365933869</v>
       </c>
       <c r="BG12" s="5">
-        <f t="shared" ref="BG12" si="37">BF12*1.02</f>
-        <v>3839.657525455124</v>
+        <f t="shared" ref="BG12" si="42">BF12*1.02</f>
+        <v>3476.5012273252546</v>
       </c>
       <c r="BH12" s="5">
-        <f t="shared" ref="BH12" si="38">BG12*1.02</f>
-        <v>3916.4506759642263</v>
+        <f t="shared" ref="BH12" si="43">BG12*1.02</f>
+        <v>3546.0312518717597</v>
       </c>
       <c r="BI12" s="5">
-        <f t="shared" ref="BI12" si="39">BH12*1.02</f>
-        <v>3994.779689483511</v>
+        <f t="shared" ref="BI12" si="44">BH12*1.02</f>
+        <v>3616.9518769091951</v>
       </c>
       <c r="BJ12" s="5">
-        <f t="shared" ref="BJ12" si="40">BI12*1.02</f>
-        <v>4074.6752832731813</v>
+        <f t="shared" ref="BJ12" si="45">BI12*1.02</f>
+        <v>3689.2909144473792</v>
       </c>
     </row>
     <row r="13" spans="2:62" x14ac:dyDescent="0.3">
@@ -3165,15 +3151,13 @@
         <v>298</v>
       </c>
       <c r="AI13" s="5">
-        <f>AE13*1.05</f>
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AJ13" s="5">
-        <f t="shared" ref="AJ13:AK13" si="41">AF13*1.05</f>
-        <v>103.95</v>
+        <v>4</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="AK13" si="46">AG13*1.05</f>
         <v>58.800000000000004</v>
       </c>
       <c r="AL13" s="5">
@@ -3206,47 +3190,47 @@
       </c>
       <c r="AZ13" s="5">
         <f>SUM(AI13:AL13)</f>
-        <v>409.55</v>
+        <v>337.20000000000005</v>
       </c>
       <c r="BA13" s="5">
-        <f t="shared" ref="BA13:BE13" si="42">AZ13*0.5</f>
-        <v>204.77500000000001</v>
+        <f t="shared" ref="BA13:BE13" si="47">AZ13*0.5</f>
+        <v>168.60000000000002</v>
       </c>
       <c r="BB13" s="5">
-        <f t="shared" si="42"/>
-        <v>102.3875</v>
+        <f t="shared" si="47"/>
+        <v>84.300000000000011</v>
       </c>
       <c r="BC13" s="5">
-        <f t="shared" si="42"/>
-        <v>51.193750000000001</v>
+        <f t="shared" si="47"/>
+        <v>42.150000000000006</v>
       </c>
       <c r="BD13" s="5">
-        <f t="shared" si="42"/>
-        <v>25.596875000000001</v>
+        <f t="shared" si="47"/>
+        <v>21.075000000000003</v>
       </c>
       <c r="BE13" s="5">
-        <f t="shared" si="42"/>
-        <v>12.7984375</v>
+        <f t="shared" si="47"/>
+        <v>10.537500000000001</v>
       </c>
       <c r="BF13" s="5">
-        <f t="shared" ref="BF13:BJ13" si="43">BE13*0.5</f>
-        <v>6.3992187500000002</v>
+        <f t="shared" ref="BF13:BJ13" si="48">BE13*0.5</f>
+        <v>5.2687500000000007</v>
       </c>
       <c r="BG13" s="5">
-        <f t="shared" si="43"/>
-        <v>3.1996093750000001</v>
+        <f t="shared" si="48"/>
+        <v>2.6343750000000004</v>
       </c>
       <c r="BH13" s="5">
-        <f t="shared" si="43"/>
-        <v>1.5998046875</v>
+        <f t="shared" si="48"/>
+        <v>1.3171875000000002</v>
       </c>
       <c r="BI13" s="5">
-        <f t="shared" si="43"/>
-        <v>0.79990234375000002</v>
+        <f t="shared" si="48"/>
+        <v>0.65859375000000009</v>
       </c>
       <c r="BJ13" s="5">
-        <f t="shared" si="43"/>
-        <v>0.39995117187500001</v>
+        <f t="shared" si="48"/>
+        <v>0.32929687500000004</v>
       </c>
     </row>
     <row r="14" spans="2:62" x14ac:dyDescent="0.3">
@@ -3254,148 +3238,148 @@
         <v>28</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" ref="C14:P14" si="44">SUM(C10:C12)</f>
+        <f t="shared" ref="C14:P14" si="49">SUM(C10:C12)</f>
         <v>1742</v>
       </c>
       <c r="D14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>1823</v>
       </c>
       <c r="E14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>1832</v>
       </c>
       <c r="F14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>1916</v>
       </c>
       <c r="G14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2048</v>
       </c>
       <c r="H14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2317</v>
       </c>
       <c r="I14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2411</v>
       </c>
       <c r="J14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2520</v>
       </c>
       <c r="K14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2613</v>
       </c>
       <c r="L14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2972</v>
       </c>
       <c r="M14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>3314</v>
       </c>
       <c r="N14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>3667</v>
       </c>
       <c r="O14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>3751</v>
       </c>
       <c r="P14" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>3662</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" ref="Q14:R14" si="45">SUM(Q10:Q12)</f>
+        <f t="shared" ref="Q14:R14" si="50">SUM(Q10:Q12)</f>
         <v>3801</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="50"/>
         <v>4145</v>
       </c>
       <c r="S14" s="5">
-        <f t="shared" ref="S14:AH14" si="46">SUM(S10:S13)</f>
+        <f t="shared" ref="S14:AH14" si="51">SUM(S10:S13)</f>
         <v>4054</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>4395</v>
       </c>
       <c r="U14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>4981</v>
       </c>
       <c r="V14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5488</v>
       </c>
       <c r="W14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5346</v>
       </c>
       <c r="X14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5400</v>
       </c>
       <c r="Y14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5289</v>
       </c>
       <c r="Z14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5927</v>
       </c>
       <c r="AA14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5710</v>
       </c>
       <c r="AB14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5014</v>
       </c>
       <c r="AC14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5064</v>
       </c>
       <c r="AD14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5517</v>
       </c>
       <c r="AE14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5262</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5383</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5446</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>5956</v>
       </c>
       <c r="AI14" s="5">
-        <f t="shared" ref="AI14:AL14" si="47">SUM(AI10:AI13)</f>
-        <v>5676.2252000000008</v>
+        <f t="shared" ref="AI14:AL14" si="52">SUM(AI10:AI13)</f>
+        <v>5622</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" si="47"/>
-        <v>5813.4706000000006</v>
+        <f t="shared" si="52"/>
+        <v>5662</v>
       </c>
       <c r="AK14" s="5">
-        <f t="shared" si="47"/>
-        <v>5782.7326000000003</v>
+        <f t="shared" si="52"/>
+        <v>5839.4970000000012</v>
       </c>
       <c r="AL14" s="5">
-        <f t="shared" si="47"/>
-        <v>6144.8364000000001</v>
+        <f t="shared" si="52"/>
+        <v>6187.5465999999997</v>
       </c>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
@@ -3422,60 +3406,60 @@
         <v>18918</v>
       </c>
       <c r="AW14" s="5">
-        <f t="shared" ref="AW14:BE14" si="48">SUM(AW10:AW13)</f>
+        <f t="shared" ref="AW14:BE14" si="53">SUM(AW10:AW13)</f>
         <v>21962</v>
       </c>
       <c r="AX14" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
         <v>21305</v>
       </c>
       <c r="AY14" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
         <v>22047</v>
       </c>
       <c r="AZ14" s="5">
-        <f t="shared" si="48"/>
-        <v>23417.264800000004</v>
+        <f t="shared" si="53"/>
+        <v>23311.043599999997</v>
       </c>
       <c r="BA14" s="5">
-        <f t="shared" si="48"/>
-        <v>23949.890750000006</v>
+        <f t="shared" si="53"/>
+        <v>23497.581750000001</v>
       </c>
       <c r="BB14" s="5">
-        <f t="shared" si="48"/>
-        <v>24290.475556000009</v>
+        <f t="shared" si="53"/>
+        <v>23846.058144000002</v>
       </c>
       <c r="BC14" s="5">
-        <f t="shared" si="48"/>
-        <v>24930.147486480004</v>
+        <f t="shared" si="53"/>
+        <v>24485.273145600007</v>
       </c>
       <c r="BD14" s="5">
-        <f t="shared" si="48"/>
-        <v>25546.706156648008</v>
+        <f t="shared" si="53"/>
+        <v>25097.637078950407</v>
       </c>
       <c r="BE14" s="5">
-        <f t="shared" si="48"/>
-        <v>26193.243669332518</v>
+        <f t="shared" si="53"/>
+        <v>25737.544585080963</v>
       </c>
       <c r="BF14" s="5">
-        <f t="shared" ref="BF14" si="49">SUM(BF10:BF13)</f>
-        <v>26638.935669830073</v>
+        <f t="shared" ref="BF14" si="54">SUM(BF10:BF13)</f>
+        <v>26176.342127896278</v>
       </c>
       <c r="BG14" s="5">
-        <f t="shared" ref="BG14" si="50">SUM(BG10:BG13)</f>
-        <v>27096.153927233685</v>
+        <f t="shared" ref="BG14" si="55">SUM(BG10:BG13)</f>
+        <v>26625.950633079039</v>
       </c>
       <c r="BH14" s="5">
-        <f t="shared" ref="BH14" si="51">SUM(BH10:BH13)</f>
-        <v>27563.458018037945</v>
+        <f t="shared" ref="BH14" si="56">SUM(BH10:BH13)</f>
+        <v>27085.209397491701</v>
       </c>
       <c r="BI14" s="5">
-        <f t="shared" ref="BI14" si="52">SUM(BI10:BI13)</f>
-        <v>28040.210537187133</v>
+        <f t="shared" ref="BI14" si="57">SUM(BI10:BI13)</f>
+        <v>27553.619370960121</v>
       </c>
       <c r="BJ14" s="5">
-        <f t="shared" ref="BJ14" si="53">SUM(BJ10:BJ13)</f>
-        <v>28526.177208510311</v>
+        <f t="shared" ref="BJ14" si="58">SUM(BJ10:BJ13)</f>
+        <v>28031.013919878103</v>
       </c>
     </row>
     <row r="15" spans="2:62" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3483,148 +3467,148 @@
         <v>29</v>
       </c>
       <c r="C15" s="9">
-        <f t="shared" ref="C15:P15" si="54">C9-C14</f>
+        <f t="shared" ref="C15:P15" si="59">C9-C14</f>
         <v>4</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>84</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>155</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>211</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>191</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>115</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>92</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>137</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>210</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>58</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>65</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>-36</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>-140</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>178</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" ref="Q15:S15" si="55">Q9-Q14</f>
+        <f t="shared" ref="Q15:S15" si="60">Q9-Q14</f>
         <v>263.25</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>193</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>354</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" ref="T15" si="56">T9-T14</f>
+        <f t="shared" ref="T15" si="61">T9-T14</f>
         <v>332</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" ref="U15" si="57">U9-U14</f>
+        <f t="shared" ref="U15" si="62">U9-U14</f>
         <v>38</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" ref="V15:W15" si="58">V9-V14</f>
+        <f t="shared" ref="V15:W15" si="63">V9-V14</f>
         <v>-176</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="63"/>
         <v>20</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" ref="X15" si="59">X9-X14</f>
+        <f t="shared" ref="X15" si="64">X9-X14</f>
         <v>193</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" ref="Y15" si="60">Y9-Y14</f>
+        <f t="shared" ref="Y15" si="65">Y9-Y14</f>
         <v>460</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" ref="Z15:AA15" si="61">Z9-Z14</f>
+        <f t="shared" ref="Z15:AA15" si="66">Z9-Z14</f>
         <v>357</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>412</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" ref="AB15" si="62">AB9-AB14</f>
+        <f t="shared" ref="AB15" si="67">AB9-AB14</f>
         <v>1476</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" ref="AC15" si="63">AC9-AC14</f>
+        <f t="shared" ref="AC15" si="68">AC9-AC14</f>
         <v>1501</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" ref="AD15:AE15" si="64">AD9-AD14</f>
+        <f t="shared" ref="AD15:AE15" si="69">AD9-AD14</f>
         <v>1622</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>1709</v>
       </c>
       <c r="AF15" s="9">
-        <f t="shared" ref="AF15" si="65">AF9-AF14</f>
+        <f t="shared" ref="AF15" si="70">AF9-AF14</f>
         <v>1783</v>
       </c>
       <c r="AG15" s="9">
-        <f t="shared" ref="AG15" si="66">AG9-AG14</f>
+        <f t="shared" ref="AG15" si="71">AG9-AG14</f>
         <v>1893</v>
       </c>
       <c r="AH15" s="9">
-        <f t="shared" ref="AH15:AL15" si="67">AH9-AH14</f>
+        <f t="shared" ref="AH15:AL15" si="72">AH9-AH14</f>
         <v>1820</v>
       </c>
       <c r="AI15" s="9">
-        <f t="shared" si="67"/>
-        <v>1936.3467999999993</v>
+        <f t="shared" si="72"/>
+        <v>1942</v>
       </c>
       <c r="AJ15" s="9">
-        <f t="shared" si="67"/>
-        <v>1884.8463000000011</v>
+        <f t="shared" si="72"/>
+        <v>2332</v>
       </c>
       <c r="AK15" s="9">
-        <f t="shared" si="67"/>
-        <v>1943.4140999999991</v>
+        <f t="shared" si="72"/>
+        <v>2221.3779999999997</v>
       </c>
       <c r="AL15" s="9">
-        <f t="shared" si="67"/>
-        <v>1931.153800000001</v>
+        <f t="shared" si="72"/>
+        <v>2123.7735000000011</v>
       </c>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
@@ -3647,64 +3631,64 @@
         <v>455</v>
       </c>
       <c r="AV15" s="9">
-        <f t="shared" ref="AV15:BE15" si="68">AV9-AV14</f>
+        <f t="shared" ref="AV15:BE15" si="73">AV9-AV14</f>
         <v>951</v>
       </c>
       <c r="AW15" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>1030</v>
       </c>
       <c r="AX15" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>5011</v>
       </c>
       <c r="AY15" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="73"/>
         <v>7205</v>
       </c>
       <c r="AZ15" s="9">
-        <f t="shared" si="68"/>
-        <v>7736.2409999999982</v>
+        <f t="shared" si="73"/>
+        <v>7725.3115000000071</v>
       </c>
       <c r="BA15" s="9">
-        <f t="shared" si="68"/>
-        <v>8948.2745500000019</v>
+        <f t="shared" si="73"/>
+        <v>9400.5835500000067</v>
       </c>
       <c r="BB15" s="9">
-        <f t="shared" si="68"/>
-        <v>9923.6163560000023</v>
+        <f t="shared" si="73"/>
+        <v>10368.033768000008</v>
       </c>
       <c r="BC15" s="9">
-        <f t="shared" si="68"/>
-        <v>10310.367182880007</v>
+        <f t="shared" si="73"/>
+        <v>10755.241523760003</v>
       </c>
       <c r="BD15" s="9">
-        <f t="shared" si="68"/>
-        <v>10751.02395279281</v>
+        <f t="shared" si="73"/>
+        <v>11200.09303049041</v>
       </c>
       <c r="BE15" s="9">
-        <f t="shared" si="68"/>
-        <v>11193.41834339152</v>
+        <f t="shared" si="73"/>
+        <v>11649.117427643076</v>
       </c>
       <c r="BF15" s="9">
-        <f t="shared" ref="BF15:BJ15" si="69">BF9-BF14</f>
-        <v>11495.459583148451</v>
+        <f t="shared" ref="BF15:BJ15" si="74">BF9-BF14</f>
+        <v>11958.053125082246</v>
       </c>
       <c r="BG15" s="9">
-        <f t="shared" si="69"/>
-        <v>11800.929230804406</v>
+        <f t="shared" si="74"/>
+        <v>12271.132524959052</v>
       </c>
       <c r="BH15" s="9">
-        <f t="shared" si="69"/>
-        <v>12111.566803160913</v>
+        <f t="shared" si="74"/>
+        <v>12589.815423707158</v>
       </c>
       <c r="BI15" s="9">
-        <f t="shared" si="69"/>
-        <v>12428.314780435703</v>
+        <f t="shared" si="74"/>
+        <v>12914.905946662715</v>
       </c>
       <c r="BJ15" s="9">
-        <f t="shared" si="69"/>
-        <v>12751.718615464986</v>
+        <f t="shared" si="74"/>
+        <v>13246.881904097194</v>
       </c>
     </row>
     <row r="16" spans="2:62" x14ac:dyDescent="0.3">
@@ -3813,10 +3797,10 @@
         <v>-96</v>
       </c>
       <c r="AI16" s="5">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AJ16" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AK16" s="5">
         <v>0</v>
@@ -3862,47 +3846,47 @@
       </c>
       <c r="AZ16" s="5">
         <f>SUM(AI16:AL16)</f>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="BA16" s="5">
-        <f t="shared" ref="BA16:BE16" si="70">AZ16*1.03</f>
-        <v>0</v>
+        <f t="shared" ref="BA16:BE16" si="75">AZ16*1.03</f>
+        <v>58.71</v>
       </c>
       <c r="BB16" s="5">
-        <f t="shared" si="70"/>
-        <v>0</v>
+        <f t="shared" si="75"/>
+        <v>60.471299999999999</v>
       </c>
       <c r="BC16" s="5">
-        <f t="shared" si="70"/>
-        <v>0</v>
+        <f t="shared" si="75"/>
+        <v>62.285439000000004</v>
       </c>
       <c r="BD16" s="5">
-        <f t="shared" si="70"/>
-        <v>0</v>
+        <f t="shared" si="75"/>
+        <v>64.154002170000012</v>
       </c>
       <c r="BE16" s="5">
-        <f t="shared" si="70"/>
-        <v>0</v>
+        <f t="shared" si="75"/>
+        <v>66.078622235100013</v>
       </c>
       <c r="BF16" s="5">
-        <f t="shared" ref="BF16" si="71">BE16*1.03</f>
-        <v>0</v>
+        <f t="shared" ref="BF16" si="76">BE16*1.03</f>
+        <v>68.06098090215302</v>
       </c>
       <c r="BG16" s="5">
-        <f t="shared" ref="BG16" si="72">BF16*1.03</f>
-        <v>0</v>
+        <f t="shared" ref="BG16" si="77">BF16*1.03</f>
+        <v>70.102810329217618</v>
       </c>
       <c r="BH16" s="5">
-        <f t="shared" ref="BH16" si="73">BG16*1.03</f>
-        <v>0</v>
+        <f t="shared" ref="BH16" si="78">BG16*1.03</f>
+        <v>72.205894639094154</v>
       </c>
       <c r="BI16" s="5">
-        <f t="shared" ref="BI16" si="74">BH16*1.03</f>
-        <v>0</v>
+        <f t="shared" ref="BI16" si="79">BH16*1.03</f>
+        <v>74.372071478266975</v>
       </c>
       <c r="BJ16" s="5">
-        <f t="shared" ref="BJ16" si="75">BI16*1.03</f>
-        <v>0</v>
+        <f t="shared" ref="BJ16" si="80">BI16*1.03</f>
+        <v>76.603233622614979</v>
       </c>
     </row>
     <row r="17" spans="2:196" x14ac:dyDescent="0.3">
@@ -4006,19 +3990,17 @@
         <v>-72</v>
       </c>
       <c r="AI17" s="5">
-        <f>AE17*0.9</f>
-        <v>-108.9</v>
+        <v>-95</v>
       </c>
       <c r="AJ17" s="5">
-        <f t="shared" ref="AJ17:AL17" si="76">AF17*0.9</f>
-        <v>-81.900000000000006</v>
+        <v>-68</v>
       </c>
       <c r="AK17" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" ref="AK17:AL17" si="81">AG17*0.9</f>
         <v>-63</v>
       </c>
       <c r="AL17" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" si="81"/>
         <v>-64.8</v>
       </c>
       <c r="AM17" s="5"/>
@@ -4059,47 +4041,47 @@
       </c>
       <c r="AZ17" s="5">
         <f>SUM(AI17:AL17)</f>
-        <v>-318.60000000000002</v>
+        <v>-290.8</v>
       </c>
       <c r="BA17" s="5">
-        <f t="shared" ref="BA17:BE17" si="77">AZ17*0.97</f>
-        <v>-309.04200000000003</v>
+        <f t="shared" ref="BA17:BE17" si="82">AZ17*0.97</f>
+        <v>-282.07600000000002</v>
       </c>
       <c r="BB17" s="5">
-        <f t="shared" si="77"/>
-        <v>-299.77074000000005</v>
+        <f t="shared" si="82"/>
+        <v>-273.61372</v>
       </c>
       <c r="BC17" s="5">
-        <f t="shared" si="77"/>
-        <v>-290.77761780000003</v>
+        <f t="shared" si="82"/>
+        <v>-265.40530839999997</v>
       </c>
       <c r="BD17" s="5">
-        <f t="shared" si="77"/>
-        <v>-282.05428926600001</v>
+        <f t="shared" si="82"/>
+        <v>-257.44314914799997</v>
       </c>
       <c r="BE17" s="5">
-        <f t="shared" si="77"/>
-        <v>-273.59266058802001</v>
+        <f t="shared" si="82"/>
+        <v>-249.71985467355998</v>
       </c>
       <c r="BF17" s="5">
-        <f t="shared" ref="BF17" si="78">BE17*0.97</f>
-        <v>-265.38488077037943</v>
+        <f t="shared" ref="BF17" si="83">BE17*0.97</f>
+        <v>-242.22825903335317</v>
       </c>
       <c r="BG17" s="5">
-        <f t="shared" ref="BG17" si="79">BF17*0.97</f>
-        <v>-257.42333434726805</v>
+        <f t="shared" ref="BG17" si="84">BF17*0.97</f>
+        <v>-234.96141126235256</v>
       </c>
       <c r="BH17" s="5">
-        <f t="shared" ref="BH17" si="80">BG17*0.97</f>
-        <v>-249.70063431685</v>
+        <f t="shared" ref="BH17" si="85">BG17*0.97</f>
+        <v>-227.91256892448197</v>
       </c>
       <c r="BI17" s="5">
-        <f t="shared" ref="BI17" si="81">BH17*0.97</f>
-        <v>-242.20961528734449</v>
+        <f t="shared" ref="BI17" si="86">BH17*0.97</f>
+        <v>-221.07519185674749</v>
       </c>
       <c r="BJ17" s="5">
-        <f t="shared" ref="BJ17" si="82">BI17*0.97</f>
-        <v>-234.94332682872414</v>
+        <f t="shared" ref="BJ17" si="87">BI17*0.97</f>
+        <v>-214.44293610104506</v>
       </c>
     </row>
     <row r="18" spans="2:196" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4107,148 +4089,148 @@
         <v>32</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:P18" si="83">C15-C16-C17</f>
+        <f t="shared" ref="C18:P18" si="88">C15-C16-C17</f>
         <v>-10</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>63</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>146</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>221</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>385</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>231</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>128</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>239</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>482</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>164</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>64</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>-4</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>47</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="88"/>
         <v>839</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" ref="Q18:S18" si="84">Q15-Q16-Q17</f>
+        <f t="shared" ref="Q18:S18" si="89">Q15-Q16-Q17</f>
         <v>1289.25</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="89"/>
         <v>425</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="89"/>
         <v>604</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18" si="85">T15-T16-T17</f>
+        <f t="shared" ref="T18" si="90">T15-T16-T17</f>
         <v>826</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" ref="U18" si="86">U15-U16-U17</f>
+        <f t="shared" ref="U18" si="91">U15-U16-U17</f>
         <v>299</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" ref="V18:W18" si="87">V15-V16-V17</f>
+        <f t="shared" ref="V18:W18" si="92">V15-V16-V17</f>
         <v>-197</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="92"/>
         <v>-29</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" ref="X18" si="88">X15-X16-X17</f>
+        <f t="shared" ref="X18" si="93">X15-X16-X17</f>
         <v>181</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="89">Y15-Y16-Y17</f>
+        <f t="shared" ref="Y18" si="94">Y15-Y16-Y17</f>
         <v>475</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18:AA18" si="90">Z15-Z16-Z17</f>
+        <f t="shared" ref="Z18:AA18" si="95">Z15-Z16-Z17</f>
         <v>33</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="95"/>
         <v>326</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" ref="AB18" si="91">AB15-AB16-AB17</f>
+        <f t="shared" ref="AB18" si="96">AB15-AB16-AB17</f>
         <v>1492</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" ref="AC18" si="92">AC15-AC16-AC17</f>
+        <f t="shared" ref="AC18" si="97">AC15-AC16-AC17</f>
         <v>1487</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" ref="AD18:AE18" si="93">AD15-AD16-AD17</f>
+        <f t="shared" ref="AD18:AE18" si="98">AD15-AD16-AD17</f>
         <v>1645</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="98"/>
         <v>1867</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18" si="94">AF15-AF16-AF17</f>
+        <f t="shared" ref="AF18" si="99">AF15-AF16-AF17</f>
         <v>1837</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" ref="AG18" si="95">AG15-AG16-AG17</f>
+        <f t="shared" ref="AG18" si="100">AG15-AG16-AG17</f>
         <v>1746</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" ref="AH18:AL18" si="96">AH15-AH16-AH17</f>
+        <f t="shared" ref="AH18:AL18" si="101">AH15-AH16-AH17</f>
         <v>1988</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="96"/>
-        <v>2045.2467999999994</v>
+        <f t="shared" si="101"/>
+        <v>1974</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="96"/>
-        <v>1966.7463000000012</v>
+        <f t="shared" si="101"/>
+        <v>2406</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="96"/>
-        <v>2006.4140999999991</v>
+        <f t="shared" si="101"/>
+        <v>2284.3779999999997</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="96"/>
-        <v>1995.9538000000009</v>
+        <f t="shared" si="101"/>
+        <v>2188.5735000000013</v>
       </c>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
@@ -4271,64 +4253,64 @@
         <v>2561</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" ref="AV18:BE18" si="97">AV15-AV16-AV17</f>
+        <f t="shared" ref="AV18:BE18" si="102">AV15-AV16-AV17</f>
         <v>1935</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>660</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>4950</v>
       </c>
       <c r="AY18" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="102"/>
         <v>7438</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" si="97"/>
-        <v>8054.8409999999985</v>
+        <f t="shared" si="102"/>
+        <v>7959.1115000000073</v>
       </c>
       <c r="BA18" s="9">
-        <f t="shared" si="97"/>
-        <v>9257.3165500000014</v>
+        <f t="shared" si="102"/>
+        <v>9623.9495500000085</v>
       </c>
       <c r="BB18" s="9">
-        <f t="shared" si="97"/>
-        <v>10223.387096000002</v>
+        <f t="shared" si="102"/>
+        <v>10581.176188000009</v>
       </c>
       <c r="BC18" s="9">
-        <f t="shared" si="97"/>
-        <v>10601.144800680007</v>
+        <f t="shared" si="102"/>
+        <v>10958.361393160005</v>
       </c>
       <c r="BD18" s="9">
-        <f t="shared" si="97"/>
-        <v>11033.078242058809</v>
+        <f t="shared" si="102"/>
+        <v>11393.382177468411</v>
       </c>
       <c r="BE18" s="9">
-        <f t="shared" si="97"/>
-        <v>11467.01100397954</v>
+        <f t="shared" si="102"/>
+        <v>11832.758660081536</v>
       </c>
       <c r="BF18" s="9">
-        <f t="shared" ref="BF18:BJ18" si="98">BF15-BF16-BF17</f>
-        <v>11760.844463918831</v>
+        <f t="shared" ref="BF18:BJ18" si="103">BF15-BF16-BF17</f>
+        <v>12132.220403213445</v>
       </c>
       <c r="BG18" s="9">
-        <f t="shared" si="98"/>
-        <v>12058.352565151674</v>
+        <f t="shared" si="103"/>
+        <v>12435.991125892187</v>
       </c>
       <c r="BH18" s="9">
-        <f t="shared" si="98"/>
-        <v>12361.267437477763</v>
+        <f t="shared" si="103"/>
+        <v>12745.522097992545</v>
       </c>
       <c r="BI18" s="9">
-        <f t="shared" si="98"/>
-        <v>12670.524395723047</v>
+        <f t="shared" si="103"/>
+        <v>13061.609067041196</v>
       </c>
       <c r="BJ18" s="9">
-        <f t="shared" si="98"/>
-        <v>12986.661942293711</v>
+        <f t="shared" si="103"/>
+        <v>13384.721606575624</v>
       </c>
     </row>
     <row r="19" spans="2:196" x14ac:dyDescent="0.3">
@@ -4432,20 +4414,18 @@
         <v>280</v>
       </c>
       <c r="AI19" s="5">
-        <f>AI18*0.18</f>
-        <v>368.1444239999999</v>
+        <v>433</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" ref="AJ19:AL19" si="99">AJ18*0.18</f>
-        <v>354.01433400000019</v>
+        <v>519</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="99"/>
-        <v>361.15453799999983</v>
+        <f t="shared" ref="AK19:AL19" si="104">AK18*0.18</f>
+        <v>411.18803999999994</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" si="99"/>
-        <v>359.27168400000016</v>
+        <f t="shared" si="104"/>
+        <v>393.9432300000002</v>
       </c>
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
@@ -4485,47 +4465,47 @@
       </c>
       <c r="AZ19" s="5">
         <f>SUM(AI19:AL19)</f>
-        <v>1442.5849800000001</v>
+        <v>1757.1312700000003</v>
       </c>
       <c r="BA19" s="5">
         <f>BA18*0.18</f>
-        <v>1666.3169790000002</v>
+        <v>1732.3109190000014</v>
       </c>
       <c r="BB19" s="5">
-        <f t="shared" ref="BB19:BJ19" si="100">BB18*0.18</f>
-        <v>1840.2096772800003</v>
+        <f t="shared" ref="BB19:BJ19" si="105">BB18*0.18</f>
+        <v>1904.6117138400014</v>
       </c>
       <c r="BC19" s="5">
-        <f t="shared" si="100"/>
-        <v>1908.2060641224014</v>
+        <f t="shared" si="105"/>
+        <v>1972.5050507688009</v>
       </c>
       <c r="BD19" s="5">
-        <f t="shared" si="100"/>
-        <v>1985.9540835705857</v>
+        <f t="shared" si="105"/>
+        <v>2050.8087919443137</v>
       </c>
       <c r="BE19" s="5">
-        <f t="shared" si="100"/>
-        <v>2064.0619807163171</v>
+        <f t="shared" si="105"/>
+        <v>2129.8965588146762</v>
       </c>
       <c r="BF19" s="5">
-        <f t="shared" si="100"/>
-        <v>2116.9520035053897</v>
+        <f t="shared" si="105"/>
+        <v>2183.7996725784201</v>
       </c>
       <c r="BG19" s="5">
-        <f t="shared" si="100"/>
-        <v>2170.5034617273013</v>
+        <f t="shared" si="105"/>
+        <v>2238.4784026605935</v>
       </c>
       <c r="BH19" s="5">
-        <f t="shared" si="100"/>
-        <v>2225.0281387459972</v>
+        <f t="shared" si="105"/>
+        <v>2294.193977638658</v>
       </c>
       <c r="BI19" s="5">
-        <f t="shared" si="100"/>
-        <v>2280.6943912301485</v>
+        <f t="shared" si="105"/>
+        <v>2351.0896320674151</v>
       </c>
       <c r="BJ19" s="5">
-        <f t="shared" si="100"/>
-        <v>2337.5991496128677</v>
+        <f t="shared" si="105"/>
+        <v>2409.2498891836121</v>
       </c>
     </row>
     <row r="20" spans="2:196" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4533,148 +4513,148 @@
         <v>34</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:P20" si="101">C18-C19</f>
+        <f t="shared" ref="C20:P20" si="106">C18-C19</f>
         <v>1</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>46</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>107</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>206</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>344</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>299</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>105</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>362</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>392</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>91</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>-109</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>-248</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>99</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="106"/>
         <v>2625</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20:S20" si="102">Q18-Q19</f>
+        <f t="shared" ref="Q20:S20" si="107">Q18-Q19</f>
         <v>1120.25</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>267</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="107"/>
         <v>469</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="103">T18-T19</f>
+        <f t="shared" ref="T20" si="108">T18-T19</f>
         <v>535</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="104">U18-U19</f>
+        <f t="shared" ref="U20" si="109">U18-U19</f>
         <v>468</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20:W20" si="105">V18-V19</f>
+        <f t="shared" ref="V20:W20" si="110">V18-V19</f>
         <v>-28</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="110"/>
         <v>28</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20" si="106">X18-X19</f>
+        <f t="shared" ref="X20" si="111">X18-X19</f>
         <v>68</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="107">Y18-Y19</f>
+        <f t="shared" ref="Y20" si="112">Y18-Y19</f>
         <v>210</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20:AA20" si="108">Z18-Z19</f>
+        <f t="shared" ref="Z20:AA20" si="113">Z18-Z19</f>
         <v>-98</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="113"/>
         <v>199</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" ref="AB20" si="109">AB18-AB19</f>
+        <f t="shared" ref="AB20" si="114">AB18-AB19</f>
         <v>1267</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="110">AC18-AC19</f>
+        <f t="shared" ref="AC20" si="115">AC18-AC19</f>
         <v>1224</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20:AE20" si="111">AD18-AD19</f>
+        <f t="shared" ref="AD20:AE20" si="116">AD18-AD19</f>
         <v>1446</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="116"/>
         <v>1533</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" ref="AF20" si="112">AF18-AF19</f>
+        <f t="shared" ref="AF20" si="117">AF18-AF19</f>
         <v>1429</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" ref="AG20" si="113">AG18-AG19</f>
+        <f t="shared" ref="AG20" si="118">AG18-AG19</f>
         <v>1527</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" ref="AH20:AL20" si="114">AH18-AH19</f>
+        <f t="shared" ref="AH20:AL20" si="119">AH18-AH19</f>
         <v>1708</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" si="114"/>
-        <v>1677.1023759999996</v>
+        <f t="shared" si="119"/>
+        <v>1541</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="114"/>
-        <v>1612.731966000001</v>
+        <f t="shared" si="119"/>
+        <v>1887</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" si="114"/>
-        <v>1645.2595619999993</v>
+        <f t="shared" si="119"/>
+        <v>1873.1899599999997</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" si="114"/>
-        <v>1636.6821160000009</v>
+        <f t="shared" si="119"/>
+        <v>1794.630270000001</v>
       </c>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
@@ -4697,600 +4677,600 @@
         <v>4072</v>
       </c>
       <c r="AV20" s="9">
-        <f t="shared" ref="AV20:BE20" si="115">AV18-AV19</f>
+        <f t="shared" ref="AV20:BE20" si="120">AV18-AV19</f>
         <v>1847</v>
       </c>
       <c r="AW20" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>208</v>
       </c>
       <c r="AX20" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>4136</v>
       </c>
       <c r="AY20" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>6197</v>
       </c>
       <c r="AZ20" s="9">
-        <f t="shared" si="115"/>
-        <v>6612.2560199999989</v>
+        <f t="shared" si="120"/>
+        <v>6201.9802300000065</v>
       </c>
       <c r="BA20" s="9">
-        <f t="shared" si="115"/>
-        <v>7590.9995710000012</v>
+        <f t="shared" si="120"/>
+        <v>7891.6386310000071</v>
       </c>
       <c r="BB20" s="9">
-        <f t="shared" si="115"/>
-        <v>8383.1774187200026</v>
+        <f t="shared" si="120"/>
+        <v>8676.5644741600081</v>
       </c>
       <c r="BC20" s="9">
-        <f t="shared" si="115"/>
-        <v>8692.9387365576058</v>
+        <f t="shared" si="120"/>
+        <v>8985.8563423912037</v>
       </c>
       <c r="BD20" s="9">
-        <f t="shared" si="115"/>
-        <v>9047.1241584882227</v>
+        <f t="shared" si="120"/>
+        <v>9342.5733855240978</v>
       </c>
       <c r="BE20" s="9">
-        <f t="shared" si="115"/>
-        <v>9402.9490232632234</v>
+        <f t="shared" si="120"/>
+        <v>9702.8621012668591</v>
       </c>
       <c r="BF20" s="9">
-        <f t="shared" ref="BF20:BJ20" si="116">BF18-BF19</f>
-        <v>9643.8924604134409</v>
+        <f t="shared" ref="BF20:BJ20" si="121">BF18-BF19</f>
+        <v>9948.4207306350254</v>
       </c>
       <c r="BG20" s="9">
-        <f t="shared" si="116"/>
-        <v>9887.8491034243725</v>
+        <f t="shared" si="121"/>
+        <v>10197.512723231594</v>
       </c>
       <c r="BH20" s="9">
-        <f t="shared" si="116"/>
-        <v>10136.239298731765</v>
+        <f t="shared" si="121"/>
+        <v>10451.328120353886</v>
       </c>
       <c r="BI20" s="9">
-        <f t="shared" si="116"/>
-        <v>10389.830004492898</v>
+        <f t="shared" si="121"/>
+        <v>10710.519434973781</v>
       </c>
       <c r="BJ20" s="9">
-        <f t="shared" si="116"/>
-        <v>10649.062792680843</v>
+        <f t="shared" si="121"/>
+        <v>10975.471717392011</v>
       </c>
       <c r="BK20" s="1">
         <f>BJ20*(1+$BM$30)</f>
-        <v>10542.572164754034</v>
+        <v>10865.71700021809</v>
       </c>
       <c r="BL20" s="1">
-        <f t="shared" ref="BL20:DW20" si="117">BK20*(1+$BM$30)</f>
-        <v>10437.146443106494</v>
+        <f t="shared" ref="BL20:DW20" si="122">BK20*(1+$BM$30)</f>
+        <v>10757.059830215909</v>
       </c>
       <c r="BM20" s="1">
-        <f t="shared" si="117"/>
-        <v>10332.774978675428</v>
+        <f t="shared" si="122"/>
+        <v>10649.489231913749</v>
       </c>
       <c r="BN20" s="1">
-        <f t="shared" si="117"/>
-        <v>10229.447228888674</v>
+        <f t="shared" si="122"/>
+        <v>10542.994339594612</v>
       </c>
       <c r="BO20" s="1">
-        <f t="shared" si="117"/>
-        <v>10127.152756599788</v>
+        <f t="shared" si="122"/>
+        <v>10437.564396198666</v>
       </c>
       <c r="BP20" s="1">
-        <f t="shared" si="117"/>
-        <v>10025.88122903379</v>
+        <f t="shared" si="122"/>
+        <v>10333.18875223668</v>
       </c>
       <c r="BQ20" s="1">
-        <f t="shared" si="117"/>
-        <v>9925.622416743452</v>
+        <f t="shared" si="122"/>
+        <v>10229.856864714313</v>
       </c>
       <c r="BR20" s="1">
-        <f t="shared" si="117"/>
-        <v>9826.3661925760171</v>
+        <f t="shared" si="122"/>
+        <v>10127.558296067169</v>
       </c>
       <c r="BS20" s="1">
-        <f t="shared" si="117"/>
-        <v>9728.1025306502561</v>
+        <f t="shared" si="122"/>
+        <v>10026.282713106497</v>
       </c>
       <c r="BT20" s="1">
-        <f t="shared" si="117"/>
-        <v>9630.8215053437543</v>
+        <f t="shared" si="122"/>
+        <v>9926.019885975431</v>
       </c>
       <c r="BU20" s="1">
-        <f t="shared" si="117"/>
-        <v>9534.5132902903169</v>
+        <f t="shared" si="122"/>
+        <v>9826.7596871156766</v>
       </c>
       <c r="BV20" s="1">
-        <f t="shared" si="117"/>
-        <v>9439.1681573874139</v>
+        <f t="shared" si="122"/>
+        <v>9728.4920902445192</v>
       </c>
       <c r="BW20" s="1">
-        <f t="shared" si="117"/>
-        <v>9344.7764758135399</v>
+        <f t="shared" si="122"/>
+        <v>9631.207169342073</v>
       </c>
       <c r="BX20" s="1">
-        <f t="shared" si="117"/>
-        <v>9251.3287110554047</v>
+        <f t="shared" si="122"/>
+        <v>9534.8950976486522</v>
       </c>
       <c r="BY20" s="1">
-        <f t="shared" si="117"/>
-        <v>9158.8154239448504</v>
+        <f t="shared" si="122"/>
+        <v>9439.5461466721663</v>
       </c>
       <c r="BZ20" s="1">
-        <f t="shared" si="117"/>
-        <v>9067.2272697054013</v>
+        <f t="shared" si="122"/>
+        <v>9345.1506852054445</v>
       </c>
       <c r="CA20" s="1">
-        <f t="shared" si="117"/>
-        <v>8976.5549970083466</v>
+        <f t="shared" si="122"/>
+        <v>9251.6991783533904</v>
       </c>
       <c r="CB20" s="1">
-        <f t="shared" si="117"/>
-        <v>8886.7894470382635</v>
+        <f t="shared" si="122"/>
+        <v>9159.1821865698566</v>
       </c>
       <c r="CC20" s="1">
-        <f t="shared" si="117"/>
-        <v>8797.921552567881</v>
+        <f t="shared" si="122"/>
+        <v>9067.5903647041578</v>
       </c>
       <c r="CD20" s="1">
-        <f t="shared" si="117"/>
-        <v>8709.9423370422028</v>
+        <f t="shared" si="122"/>
+        <v>8976.9144610571166</v>
       </c>
       <c r="CE20" s="1">
-        <f t="shared" si="117"/>
-        <v>8622.8429136717805</v>
+        <f t="shared" si="122"/>
+        <v>8887.1453164465456</v>
       </c>
       <c r="CF20" s="1">
-        <f t="shared" si="117"/>
-        <v>8536.6144845350627</v>
+        <f t="shared" si="122"/>
+        <v>8798.2738632820801</v>
       </c>
       <c r="CG20" s="1">
-        <f t="shared" si="117"/>
-        <v>8451.2483396897114</v>
+        <f t="shared" si="122"/>
+        <v>8710.2911246492586</v>
       </c>
       <c r="CH20" s="1">
-        <f t="shared" si="117"/>
-        <v>8366.7358562928148</v>
+        <f t="shared" si="122"/>
+        <v>8623.1882134027655</v>
       </c>
       <c r="CI20" s="1">
-        <f t="shared" si="117"/>
-        <v>8283.0684977298861</v>
+        <f t="shared" si="122"/>
+        <v>8536.9563312687369</v>
       </c>
       <c r="CJ20" s="1">
-        <f t="shared" si="117"/>
-        <v>8200.2378127525863</v>
+        <f t="shared" si="122"/>
+        <v>8451.5867679560488</v>
       </c>
       <c r="CK20" s="1">
-        <f t="shared" si="117"/>
-        <v>8118.2354346250604</v>
+        <f t="shared" si="122"/>
+        <v>8367.0709002764888</v>
       </c>
       <c r="CL20" s="1">
-        <f t="shared" si="117"/>
-        <v>8037.0530802788098</v>
+        <f t="shared" si="122"/>
+        <v>8283.400191273724</v>
       </c>
       <c r="CM20" s="1">
-        <f t="shared" si="117"/>
-        <v>7956.6825494760214</v>
+        <f t="shared" si="122"/>
+        <v>8200.5661893609868</v>
       </c>
       <c r="CN20" s="1">
-        <f t="shared" si="117"/>
-        <v>7877.115723981261</v>
+        <f t="shared" si="122"/>
+        <v>8118.5605274673771</v>
       </c>
       <c r="CO20" s="1">
-        <f t="shared" si="117"/>
-        <v>7798.344566741448</v>
+        <f t="shared" si="122"/>
+        <v>8037.3749221927037</v>
       </c>
       <c r="CP20" s="1">
-        <f t="shared" si="117"/>
-        <v>7720.3611210740337</v>
+        <f t="shared" si="122"/>
+        <v>7957.0011729707767</v>
       </c>
       <c r="CQ20" s="1">
-        <f t="shared" si="117"/>
-        <v>7643.1575098632929</v>
+        <f t="shared" si="122"/>
+        <v>7877.4311612410693</v>
       </c>
       <c r="CR20" s="1">
-        <f t="shared" si="117"/>
-        <v>7566.7259347646595</v>
+        <f t="shared" si="122"/>
+        <v>7798.6568496286582</v>
       </c>
       <c r="CS20" s="1">
-        <f t="shared" si="117"/>
-        <v>7491.0586754170126</v>
+        <f t="shared" si="122"/>
+        <v>7720.6702811323712</v>
       </c>
       <c r="CT20" s="1">
-        <f t="shared" si="117"/>
-        <v>7416.1480886628424</v>
+        <f t="shared" si="122"/>
+        <v>7643.4635783210479</v>
       </c>
       <c r="CU20" s="1">
-        <f t="shared" si="117"/>
-        <v>7341.9866077762135</v>
+        <f t="shared" si="122"/>
+        <v>7567.0289425378369</v>
       </c>
       <c r="CV20" s="1">
-        <f t="shared" si="117"/>
-        <v>7268.5667416984516</v>
+        <f t="shared" si="122"/>
+        <v>7491.3586531124583</v>
       </c>
       <c r="CW20" s="1">
-        <f t="shared" si="117"/>
-        <v>7195.8810742814667</v>
+        <f t="shared" si="122"/>
+        <v>7416.4450665813338</v>
       </c>
       <c r="CX20" s="1">
-        <f t="shared" si="117"/>
-        <v>7123.9222635386523</v>
+        <f t="shared" si="122"/>
+        <v>7342.2806159155207</v>
       </c>
       <c r="CY20" s="1">
-        <f t="shared" si="117"/>
-        <v>7052.6830409032655</v>
+        <f t="shared" si="122"/>
+        <v>7268.857809756365</v>
       </c>
       <c r="CZ20" s="1">
-        <f t="shared" si="117"/>
-        <v>6982.1562104942332</v>
+        <f t="shared" si="122"/>
+        <v>7196.1692316588014</v>
       </c>
       <c r="DA20" s="1">
-        <f t="shared" si="117"/>
-        <v>6912.334648389291</v>
+        <f t="shared" si="122"/>
+        <v>7124.2075393422137</v>
       </c>
       <c r="DB20" s="1">
-        <f t="shared" si="117"/>
-        <v>6843.2113019053977</v>
+        <f t="shared" si="122"/>
+        <v>7052.9654639487917</v>
       </c>
       <c r="DC20" s="1">
-        <f t="shared" si="117"/>
-        <v>6774.7791888863439</v>
+        <f t="shared" si="122"/>
+        <v>6982.4358093093033</v>
       </c>
       <c r="DD20" s="1">
-        <f t="shared" si="117"/>
-        <v>6707.0313969974804</v>
+        <f t="shared" si="122"/>
+        <v>6912.6114512162103</v>
       </c>
       <c r="DE20" s="1">
-        <f t="shared" si="117"/>
-        <v>6639.961083027506</v>
+        <f t="shared" si="122"/>
+        <v>6843.4853367040478</v>
       </c>
       <c r="DF20" s="1">
-        <f t="shared" si="117"/>
-        <v>6573.5614721972306</v>
+        <f t="shared" si="122"/>
+        <v>6775.0504833370069</v>
       </c>
       <c r="DG20" s="1">
-        <f t="shared" si="117"/>
-        <v>6507.8258574752581</v>
+        <f t="shared" si="122"/>
+        <v>6707.2999785036363</v>
       </c>
       <c r="DH20" s="1">
-        <f t="shared" si="117"/>
-        <v>6442.7475989005052</v>
+        <f t="shared" si="122"/>
+        <v>6640.2269787185996</v>
       </c>
       <c r="DI20" s="1">
-        <f t="shared" si="117"/>
-        <v>6378.3201229115002</v>
+        <f t="shared" si="122"/>
+        <v>6573.8247089314136</v>
       </c>
       <c r="DJ20" s="1">
-        <f t="shared" si="117"/>
-        <v>6314.5369216823856</v>
+        <f t="shared" si="122"/>
+        <v>6508.0864618420992</v>
       </c>
       <c r="DK20" s="1">
-        <f t="shared" si="117"/>
-        <v>6251.3915524655613</v>
+        <f t="shared" si="122"/>
+        <v>6443.0055972236778</v>
       </c>
       <c r="DL20" s="1">
-        <f t="shared" si="117"/>
-        <v>6188.8776369409052</v>
+        <f t="shared" si="122"/>
+        <v>6378.5755412514409</v>
       </c>
       <c r="DM20" s="1">
-        <f t="shared" si="117"/>
-        <v>6126.9888605714959</v>
+        <f t="shared" si="122"/>
+        <v>6314.789785838926</v>
       </c>
       <c r="DN20" s="1">
-        <f t="shared" si="117"/>
-        <v>6065.7189719657808</v>
+        <f t="shared" si="122"/>
+        <v>6251.6418879805369</v>
       </c>
       <c r="DO20" s="1">
-        <f t="shared" si="117"/>
-        <v>6005.0617822461227</v>
+        <f t="shared" si="122"/>
+        <v>6189.1254691007316</v>
       </c>
       <c r="DP20" s="1">
-        <f t="shared" si="117"/>
-        <v>5945.0111644236613</v>
+        <f t="shared" si="122"/>
+        <v>6127.2342144097238</v>
       </c>
       <c r="DQ20" s="1">
-        <f t="shared" si="117"/>
-        <v>5885.5610527794242</v>
+        <f t="shared" si="122"/>
+        <v>6065.9618722656269</v>
       </c>
       <c r="DR20" s="1">
-        <f t="shared" si="117"/>
-        <v>5826.7054422516303</v>
+        <f t="shared" si="122"/>
+        <v>6005.3022535429709</v>
       </c>
       <c r="DS20" s="1">
-        <f t="shared" si="117"/>
-        <v>5768.4383878291137</v>
+        <f t="shared" si="122"/>
+        <v>5945.2492310075413</v>
       </c>
       <c r="DT20" s="1">
-        <f t="shared" si="117"/>
-        <v>5710.7540039508222</v>
+        <f t="shared" si="122"/>
+        <v>5885.796738697466</v>
       </c>
       <c r="DU20" s="1">
-        <f t="shared" si="117"/>
-        <v>5653.6464639113137</v>
+        <f t="shared" si="122"/>
+        <v>5826.9387713104916</v>
       </c>
       <c r="DV20" s="1">
-        <f t="shared" si="117"/>
-        <v>5597.1099992722002</v>
+        <f t="shared" si="122"/>
+        <v>5768.6693835973865</v>
       </c>
       <c r="DW20" s="1">
-        <f t="shared" si="117"/>
-        <v>5541.1388992794782</v>
+        <f t="shared" si="122"/>
+        <v>5710.982689761413</v>
       </c>
       <c r="DX20" s="1">
-        <f t="shared" ref="DX20:GI20" si="118">DW20*(1+$BM$30)</f>
-        <v>5485.7275102866834</v>
+        <f t="shared" ref="DX20:GI20" si="123">DW20*(1+$BM$30)</f>
+        <v>5653.8728628637991</v>
       </c>
       <c r="DY20" s="1">
-        <f t="shared" si="118"/>
-        <v>5430.8702351838165</v>
+        <f t="shared" si="123"/>
+        <v>5597.3341342351614</v>
       </c>
       <c r="DZ20" s="1">
-        <f t="shared" si="118"/>
-        <v>5376.5615328319782</v>
+        <f t="shared" si="123"/>
+        <v>5541.3607928928095</v>
       </c>
       <c r="EA20" s="1">
-        <f t="shared" si="118"/>
-        <v>5322.7959175036585</v>
+        <f t="shared" si="123"/>
+        <v>5485.9471849638812</v>
       </c>
       <c r="EB20" s="1">
-        <f t="shared" si="118"/>
-        <v>5269.5679583286219</v>
+        <f t="shared" si="123"/>
+        <v>5431.0877131142424</v>
       </c>
       <c r="EC20" s="1">
-        <f t="shared" si="118"/>
-        <v>5216.8722787453353</v>
+        <f t="shared" si="123"/>
+        <v>5376.7768359830998</v>
       </c>
       <c r="ED20" s="1">
-        <f t="shared" si="118"/>
-        <v>5164.7035559578817</v>
+        <f t="shared" si="123"/>
+        <v>5323.0090676232685</v>
       </c>
       <c r="EE20" s="1">
-        <f t="shared" si="118"/>
-        <v>5113.0565203983024</v>
+        <f t="shared" si="123"/>
+        <v>5269.7789769470355</v>
       </c>
       <c r="EF20" s="1">
-        <f t="shared" si="118"/>
-        <v>5061.9259551943196</v>
+        <f t="shared" si="123"/>
+        <v>5217.081187177565</v>
       </c>
       <c r="EG20" s="1">
-        <f t="shared" si="118"/>
-        <v>5011.3066956423763</v>
+        <f t="shared" si="123"/>
+        <v>5164.9103753057889</v>
       </c>
       <c r="EH20" s="1">
-        <f t="shared" si="118"/>
-        <v>4961.1936286859527</v>
+        <f t="shared" si="123"/>
+        <v>5113.2612715527312</v>
       </c>
       <c r="EI20" s="1">
-        <f t="shared" si="118"/>
-        <v>4911.5816923990933</v>
+        <f t="shared" si="123"/>
+        <v>5062.1286588372041</v>
       </c>
       <c r="EJ20" s="1">
-        <f t="shared" si="118"/>
-        <v>4862.4658754751026</v>
+        <f t="shared" si="123"/>
+        <v>5011.5073722488323</v>
       </c>
       <c r="EK20" s="1">
-        <f t="shared" si="118"/>
-        <v>4813.8412167203514</v>
+        <f t="shared" si="123"/>
+        <v>4961.3922985263443</v>
       </c>
       <c r="EL20" s="1">
-        <f t="shared" si="118"/>
-        <v>4765.7028045531479</v>
+        <f t="shared" si="123"/>
+        <v>4911.778375541081</v>
       </c>
       <c r="EM20" s="1">
-        <f t="shared" si="118"/>
-        <v>4718.0457765076162</v>
+        <f t="shared" si="123"/>
+        <v>4862.6605917856705</v>
       </c>
       <c r="EN20" s="1">
-        <f t="shared" si="118"/>
-        <v>4670.8653187425398</v>
+        <f t="shared" si="123"/>
+        <v>4814.0339858678135</v>
       </c>
       <c r="EO20" s="1">
-        <f t="shared" si="118"/>
-        <v>4624.1566655551142</v>
+        <f t="shared" si="123"/>
+        <v>4765.8936460091354</v>
       </c>
       <c r="EP20" s="1">
-        <f t="shared" si="118"/>
-        <v>4577.9150988995634</v>
+        <f t="shared" si="123"/>
+        <v>4718.2347095490441</v>
       </c>
       <c r="EQ20" s="1">
-        <f t="shared" si="118"/>
-        <v>4532.1359479105677</v>
+        <f t="shared" si="123"/>
+        <v>4671.0523624535535</v>
       </c>
       <c r="ER20" s="1">
-        <f t="shared" si="118"/>
-        <v>4486.8145884314617</v>
+        <f t="shared" si="123"/>
+        <v>4624.3418388290183</v>
       </c>
       <c r="ES20" s="1">
-        <f t="shared" si="118"/>
-        <v>4441.9464425471469</v>
+        <f t="shared" si="123"/>
+        <v>4578.0984204407278</v>
       </c>
       <c r="ET20" s="1">
-        <f t="shared" si="118"/>
-        <v>4397.5269781216757</v>
+        <f t="shared" si="123"/>
+        <v>4532.3174362363206</v>
       </c>
       <c r="EU20" s="1">
-        <f t="shared" si="118"/>
-        <v>4353.5517083404593</v>
+        <f t="shared" si="123"/>
+        <v>4486.9942618739578</v>
       </c>
       <c r="EV20" s="1">
-        <f t="shared" si="118"/>
-        <v>4310.0161912570547</v>
+        <f t="shared" si="123"/>
+        <v>4442.1243192552183</v>
       </c>
       <c r="EW20" s="1">
-        <f t="shared" si="118"/>
-        <v>4266.9160293444838</v>
+        <f t="shared" si="123"/>
+        <v>4397.7030760626658</v>
       </c>
       <c r="EX20" s="1">
-        <f t="shared" si="118"/>
-        <v>4224.2468690510386</v>
+        <f t="shared" si="123"/>
+        <v>4353.726045302039</v>
       </c>
       <c r="EY20" s="1">
-        <f t="shared" si="118"/>
-        <v>4182.0044003605281</v>
+        <f t="shared" si="123"/>
+        <v>4310.1887848490187</v>
       </c>
       <c r="EZ20" s="1">
-        <f t="shared" si="118"/>
-        <v>4140.1843563569228</v>
+        <f t="shared" si="123"/>
+        <v>4267.0868970005286</v>
       </c>
       <c r="FA20" s="1">
-        <f t="shared" si="118"/>
-        <v>4098.7825127933538</v>
+        <f t="shared" si="123"/>
+        <v>4224.4160280305232</v>
       </c>
       <c r="FB20" s="1">
-        <f t="shared" si="118"/>
-        <v>4057.79468766542</v>
+        <f t="shared" si="123"/>
+        <v>4182.1718677502176</v>
       </c>
       <c r="FC20" s="1">
-        <f t="shared" si="118"/>
-        <v>4017.2167407887659</v>
+        <f t="shared" si="123"/>
+        <v>4140.3501490727158</v>
       </c>
       <c r="FD20" s="1">
-        <f t="shared" si="118"/>
-        <v>3977.0445733808783</v>
+        <f t="shared" si="123"/>
+        <v>4098.9466475819881</v>
       </c>
       <c r="FE20" s="1">
-        <f t="shared" si="118"/>
-        <v>3937.2741276470697</v>
+        <f t="shared" si="123"/>
+        <v>4057.9571811061683</v>
       </c>
       <c r="FF20" s="1">
-        <f t="shared" si="118"/>
-        <v>3897.9013863705991</v>
+        <f t="shared" si="123"/>
+        <v>4017.3776092951066</v>
       </c>
       <c r="FG20" s="1">
-        <f t="shared" si="118"/>
-        <v>3858.9223725068932</v>
+        <f t="shared" si="123"/>
+        <v>3977.2038332021557</v>
       </c>
       <c r="FH20" s="1">
-        <f t="shared" si="118"/>
-        <v>3820.3331487818241</v>
+        <f t="shared" si="123"/>
+        <v>3937.4317948701341</v>
       </c>
       <c r="FI20" s="1">
-        <f t="shared" si="118"/>
-        <v>3782.129817294006</v>
+        <f t="shared" si="123"/>
+        <v>3898.0574769214327</v>
       </c>
       <c r="FJ20" s="1">
-        <f t="shared" si="118"/>
-        <v>3744.3085191210657</v>
+        <f t="shared" si="123"/>
+        <v>3859.0769021522183</v>
       </c>
       <c r="FK20" s="1">
-        <f t="shared" si="118"/>
-        <v>3706.865433929855</v>
+        <f t="shared" si="123"/>
+        <v>3820.4861331306961</v>
       </c>
       <c r="FL20" s="1">
-        <f t="shared" si="118"/>
-        <v>3669.7967795905565</v>
+        <f t="shared" si="123"/>
+        <v>3782.2812717993893</v>
       </c>
       <c r="FM20" s="1">
-        <f t="shared" si="118"/>
-        <v>3633.0988117946508</v>
+        <f t="shared" si="123"/>
+        <v>3744.4584590813952</v>
       </c>
       <c r="FN20" s="1">
-        <f t="shared" si="118"/>
-        <v>3596.7678236767042</v>
+        <f t="shared" si="123"/>
+        <v>3707.0138744905812</v>
       </c>
       <c r="FO20" s="1">
-        <f t="shared" si="118"/>
-        <v>3560.8001454399373</v>
+        <f t="shared" si="123"/>
+        <v>3669.9437357456754</v>
       </c>
       <c r="FP20" s="1">
-        <f t="shared" si="118"/>
-        <v>3525.1921439855378</v>
+        <f t="shared" si="123"/>
+        <v>3633.2442983882188</v>
       </c>
       <c r="FQ20" s="1">
-        <f t="shared" si="118"/>
-        <v>3489.9402225456824</v>
+        <f t="shared" si="123"/>
+        <v>3596.9118554043366</v>
       </c>
       <c r="FR20" s="1">
-        <f t="shared" si="118"/>
-        <v>3455.0408203202255</v>
+        <f t="shared" si="123"/>
+        <v>3560.9427368502934</v>
       </c>
       <c r="FS20" s="1">
-        <f t="shared" si="118"/>
-        <v>3420.4904121170234</v>
+        <f t="shared" si="123"/>
+        <v>3525.3333094817904</v>
       </c>
       <c r="FT20" s="1">
-        <f t="shared" si="118"/>
-        <v>3386.2855079958531</v>
+        <f t="shared" si="123"/>
+        <v>3490.0799763869722</v>
       </c>
       <c r="FU20" s="1">
-        <f t="shared" si="118"/>
-        <v>3352.4226529158946</v>
+        <f t="shared" si="123"/>
+        <v>3455.1791766231026</v>
       </c>
       <c r="FV20" s="1">
-        <f t="shared" si="118"/>
-        <v>3318.8984263867355</v>
+        <f t="shared" si="123"/>
+        <v>3420.6273848568717</v>
       </c>
       <c r="FW20" s="1">
-        <f t="shared" si="118"/>
-        <v>3285.709442122868</v>
+        <f t="shared" si="123"/>
+        <v>3386.4211110083029</v>
       </c>
       <c r="FX20" s="1">
-        <f t="shared" si="118"/>
-        <v>3252.8523477016392</v>
+        <f t="shared" si="123"/>
+        <v>3352.5568998982199</v>
       </c>
       <c r="FY20" s="1">
-        <f t="shared" si="118"/>
-        <v>3220.323824224623</v>
+        <f t="shared" si="123"/>
+        <v>3319.0313308992377</v>
       </c>
       <c r="FZ20" s="1">
-        <f t="shared" si="118"/>
-        <v>3188.1205859823767</v>
+        <f t="shared" si="123"/>
+        <v>3285.8410175902454</v>
       </c>
       <c r="GA20" s="1">
-        <f t="shared" si="118"/>
-        <v>3156.239380122553</v>
+        <f t="shared" si="123"/>
+        <v>3252.982607414343</v>
       </c>
       <c r="GB20" s="1">
-        <f t="shared" si="118"/>
-        <v>3124.6769863213276</v>
+        <f t="shared" si="123"/>
+        <v>3220.4527813401996</v>
       </c>
       <c r="GC20" s="1">
-        <f t="shared" si="118"/>
-        <v>3093.4302164581145</v>
+        <f t="shared" si="123"/>
+        <v>3188.2482535267977</v>
       </c>
       <c r="GD20" s="1">
-        <f t="shared" si="118"/>
-        <v>3062.4959142935331</v>
+        <f t="shared" si="123"/>
+        <v>3156.3657709915296</v>
       </c>
       <c r="GE20" s="1">
-        <f t="shared" si="118"/>
-        <v>3031.8709551505976</v>
+        <f t="shared" si="123"/>
+        <v>3124.8021132816143</v>
       </c>
       <c r="GF20" s="1">
-        <f t="shared" si="118"/>
-        <v>3001.5522455990917</v>
+        <f t="shared" si="123"/>
+        <v>3093.5540921487982</v>
       </c>
       <c r="GG20" s="1">
-        <f t="shared" si="118"/>
-        <v>2971.536723143101</v>
+        <f t="shared" si="123"/>
+        <v>3062.61855122731</v>
       </c>
       <c r="GH20" s="1">
-        <f t="shared" si="118"/>
-        <v>2941.8213559116698</v>
+        <f t="shared" si="123"/>
+        <v>3031.9923657150371</v>
       </c>
       <c r="GI20" s="1">
-        <f t="shared" si="118"/>
-        <v>2912.403142352553</v>
+        <f t="shared" si="123"/>
+        <v>3001.6724420578867</v>
       </c>
       <c r="GJ20" s="1">
-        <f t="shared" ref="GJ20:GN20" si="119">GI20*(1+$BM$30)</f>
-        <v>2883.2791109290274</v>
+        <f t="shared" ref="GJ20:GN20" si="124">GI20*(1+$BM$30)</f>
+        <v>2971.6557176373076</v>
       </c>
       <c r="GK20" s="1">
-        <f t="shared" si="119"/>
-        <v>2854.4463198197373</v>
+        <f t="shared" si="124"/>
+        <v>2941.9391604609345</v>
       </c>
       <c r="GL20" s="1">
-        <f t="shared" si="119"/>
-        <v>2825.90185662154</v>
+        <f t="shared" si="124"/>
+        <v>2912.5197688563253</v>
       </c>
       <c r="GM20" s="1">
-        <f t="shared" si="119"/>
-        <v>2797.6428380553248</v>
+        <f t="shared" si="124"/>
+        <v>2883.394571167762</v>
       </c>
       <c r="GN20" s="1">
-        <f t="shared" si="119"/>
-        <v>2769.6664096747713</v>
+        <f t="shared" si="124"/>
+        <v>2854.5606254560844</v>
       </c>
     </row>
     <row r="21" spans="2:196" x14ac:dyDescent="0.3">
@@ -5394,16 +5374,17 @@
         <v>961</v>
       </c>
       <c r="AI21" s="5">
-        <v>961</v>
+        <f>960</f>
+        <v>960</v>
       </c>
       <c r="AJ21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="AK21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="AL21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
@@ -5434,37 +5415,37 @@
         <v>961</v>
       </c>
       <c r="AZ21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BA21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BB21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BC21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BD21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BE21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BF21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BG21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BH21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BI21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="BJ21" s="5">
-        <v>961</v>
+        <v>952</v>
       </c>
     </row>
     <row r="22" spans="2:196" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5472,148 +5453,148 @@
         <v>35</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:P22" si="120">C20/C21</f>
+        <f t="shared" ref="C22:P22" si="125">C20/C21</f>
         <v>1.0989010989010989E-3</v>
       </c>
       <c r="D22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>5.054945054945055E-2</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.11758241758241758</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.22637362637362637</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.37802197802197801</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.32857142857142857</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.39780219780219778</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.43076923076923079</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.1</v>
       </c>
       <c r="M22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>-0.11978021978021978</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>-0.2725274725274725</v>
       </c>
       <c r="O22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>0.10879120879120879</v>
       </c>
       <c r="P22" s="7">
-        <f t="shared" si="120"/>
+        <f t="shared" si="125"/>
         <v>2.8846153846153846</v>
       </c>
       <c r="Q22" s="7">
-        <f t="shared" ref="Q22:S22" si="121">Q20/Q21</f>
+        <f t="shared" ref="Q22:S22" si="126">Q20/Q21</f>
         <v>1.2296926454445665</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>0.29308452250274425</v>
       </c>
       <c r="S22" s="7">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>0.50922909880564604</v>
       </c>
       <c r="T22" s="7">
-        <f t="shared" ref="T22" si="122">T20/T21</f>
+        <f t="shared" ref="T22" si="127">T20/T21</f>
         <v>0.57341907824222937</v>
       </c>
       <c r="U22" s="7">
-        <f t="shared" ref="U22" si="123">U20/U21</f>
+        <f t="shared" ref="U22" si="128">U20/U21</f>
         <v>0.47755102040816327</v>
       </c>
       <c r="V22" s="7">
-        <f t="shared" ref="V22:W22" si="124">V20/V21</f>
+        <f t="shared" ref="V22:W22" si="129">V20/V21</f>
         <v>-2.8397565922920892E-2</v>
       </c>
       <c r="W22" s="7">
-        <f t="shared" si="124"/>
+        <f t="shared" si="129"/>
         <v>3.0010718113612004E-2</v>
       </c>
       <c r="X22" s="7">
-        <f t="shared" ref="X22" si="125">X20/X21</f>
+        <f t="shared" ref="X22" si="130">X20/X21</f>
         <v>6.820461384152457E-2</v>
       </c>
       <c r="Y22" s="7">
-        <f t="shared" ref="Y22" si="126">Y20/Y21</f>
+        <f t="shared" ref="Y22" si="131">Y20/Y21</f>
         <v>0.21063189568706117</v>
       </c>
       <c r="Z22" s="7">
-        <f t="shared" ref="Z22:AA22" si="127">Z20/Z21</f>
+        <f t="shared" ref="Z22:AA22" si="132">Z20/Z21</f>
         <v>-9.959349593495935E-2</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" si="127"/>
+        <f t="shared" si="132"/>
         <v>0.20306122448979591</v>
       </c>
       <c r="AB22" s="7">
-        <f t="shared" ref="AB22" si="128">AB20/AB21</f>
+        <f t="shared" ref="AB22" si="133">AB20/AB21</f>
         <v>1.2994871794871794</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" ref="AC22" si="129">AC20/AC21</f>
+        <f t="shared" ref="AC22" si="134">AC20/AC21</f>
         <v>1.2592592592592593</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" ref="AD22:AE22" si="130">AD20/AD21</f>
+        <f t="shared" ref="AD22:AE22" si="135">AD20/AD21</f>
         <v>1.4907216494845361</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" si="130"/>
+        <f t="shared" si="135"/>
         <v>1.5804123711340206</v>
       </c>
       <c r="AF22" s="7">
-        <f t="shared" ref="AF22" si="131">AF20/AF21</f>
+        <f t="shared" ref="AF22" si="136">AF20/AF21</f>
         <v>1.4823651452282158</v>
       </c>
       <c r="AG22" s="7">
-        <f t="shared" ref="AG22" si="132">AG20/AG21</f>
+        <f t="shared" ref="AG22" si="137">AG20/AG21</f>
         <v>1.5972803347280335</v>
       </c>
       <c r="AH22" s="7">
-        <f t="shared" ref="AH22:AL22" si="133">AH20/AH21</f>
+        <f t="shared" ref="AH22:AL22" si="138">AH20/AH21</f>
         <v>1.777315296566077</v>
       </c>
       <c r="AI22" s="7">
-        <f t="shared" si="133"/>
-        <v>1.7451637627471379</v>
+        <f t="shared" si="138"/>
+        <v>1.6052083333333333</v>
       </c>
       <c r="AJ22" s="7">
-        <f t="shared" si="133"/>
-        <v>1.6781810260145691</v>
+        <f t="shared" si="138"/>
+        <v>1.9821428571428572</v>
       </c>
       <c r="AK22" s="7">
-        <f t="shared" si="133"/>
-        <v>1.7120286805411022</v>
+        <f t="shared" si="138"/>
+        <v>1.9676365126050417</v>
       </c>
       <c r="AL22" s="7">
-        <f t="shared" si="133"/>
-        <v>1.7031031383975035</v>
+        <f t="shared" si="138"/>
+        <v>1.8851158298319339</v>
       </c>
       <c r="AM22" s="7"/>
       <c r="AN22" s="7"/>
@@ -5636,64 +5617,64 @@
         <v>4.4698133918770582</v>
       </c>
       <c r="AV22" s="7">
-        <f t="shared" ref="AV22:BE22" si="134">AV20/AV21</f>
+        <f t="shared" ref="AV22:BE22" si="139">AV20/AV21</f>
         <v>1.8732251521298176</v>
       </c>
       <c r="AW22" s="7">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>0.21138211382113822</v>
       </c>
       <c r="AX22" s="7">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>4.2639175257731958</v>
       </c>
       <c r="AY22" s="7">
-        <f t="shared" si="134"/>
+        <f t="shared" si="139"/>
         <v>6.4484911550468258</v>
       </c>
       <c r="AZ22" s="7">
-        <f t="shared" si="134"/>
-        <v>6.880599396462018</v>
+        <f t="shared" si="139"/>
+        <v>6.5146851155462251</v>
       </c>
       <c r="BA22" s="7">
-        <f t="shared" si="134"/>
-        <v>7.8990630291363173</v>
+        <f t="shared" si="139"/>
+        <v>8.2895363771008483</v>
       </c>
       <c r="BB22" s="7">
-        <f t="shared" si="134"/>
-        <v>8.7233896136524489</v>
+        <f t="shared" si="139"/>
+        <v>9.1140383131932854</v>
       </c>
       <c r="BC22" s="7">
-        <f t="shared" si="134"/>
-        <v>9.0457218902784664</v>
+        <f t="shared" si="139"/>
+        <v>9.4389247294025242</v>
       </c>
       <c r="BD22" s="7">
-        <f t="shared" si="134"/>
-        <v>9.4142811222562148</v>
+        <f t="shared" si="139"/>
+        <v>9.8136275058026232</v>
       </c>
       <c r="BE22" s="7">
-        <f t="shared" si="134"/>
-        <v>9.78454633013863</v>
+        <f t="shared" si="139"/>
+        <v>10.192082039145861</v>
       </c>
       <c r="BF22" s="7">
-        <f t="shared" ref="BF22:BJ22" si="135">BF20/BF21</f>
-        <v>10.035267908858939</v>
+        <f t="shared" ref="BF22:BJ22" si="140">BF20/BF21</f>
+        <v>10.450021775877127</v>
       </c>
       <c r="BG22" s="7">
-        <f t="shared" si="135"/>
-        <v>10.289124977548775</v>
+        <f t="shared" si="140"/>
+        <v>10.711673028604615</v>
       </c>
       <c r="BH22" s="7">
-        <f t="shared" si="135"/>
-        <v>10.547595524174573</v>
+        <f t="shared" si="140"/>
+        <v>10.978285840707864</v>
       </c>
       <c r="BI22" s="7">
-        <f t="shared" si="135"/>
-        <v>10.811477632146616</v>
+        <f t="shared" si="140"/>
+        <v>11.250545624972458</v>
       </c>
       <c r="BJ22" s="7">
-        <f t="shared" si="135"/>
-        <v>11.081230793632511</v>
+        <f t="shared" si="140"/>
+        <v>11.528856846000011</v>
       </c>
     </row>
     <row r="24" spans="2:196" x14ac:dyDescent="0.3">
@@ -5701,124 +5682,124 @@
         <v>83</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" ref="W24:W25" si="136">W3/S3-1</f>
+        <f t="shared" ref="W24:W25" si="141">W3/S3-1</f>
         <v>0.2384393063583814</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" ref="X24:X25" si="137">X3/T3-1</f>
+        <f t="shared" ref="X24:X25" si="142">X3/T3-1</f>
         <v>0.2078119715928306</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" ref="Y24:Y25" si="138">Y3/U3-1</f>
+        <f t="shared" ref="Y24:Y25" si="143">Y3/U3-1</f>
         <v>0.13387678319485818</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" ref="Z24:Z25" si="139">Z3/V3-1</f>
+        <f t="shared" ref="Z24:Z25" si="144">Z3/V3-1</f>
         <v>0.1407439953134153</v>
       </c>
       <c r="AA24" s="8">
-        <f t="shared" ref="AA24:AA25" si="140">AA3/W3-1</f>
+        <f t="shared" ref="AA24:AA25" si="145">AA3/W3-1</f>
         <v>0.11464410735122521</v>
       </c>
       <c r="AB24" s="8">
-        <f t="shared" ref="AB24:AB25" si="141">AB3/X3-1</f>
+        <f t="shared" ref="AB24:AB25" si="146">AB3/X3-1</f>
         <v>0.12081758364832695</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" ref="AC24:AC25" si="142">AC3/Y3-1</f>
+        <f t="shared" ref="AC24:AC25" si="147">AC3/Y3-1</f>
         <v>0.12553573897414627</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" ref="AD24:AD25" si="143">AD3/Z3-1</f>
+        <f t="shared" ref="AD24:AD25" si="148">AD3/Z3-1</f>
         <v>0.12312235203492095</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" ref="AE24:AE25" si="144">AE3/AA3-1</f>
+        <f t="shared" ref="AE24:AE25" si="149">AE3/AA3-1</f>
         <v>0.12339701648783041</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" ref="AF24:AF25" si="145">AF3/AB3-1</f>
+        <f t="shared" ref="AF24:AF25" si="150">AF3/AB3-1</f>
         <v>9.4678990756932313E-2</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" ref="AG24:AG25" si="146">AG3/AC3-1</f>
+        <f t="shared" ref="AG24:AG25" si="151">AG3/AC3-1</f>
         <v>9.0652254022847378E-2</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" ref="AH24:AH25" si="147">AH3/AD3-1</f>
+        <f t="shared" ref="AH24:AH25" si="152">AH3/AD3-1</f>
         <v>8.0361225422953764E-2</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" ref="AI24:AI25" si="148">AI3/AE3-1</f>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" ref="AI24:AI25" si="153">AI3/AE3-1</f>
+        <v>8.2935352358765257E-2</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" ref="AJ24:AJ26" si="149">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ24:AJ26" si="154">AJ3/AF3-1</f>
+        <v>0.10565951620264724</v>
+      </c>
+      <c r="AK24" s="8">
+        <f t="shared" ref="AK24:AK26" si="155">AK3/AG3-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AL24" s="8">
+        <f t="shared" ref="AL24:AL26" si="156">AL3/AH3-1</f>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AK24" s="8">
-        <f t="shared" ref="AK24:AK26" si="150">AK3/AG3-1</f>
+      <c r="AW24" s="8">
+        <f t="shared" ref="AW24:AW25" si="157">AW3/AV3-1</f>
+        <v>0.17698827919049354</v>
+      </c>
+      <c r="AX24" s="8">
+        <f t="shared" ref="AX24:AX25" si="158">AX3/AW3-1</f>
+        <v>0.12115364735880907</v>
+      </c>
+      <c r="AY24" s="8">
+        <f t="shared" ref="AY24:AY25" si="159">AY3/AX3-1</f>
+        <v>9.6566985278298656E-2</v>
+      </c>
+      <c r="AZ24" s="8">
+        <f t="shared" ref="AT24:BE26" si="160">AZ3/AY3-1</f>
+        <v>8.9337425376271762E-2</v>
+      </c>
+      <c r="BA24" s="8">
+        <f t="shared" ref="BA24:BA25" si="161">BA3/AZ3-1</f>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AL24" s="8">
-        <f t="shared" ref="AL24:AL26" si="151">AL3/AH3-1</f>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AW24" s="8">
-        <f t="shared" ref="AW24:AW25" si="152">AW3/AV3-1</f>
-        <v>0.17698827919049354</v>
-      </c>
-      <c r="AX24" s="8">
-        <f t="shared" ref="AX24:AX25" si="153">AX3/AW3-1</f>
-        <v>0.12115364735880907</v>
-      </c>
-      <c r="AY24" s="8">
-        <f t="shared" ref="AY24:AY25" si="154">AY3/AX3-1</f>
-        <v>9.6566985278298656E-2</v>
-      </c>
-      <c r="AZ24" s="8">
-        <f t="shared" ref="AT24:BE26" si="155">AZ3/AY3-1</f>
-        <v>6.1970907256369445E-2</v>
-      </c>
-      <c r="BA24" s="8">
-        <f t="shared" ref="BA24:BA25" si="156">BA3/AZ3-1</f>
-        <v>4.0000000000000036E-2</v>
-      </c>
       <c r="BB24" s="8">
-        <f t="shared" ref="BB24:BB25" si="157">BB3/BA3-1</f>
+        <f t="shared" ref="BB24:BB25" si="162">BB3/BA3-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="BC24" s="8">
+        <f t="shared" ref="BC24:BC25" si="163">BC3/BB3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BC24" s="8">
-        <f t="shared" ref="BC24:BC25" si="158">BC3/BB3-1</f>
+      <c r="BD24" s="8">
+        <f t="shared" ref="BD24:BD25" si="164">BD3/BC3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD24" s="8">
-        <f t="shared" ref="BD24:BD25" si="159">BD3/BC3-1</f>
+      <c r="BE24" s="8">
+        <f t="shared" ref="BE24:BE25" si="165">BE3/BD3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE24" s="8">
-        <f t="shared" ref="BE24:BE25" si="160">BE3/BD3-1</f>
+      <c r="BF24" s="8">
+        <f t="shared" ref="BF24:BF25" si="166">BF3/BE3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF24" s="8">
-        <f t="shared" ref="BF24:BF25" si="161">BF3/BE3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BG24" s="8">
-        <f t="shared" ref="BG24:BG25" si="162">BG3/BF3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BG24:BG25" si="167">BG3/BF3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH24" s="8">
-        <f t="shared" ref="BH24:BH25" si="163">BH3/BG3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BH24:BH25" si="168">BH3/BG3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BI24" s="8">
-        <f t="shared" ref="BI24:BI25" si="164">BI3/BH3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BI24:BI25" si="169">BI3/BH3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ24" s="8">
-        <f t="shared" ref="BJ24:BJ25" si="165">BJ3/BI3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BJ24:BJ25" si="170">BJ3/BI3-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="25" spans="2:196" x14ac:dyDescent="0.3">
@@ -5826,123 +5807,123 @@
         <v>82</v>
       </c>
       <c r="W25" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="141"/>
         <v>0.29976580796252938</v>
       </c>
       <c r="X25" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="142"/>
         <v>0.35446009389671351</v>
       </c>
       <c r="Y25" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="143"/>
         <v>0.24793388429752072</v>
       </c>
       <c r="Z25" s="8">
-        <f t="shared" si="139"/>
+        <f t="shared" si="144"/>
         <v>0.19477911646586343</v>
       </c>
       <c r="AA25" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="145"/>
         <v>9.0090090090090058E-2</v>
       </c>
       <c r="AB25" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="146"/>
         <v>3.4662045060658508E-2</v>
       </c>
       <c r="AC25" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="147"/>
         <v>-4.1390728476821237E-2</v>
       </c>
       <c r="AD25" s="8">
-        <f t="shared" si="143"/>
+        <f t="shared" si="148"/>
         <v>-9.4117647058823528E-2</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" si="144"/>
+        <f t="shared" si="149"/>
         <v>-9.4214876033057893E-2</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="145"/>
+        <f t="shared" si="150"/>
         <v>-6.0301507537688481E-2</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="151"/>
         <v>-2.4179620034542326E-2</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="152"/>
         <v>5.5658627087198376E-3</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="153"/>
+        <v>-2.9197080291970767E-2</v>
+      </c>
+      <c r="AJ25" s="8">
+        <f t="shared" si="154"/>
+        <v>-2.6737967914438499E-2</v>
+      </c>
+      <c r="AK25" s="8">
+        <f t="shared" si="155"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ25" s="8">
-        <f t="shared" si="149"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AK25" s="8">
-        <f t="shared" si="150"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AL25" s="8">
-        <f t="shared" si="151"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AW25" s="8">
-        <f t="shared" si="152"/>
-        <v>0.27029972752043596</v>
-      </c>
-      <c r="AX25" s="8">
-        <f t="shared" si="153"/>
-        <v>-4.7190047190047713E-3</v>
-      </c>
-      <c r="AY25" s="8">
-        <f t="shared" si="154"/>
-        <v>-4.482758620689653E-2</v>
-      </c>
-      <c r="AZ25" s="8">
-        <f t="shared" si="155"/>
-        <v>1.0000000000000231E-2</v>
-      </c>
-      <c r="BA25" s="8">
         <f t="shared" si="156"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BB25" s="8">
+      <c r="AW25" s="8">
         <f t="shared" si="157"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BC25" s="8">
+        <v>0.27029972752043596</v>
+      </c>
+      <c r="AX25" s="8">
         <f t="shared" si="158"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BD25" s="8">
+        <v>-4.7190047190047713E-3</v>
+      </c>
+      <c r="AY25" s="8">
         <f t="shared" si="159"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BE25" s="8">
+        <v>-4.482758620689653E-2</v>
+      </c>
+      <c r="AZ25" s="8">
         <f t="shared" si="160"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BF25" s="8">
+        <v>-8.9936823104692643E-3</v>
+      </c>
+      <c r="BA25" s="8">
         <f t="shared" si="161"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BG25" s="8">
+      <c r="BB25" s="8">
         <f t="shared" si="162"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH25" s="8">
+      <c r="BC25" s="8">
         <f t="shared" si="163"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BI25" s="8">
+      <c r="BD25" s="8">
         <f t="shared" si="164"/>
         <v>1.0000000000000009E-2</v>
       </c>
+      <c r="BE25" s="8">
+        <f t="shared" si="165"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BF25" s="8">
+        <f t="shared" si="166"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BG25" s="8">
+        <f t="shared" si="167"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BH25" s="8">
+        <f t="shared" si="168"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BI25" s="8">
+        <f t="shared" si="169"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="BJ25" s="8">
-        <f t="shared" si="165"/>
+        <f t="shared" si="170"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -5955,128 +5936,128 @@
         <v>0.25406758448060085</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:R26" si="166">H5/D5-1</f>
+        <f t="shared" ref="H26:R26" si="171">H5/D5-1</f>
         <v>0.27318587504850611</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.25583117363939278</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.25759162303664929</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.24318030605455765</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.21822615056385253</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.33048349056603765</v>
       </c>
       <c r="N26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.34637801831806825</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.30184640085630177</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.28871653740305225</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.20075337912696645</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="166"/>
+        <f t="shared" si="171"/>
         <v>0.19913419913419905</v>
       </c>
       <c r="S26" s="8">
-        <f t="shared" ref="S26" si="167">S5/O5-1</f>
+        <f t="shared" ref="S26" si="172">S5/O5-1</f>
         <v>0.225693730729702</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" ref="T26" si="168">T5/P5-1</f>
+        <f t="shared" ref="T26" si="173">T5/P5-1</f>
         <v>0.23082896524946617</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" ref="U26" si="169">U5/Q5-1</f>
+        <f t="shared" ref="U26" si="174">U5/Q5-1</f>
         <v>0.26646982838162026</v>
       </c>
       <c r="V26" s="8">
-        <f t="shared" ref="V26" si="170">V5/R5-1</f>
+        <f t="shared" ref="V26" si="175">V5/R5-1</f>
         <v>0.25941206807632811</v>
       </c>
       <c r="W26" s="8">
-        <f t="shared" ref="W26" si="171">W5/S5-1</f>
+        <f t="shared" ref="W26" si="176">W5/S5-1</f>
         <v>0.24283078987087037</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" ref="X26" si="172">X5/T5-1</f>
+        <f t="shared" ref="X26" si="177">X5/T5-1</f>
         <v>0.21766561514195581</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" ref="Y26" si="173">Y5/U5-1</f>
+        <f t="shared" ref="Y26" si="178">Y5/U5-1</f>
         <v>0.14192044295497586</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" ref="Z26" si="174">Z5/V5-1</f>
+        <f t="shared" ref="Z26" si="179">Z5/V5-1</f>
         <v>0.14441714441714448</v>
       </c>
       <c r="AA26" s="8">
-        <f t="shared" ref="AA26" si="175">AA5/W5-1</f>
+        <f t="shared" ref="AA26" si="180">AA5/W5-1</f>
         <v>0.11280528943462431</v>
       </c>
       <c r="AB26" s="8">
-        <f t="shared" ref="AB26" si="176">AB5/X5-1</f>
+        <f t="shared" ref="AB26" si="181">AB5/X5-1</f>
         <v>0.11437823834196892</v>
       </c>
       <c r="AC26" s="8">
-        <f t="shared" ref="AC26" si="177">AC5/Y5-1</f>
+        <f t="shared" ref="AC26" si="182">AC5/Y5-1</f>
         <v>0.11267066479520227</v>
       </c>
       <c r="AD26" s="8">
-        <f t="shared" ref="AD26" si="178">AD5/Z5-1</f>
+        <f t="shared" ref="AD26" si="183">AD5/Z5-1</f>
         <v>0.10770515267175562</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" ref="AE26" si="179">AE5/AA5-1</f>
+        <f t="shared" ref="AE26" si="184">AE5/AA5-1</f>
         <v>0.10743300594155447</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" ref="AF26" si="180">AF5/AB5-1</f>
+        <f t="shared" ref="AF26" si="185">AF5/AB5-1</f>
         <v>8.3924212484017158E-2</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" ref="AG26" si="181">AG5/AC5-1</f>
+        <f t="shared" ref="AG26" si="186">AG5/AC5-1</f>
         <v>8.3027522935779752E-2</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" ref="AH26" si="182">AH5/AD5-1</f>
+        <f t="shared" ref="AH26" si="187">AH5/AD5-1</f>
         <v>7.6020243350920724E-2</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" ref="AI26" si="183">AI5/AE5-1</f>
-        <v>7.5799846709734053E-2</v>
+        <f t="shared" ref="AI26" si="188">AI5/AE5-1</f>
+        <v>7.6207160845286337E-2</v>
       </c>
       <c r="AJ26" s="8">
-        <f t="shared" si="149"/>
-        <v>6.6390348525469323E-2</v>
+        <f t="shared" si="154"/>
+        <v>9.7694369973190254E-2</v>
       </c>
       <c r="AK26" s="8">
-        <f t="shared" si="150"/>
-        <v>5.7008682761541696E-2</v>
+        <f t="shared" si="155"/>
+        <v>9.4615628970775134E-2</v>
       </c>
       <c r="AL26" s="8">
-        <f t="shared" si="151"/>
-        <v>3.8372861002702097E-2</v>
+        <f t="shared" si="156"/>
+        <v>6.674572200540374E-2</v>
       </c>
       <c r="AM26" s="8"/>
       <c r="AN26" s="8"/>
@@ -6087,71 +6068,71 @@
         <v>0.26015180265654658</v>
       </c>
       <c r="AT26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>0.28730612859509108</v>
       </c>
       <c r="AU26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>0.24295239209264241</v>
       </c>
       <c r="AV26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>0.24656502917372491</v>
       </c>
       <c r="AW26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>0.18345160803261362</v>
       </c>
       <c r="AX26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>0.11179510079101806</v>
       </c>
       <c r="AY26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>8.7156094902028247E-2</v>
       </c>
       <c r="AZ26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BA26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BB26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BC26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BD26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BE26" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="160"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BF26" s="8">
-        <f t="shared" ref="BF26" si="184">BF5/BE5-1</f>
+        <f t="shared" ref="BF26" si="189">BF5/BE5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG26" s="8">
-        <f t="shared" ref="BG26" si="185">BG5/BF5-1</f>
+        <f t="shared" ref="BG26" si="190">BG5/BF5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH26" s="8">
-        <f t="shared" ref="BH26" si="186">BH5/BG5-1</f>
+        <f t="shared" ref="BH26" si="191">BH5/BG5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BI26" s="8">
-        <f t="shared" ref="BI26" si="187">BI5/BH5-1</f>
+        <f t="shared" ref="BI26" si="192">BI5/BH5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ26" s="8">
-        <f t="shared" ref="BJ26" si="188">BJ5/BI5-1</f>
+        <f t="shared" ref="BJ26" si="193">BJ5/BI5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -6172,63 +6153,63 @@
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="8">
-        <f t="shared" ref="S27:AG27" si="189">(S3-S6)/S3</f>
+        <f t="shared" ref="S27:AG27" si="194">(S3-S6)/S3</f>
         <v>0.79732658959537572</v>
       </c>
       <c r="T27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.80622252282718976</v>
       </c>
       <c r="U27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.79071954851857662</v>
       </c>
       <c r="V27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.78676039835969536</v>
       </c>
       <c r="W27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.78996499416569432</v>
       </c>
       <c r="X27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.79140417191656165</v>
       </c>
       <c r="Y27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.79939167703580816</v>
       </c>
       <c r="Z27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.81512389266914875</v>
       </c>
       <c r="AA27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.80240774666317716</v>
       </c>
       <c r="AB27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.81076692480639523</v>
       </c>
       <c r="AC27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.80702616386193338</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.81927297668038412</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.81828771112405363</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.82245549977179366</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="194"/>
         <v>0.83094943124225706</v>
       </c>
       <c r="AH27" s="8">
@@ -6236,20 +6217,20 @@
         <v>0.83271611469685747</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" ref="AI27:AL27" si="190">(AI3-AI6)/AI3</f>
+        <f t="shared" ref="AI27:AL27" si="195">(AI3-AI6)/AI3</f>
+        <v>0.82671829622458859</v>
+      </c>
+      <c r="AJ27" s="8">
+        <f t="shared" si="195"/>
+        <v>0.83023735810113519</v>
+      </c>
+      <c r="AK27" s="8">
+        <f t="shared" si="195"/>
         <v>0.83</v>
       </c>
-      <c r="AJ27" s="8">
-        <f t="shared" si="190"/>
-        <v>0.83</v>
-      </c>
-      <c r="AK27" s="8">
-        <f t="shared" si="190"/>
-        <v>0.83</v>
-      </c>
       <c r="AL27" s="8">
-        <f t="shared" si="190"/>
-        <v>0.83</v>
+        <f t="shared" si="195"/>
+        <v>0.83000000000000007</v>
       </c>
       <c r="AM27" s="8"/>
       <c r="AN27" s="8"/>
@@ -6259,24 +6240,24 @@
       <c r="AT27" s="8"/>
       <c r="AU27" s="8"/>
       <c r="AV27" s="8">
-        <f t="shared" ref="AV27:AY27" si="191">(AV3-AV6)/AV3</f>
+        <f t="shared" ref="AV27:AY27" si="196">(AV3-AV6)/AV3</f>
         <v>0.79482499898608916</v>
       </c>
       <c r="AW27" s="8">
-        <f t="shared" si="191"/>
+        <f t="shared" si="196"/>
         <v>0.79942110885221052</v>
       </c>
       <c r="AX27" s="8">
-        <f t="shared" si="191"/>
+        <f t="shared" si="196"/>
         <v>0.81015459323232009</v>
       </c>
       <c r="AY27" s="8">
-        <f t="shared" si="191"/>
+        <f t="shared" si="196"/>
         <v>0.82628436895652901</v>
       </c>
       <c r="AZ27" s="8">
-        <f t="shared" ref="AZ27" si="192">(AZ3-AZ6)/AZ3</f>
-        <v>0.83000000000000007</v>
+        <f t="shared" ref="AZ27" si="197">(AZ3-AZ6)/AZ3</f>
+        <v>0.82927418157604738</v>
       </c>
       <c r="BA27" s="8"/>
       <c r="BB27" s="8"/>
@@ -6306,63 +6287,63 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="8">
-        <f t="shared" ref="S28:AG28" si="193">(S4-S7)/S4</f>
+        <f t="shared" ref="S28:AG28" si="198">(S4-S7)/S4</f>
         <v>-1.405152224824356E-2</v>
       </c>
       <c r="T28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-9.6244131455399062E-2</v>
       </c>
       <c r="U28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-5.1652892561983473E-2</v>
       </c>
       <c r="V28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-0.12048192771084337</v>
       </c>
       <c r="W28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-9.0090090090090086E-2</v>
       </c>
       <c r="X28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-0.10398613518197573</v>
       </c>
       <c r="Y28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-5.4635761589403975E-2</v>
       </c>
       <c r="Z28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-0.1092436974789916</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-1.6528925619834711E-2</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-1.6750418760469012E-3</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-8.6355785837651123E-3</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-5.1948051948051951E-2</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-9.8540145985401464E-2</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-7.4866310160427801E-2</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="193"/>
+        <f t="shared" si="198"/>
         <v>-6.9026548672566371E-2</v>
       </c>
       <c r="AH28" s="8">
@@ -6370,19 +6351,19 @@
         <v>-0.17343173431734318</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" ref="AI28:AL28" si="194">(AI4-AI7)/AI4</f>
-        <v>-0.14999999999999988</v>
+        <f t="shared" ref="AI28:AL28" si="199">(AI4-AI7)/AI4</f>
+        <v>-0.22932330827067668</v>
       </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="194"/>
-        <v>-0.14999999999999994</v>
+        <f t="shared" si="199"/>
+        <v>-9.3406593406593408E-2</v>
       </c>
       <c r="AK28" s="8">
-        <f t="shared" si="194"/>
-        <v>-0.14999999999999994</v>
+        <f t="shared" si="199"/>
+        <v>-8.0000000000000085E-2</v>
       </c>
       <c r="AL28" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="199"/>
         <v>-0.14999999999999991</v>
       </c>
       <c r="AM28" s="8"/>
@@ -6393,24 +6374,24 @@
       <c r="AT28" s="8"/>
       <c r="AU28" s="8"/>
       <c r="AV28" s="8">
-        <f t="shared" ref="AV28:AY28" si="195">(AV4-AV7)/AV4</f>
+        <f t="shared" ref="AV28:AY28" si="200">(AV4-AV7)/AV4</f>
         <v>-7.1934604904632146E-2</v>
       </c>
       <c r="AW28" s="8">
-        <f t="shared" si="195"/>
+        <f t="shared" si="200"/>
         <v>-8.9232089232089237E-2</v>
       </c>
       <c r="AX28" s="8">
-        <f t="shared" si="195"/>
+        <f t="shared" si="200"/>
         <v>-1.896551724137931E-2</v>
       </c>
       <c r="AY28" s="8">
-        <f t="shared" si="195"/>
+        <f t="shared" si="200"/>
         <v>-0.10333935018050541</v>
       </c>
       <c r="AZ28" s="8">
-        <f t="shared" ref="AZ28" si="196">(AZ4-AZ7)/AZ4</f>
-        <v>-0.14999999999999986</v>
+        <f t="shared" ref="AZ28" si="201">(AZ4-AZ7)/AZ4</f>
+        <v>-0.13695601688470763</v>
       </c>
       <c r="BA28" s="8"/>
       <c r="BB28" s="8"/>
@@ -6432,223 +6413,223 @@
         <v>0.7284105131414268</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" ref="D29:R29" si="197">D9/D5</f>
+        <f t="shared" ref="D29:R29" si="202">D9/D5</f>
         <v>0.74000776096235932</v>
       </c>
       <c r="E29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.73565346168085899</v>
       </c>
       <c r="F29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.74240837696335082</v>
       </c>
       <c r="G29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.74484364604125086</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.74123742761353251</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.73791273584905659</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.7374410213710797</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.75541878512175542</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.75806855141356022</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.74872590294704189</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.74850546279117702</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.74224049331963005</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.74548631333721604</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.75</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="197"/>
+        <f t="shared" si="202"/>
         <v>0.74574522949974209</v>
       </c>
       <c r="S29" s="8">
-        <f t="shared" ref="S29:AL29" si="198">S9/S5</f>
+        <f t="shared" ref="S29:AL29" si="203">S9/S5</f>
         <v>0.73922522220358877</v>
       </c>
       <c r="T29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.74558359621451109</v>
       </c>
       <c r="U29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.73131283695177041</v>
       </c>
       <c r="V29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.72508872508872513</v>
       </c>
       <c r="W29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.72405883146673866</v>
       </c>
       <c r="X29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.72448186528497405</v>
       </c>
       <c r="Y29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.73357151971417633</v>
       </c>
       <c r="Z29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.74952290076335881</v>
       </c>
       <c r="AA29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.74233054444040258</v>
       </c>
       <c r="AB29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.75438800418458674</v>
       </c>
       <c r="AC29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.75286697247706424</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.76870894799181655</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.7632760319719698</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.76847184986595174</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.77710715798390517</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="203"/>
         <v>0.77814470129090363</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="198"/>
-        <v>0.77479440789473675</v>
+        <f t="shared" si="203"/>
+        <v>0.76955946688371146</v>
       </c>
       <c r="AJ29" s="8">
-        <f t="shared" si="198"/>
-        <v>0.77416001866435236</v>
+        <f t="shared" si="203"/>
+        <v>0.78096912856584599</v>
       </c>
       <c r="AK29" s="8">
-        <f t="shared" si="198"/>
-        <v>0.77397764463219731</v>
+        <f t="shared" si="203"/>
+        <v>0.77976648238702595</v>
       </c>
       <c r="AL29" s="8">
-        <f t="shared" si="198"/>
-        <v>0.77829916946627276</v>
+        <f t="shared" si="203"/>
+        <v>0.77967428674886197</v>
       </c>
       <c r="AM29" s="8"/>
       <c r="AN29" s="8"/>
       <c r="AO29" s="8"/>
       <c r="AP29" s="8"/>
       <c r="AR29" s="8">
-        <f t="shared" ref="AR29:BE29" si="199">AR9/AR5</f>
+        <f t="shared" ref="AR29:BE29" si="204">AR9/AR5</f>
         <v>0.7369070208728653</v>
       </c>
       <c r="AS29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.74017467248908297</v>
       </c>
       <c r="AT29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.75231021172066903</v>
       </c>
       <c r="AU29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.74411820063993972</v>
       </c>
       <c r="AV29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.75</v>
       </c>
       <c r="AW29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.73335034447563152</v>
       </c>
       <c r="AX29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.75497030725535763</v>
       </c>
       <c r="AY29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.77192241720543608</v>
       </c>
       <c r="AZ29" s="8">
-        <f t="shared" si="199"/>
-        <v>0.77556669247448884</v>
+        <f t="shared" si="204"/>
+        <v>0.77265022517532311</v>
       </c>
       <c r="BA29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.78</v>
       </c>
       <c r="BB29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.78</v>
       </c>
       <c r="BC29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.77999999999999992</v>
       </c>
       <c r="BD29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.78</v>
       </c>
       <c r="BE29" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="204"/>
         <v>0.78</v>
       </c>
       <c r="BF29" s="8">
-        <f t="shared" ref="BF29:BJ29" si="200">BF9/BF5</f>
+        <f t="shared" ref="BF29:BJ29" si="205">BF9/BF5</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="BG29" s="8">
-        <f t="shared" si="200"/>
+        <f t="shared" si="205"/>
         <v>0.77999999999999992</v>
       </c>
       <c r="BH29" s="8">
-        <f t="shared" si="200"/>
+        <f t="shared" si="205"/>
         <v>0.78</v>
       </c>
       <c r="BI29" s="8">
-        <f t="shared" si="200"/>
+        <f t="shared" si="205"/>
         <v>0.78</v>
       </c>
       <c r="BJ29" s="8">
-        <f t="shared" si="200"/>
+        <f t="shared" si="205"/>
         <v>0.78</v>
       </c>
     </row>
@@ -6661,224 +6642,224 @@
         <v>1.6687526074259491E-3</v>
       </c>
       <c r="D30" s="8">
-        <f t="shared" ref="D30:R30" si="201">D15/D5</f>
+        <f t="shared" ref="D30:R30" si="206">D15/D5</f>
         <v>3.2596041909196738E-2</v>
       </c>
       <c r="E30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>5.7386153276564232E-2</v>
       </c>
       <c r="F30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>7.3647469458987785E-2</v>
       </c>
       <c r="G30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>6.35395874916833E-2</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>3.505028954587016E-2</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>2.7122641509433963E-2</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>3.8023868998057174E-2</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>5.6194808670056197E-2</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>1.451088316237178E-2</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>1.4402836250830933E-2</v>
       </c>
       <c r="N30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>-7.4211502782931356E-3</v>
       </c>
       <c r="O30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>-2.8776978417266189E-2</v>
       </c>
       <c r="P30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>3.4556396816152204E-2</v>
       </c>
       <c r="Q30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>4.8579073629821001E-2</v>
       </c>
       <c r="R30" s="8">
-        <f t="shared" si="201"/>
+        <f t="shared" si="206"/>
         <v>3.3178614406051229E-2</v>
       </c>
       <c r="S30" s="8">
-        <f t="shared" ref="S30:AL30" si="202">S15/S5</f>
+        <f t="shared" ref="S30:AL30" si="207">S15/S5</f>
         <v>5.9366090893845383E-2</v>
       </c>
       <c r="T30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>5.2365930599369087E-2</v>
       </c>
       <c r="U30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>5.5369371994754479E-3</v>
       </c>
       <c r="V30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>-2.4024024024024024E-2</v>
       </c>
       <c r="W30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>2.698691134799622E-3</v>
       </c>
       <c r="X30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Y30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>5.8695929564884522E-2</v>
       </c>
       <c r="Z30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>4.2581106870229007E-2</v>
       </c>
       <c r="AA30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>4.9957560324966656E-2</v>
       </c>
       <c r="AB30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>0.17156805765430663</v>
       </c>
       <c r="AC30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>0.17213302752293577</v>
       </c>
       <c r="AD30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>0.17465274038979217</v>
       </c>
       <c r="AE30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>0.18712361765027921</v>
       </c>
       <c r="AF30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>0.1912064343163539</v>
       </c>
       <c r="AG30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>0.20044472681067343</v>
       </c>
       <c r="AH30" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="207"/>
         <v>0.18212748924246974</v>
       </c>
       <c r="AI30" s="8">
-        <f t="shared" si="202"/>
-        <v>0.19707802729286078</v>
+        <f t="shared" si="207"/>
+        <v>0.19757859395665886</v>
       </c>
       <c r="AJ30" s="8">
-        <f t="shared" si="202"/>
-        <v>0.18954437258713475</v>
+        <f t="shared" si="207"/>
+        <v>0.2278233685033216</v>
       </c>
       <c r="AK30" s="8">
-        <f t="shared" si="202"/>
-        <v>0.19468424896242276</v>
+        <f t="shared" si="207"/>
+        <v>0.21488437782646755</v>
       </c>
       <c r="AL30" s="8">
-        <f t="shared" si="202"/>
-        <v>0.18610911621111639</v>
+        <f t="shared" si="207"/>
+        <v>0.19922847019556314</v>
       </c>
       <c r="AM30" s="8"/>
       <c r="AN30" s="8"/>
       <c r="AO30" s="8"/>
       <c r="AP30" s="8"/>
       <c r="AR30" s="8">
-        <f t="shared" ref="AR30:BE30" si="203">AR15/AR5</f>
+        <f t="shared" ref="AR30:BE30" si="208">AR15/AR5</f>
         <v>4.3074003795066415E-2</v>
       </c>
       <c r="AS30" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="208"/>
         <v>4.0280078301460624E-2</v>
       </c>
       <c r="AT30" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="208"/>
         <v>1.7370452684524505E-2</v>
       </c>
       <c r="AU30" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="208"/>
         <v>2.1409749670619236E-2</v>
       </c>
       <c r="AV30" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="208"/>
         <v>3.5897629473048469E-2</v>
       </c>
       <c r="AW30" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="208"/>
         <v>3.2852768563409032E-2</v>
       </c>
       <c r="AX30" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="208"/>
         <v>0.14375878589666352</v>
       </c>
       <c r="AY30" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="208"/>
         <v>0.19013062409288825</v>
       </c>
       <c r="AZ30" s="8">
-        <f t="shared" si="203"/>
-        <v>0.19259376081376786</v>
+        <f t="shared" si="208"/>
+        <v>0.19232167085317689</v>
       </c>
       <c r="BA30" s="8">
-        <f t="shared" si="203"/>
-        <v>0.21215937379340727</v>
+        <f t="shared" si="208"/>
+        <v>0.22288340708775037</v>
       </c>
       <c r="BB30" s="8">
-        <f t="shared" si="203"/>
-        <v>0.226234873559955</v>
+        <f t="shared" si="208"/>
+        <v>0.23636653457996953</v>
       </c>
       <c r="BC30" s="8">
-        <f t="shared" si="203"/>
-        <v>0.22820570238829757</v>
+        <f t="shared" si="208"/>
+        <v>0.23805237997351739</v>
       </c>
       <c r="BD30" s="8">
-        <f t="shared" si="203"/>
-        <v>0.23102818434911712</v>
+        <f t="shared" si="208"/>
+        <v>0.24067820597713691</v>
       </c>
       <c r="BE30" s="8">
-        <f t="shared" si="203"/>
-        <v>0.23352890677627106</v>
+        <f t="shared" si="208"/>
+        <v>0.24303618200708041</v>
       </c>
       <c r="BF30" s="8">
-        <f t="shared" ref="BF30:BJ30" si="204">BF15/BF5</f>
-        <v>0.2351278528313743</v>
+        <f t="shared" ref="BF30:BJ30" si="209">BF15/BF5</f>
+        <v>0.24458972997180639</v>
       </c>
       <c r="BG30" s="8">
-        <f t="shared" si="204"/>
-        <v>0.23664306042252112</v>
+        <f t="shared" si="209"/>
+        <v>0.24607200829376613</v>
       </c>
       <c r="BH30" s="8">
-        <f t="shared" si="204"/>
-        <v>0.23811004905579419</v>
+        <f t="shared" si="209"/>
+        <v>0.24751228448493887</v>
       </c>
       <c r="BI30" s="8">
-        <f t="shared" si="204"/>
-        <v>0.23954630055467732</v>
+        <f t="shared" si="209"/>
+        <v>0.24892497463973945</v>
       </c>
       <c r="BJ30" s="8">
-        <f t="shared" si="204"/>
-        <v>0.24096045405215621</v>
+        <f t="shared" si="209"/>
+        <v>0.25031721406676893</v>
       </c>
       <c r="BL30" t="s">
         <v>44</v>
@@ -6896,131 +6877,131 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8">
-        <f t="shared" ref="G31:R31" si="205">G10/C10-1</f>
+        <f t="shared" ref="G31:R31" si="210">G10/C10-1</f>
         <v>0.12765957446808507</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.19638242894056845</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.22081218274111669</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.30808080808080818</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.30660377358490565</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.31101511879049681</v>
       </c>
       <c r="M31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.60914760914760913</v>
       </c>
       <c r="N31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.60424710424710426</v>
       </c>
       <c r="O31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.55054151624548742</v>
       </c>
       <c r="P31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.47940691927512358</v>
       </c>
       <c r="Q31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.1653746770025839</v>
       </c>
       <c r="R31" s="8">
-        <f t="shared" si="205"/>
+        <f t="shared" si="210"/>
         <v>0.12996389891696758</v>
       </c>
       <c r="S31" s="8">
-        <f t="shared" ref="S31" si="206">S10/O10-1</f>
+        <f t="shared" ref="S31" si="211">S10/O10-1</f>
         <v>0.1071012805587892</v>
       </c>
       <c r="T31" s="8">
-        <f t="shared" ref="T31" si="207">T10/P10-1</f>
+        <f t="shared" ref="T31" si="212">T10/P10-1</f>
         <v>0.13585746102449892</v>
       </c>
       <c r="U31" s="8">
-        <f t="shared" ref="U31" si="208">U10/Q10-1</f>
+        <f t="shared" ref="U31" si="213">U10/Q10-1</f>
         <v>0.33370288248337032</v>
       </c>
       <c r="V31" s="8">
-        <f t="shared" ref="V31" si="209">V10/R10-1</f>
+        <f t="shared" ref="V31" si="214">V10/R10-1</f>
         <v>0.37486687965921184</v>
       </c>
       <c r="W31" s="8">
-        <f t="shared" ref="W31" si="210">W10/S10-1</f>
+        <f t="shared" ref="W31" si="215">W10/S10-1</f>
         <v>0.3859095688748686</v>
       </c>
       <c r="X31" s="8">
-        <f t="shared" ref="X31" si="211">X10/T10-1</f>
+        <f t="shared" ref="X31" si="216">X10/T10-1</f>
         <v>0.30294117647058827</v>
       </c>
       <c r="Y31" s="8">
-        <f t="shared" ref="Y31" si="212">Y10/U10-1</f>
+        <f t="shared" ref="Y31" si="217">Y10/U10-1</f>
         <v>6.4006650041562807E-2</v>
       </c>
       <c r="Z31" s="8">
-        <f t="shared" ref="Z31" si="213">Z10/V10-1</f>
+        <f t="shared" ref="Z31" si="218">Z10/V10-1</f>
         <v>-0.12625871417505807</v>
       </c>
       <c r="AA31" s="8">
-        <f t="shared" ref="AA31" si="214">AA10/W10-1</f>
+        <f t="shared" ref="AA31" si="219">AA10/W10-1</f>
         <v>-8.4218512898330822E-2</v>
       </c>
       <c r="AB31" s="8">
-        <f t="shared" ref="AB31" si="215">AB10/X10-1</f>
+        <f t="shared" ref="AB31" si="220">AB10/X10-1</f>
         <v>-8.2016553799849512E-2</v>
       </c>
       <c r="AC31" s="8">
-        <f t="shared" ref="AC31" si="216">AC10/Y10-1</f>
+        <f t="shared" ref="AC31" si="221">AC10/Y10-1</f>
         <v>-5.9374999999999956E-2</v>
       </c>
       <c r="AD31" s="8">
-        <f t="shared" ref="AD31" si="217">AD10/Z10-1</f>
+        <f t="shared" ref="AD31" si="222">AD10/Z10-1</f>
         <v>0.13031914893617014</v>
       </c>
       <c r="AE31" s="8">
-        <f t="shared" ref="AE31" si="218">AE10/AA10-1</f>
+        <f t="shared" ref="AE31" si="223">AE10/AA10-1</f>
         <v>0.13338856669428334</v>
       </c>
       <c r="AF31" s="8">
-        <f t="shared" ref="AF31" si="219">AF10/AB10-1</f>
+        <f t="shared" ref="AF31" si="224">AF10/AB10-1</f>
         <v>0.1057377049180328</v>
       </c>
       <c r="AG31" s="8">
-        <f t="shared" ref="AG31" si="220">AG10/AC10-1</f>
+        <f t="shared" ref="AG31" si="225">AG10/AC10-1</f>
         <v>0.12624584717607967</v>
       </c>
       <c r="AH31" s="8">
-        <f t="shared" ref="AH31" si="221">AH10/AD10-1</f>
+        <f t="shared" ref="AH31" si="226">AH10/AD10-1</f>
         <v>0.11372549019607847</v>
       </c>
       <c r="AI31" s="8">
-        <f t="shared" ref="AI31" si="222">AI10/AE10-1</f>
+        <f t="shared" ref="AI31" si="227">AI10/AE10-1</f>
+        <v>6.7251461988304007E-2</v>
+      </c>
+      <c r="AJ31" s="8">
+        <f t="shared" ref="AJ31" si="228">AJ10/AF10-1</f>
+        <v>9.7850259451445432E-2</v>
+      </c>
+      <c r="AK31" s="8">
+        <f t="shared" ref="AK31" si="229">AK10/AG10-1</f>
         <v>0.1100000000000001</v>
       </c>
-      <c r="AJ31" s="8">
-        <f t="shared" ref="AJ31" si="223">AJ10/AF10-1</f>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="AK31" s="8">
-        <f t="shared" ref="AK31" si="224">AK10/AG10-1</f>
-        <v>0.1100000000000001</v>
-      </c>
       <c r="AL31" s="8">
-        <f t="shared" ref="AL31" si="225">AL10/AH10-1</f>
+        <f t="shared" ref="AL31" si="230">AL10/AH10-1</f>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AM31" s="8"/>
@@ -7029,75 +7010,75 @@
       <c r="AP31" s="8"/>
       <c r="AR31" s="8"/>
       <c r="AS31" s="8">
-        <f t="shared" ref="AS31:BE31" si="226">AS10/AR10-1</f>
+        <f t="shared" ref="AS31:BE31" si="231">AS10/AR10-1</f>
         <v>0.21442369607211842</v>
       </c>
       <c r="AT31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>0.46659597030752908</v>
       </c>
       <c r="AU31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>0.30079537237888654</v>
       </c>
       <c r="AV31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>0.24096720400222349</v>
       </c>
       <c r="AW31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>0.13213885778275469</v>
       </c>
       <c r="AX31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>-2.9475766567754746E-2</v>
       </c>
       <c r="AY31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>0.11964940888707698</v>
       </c>
       <c r="AZ31" s="8">
-        <f t="shared" si="226"/>
-        <v>0.10211541962497717</v>
+        <f t="shared" si="231"/>
+        <v>8.6029492080829995E-2</v>
       </c>
       <c r="BA31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BB31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BC31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BD31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE31" s="8">
-        <f t="shared" si="226"/>
+        <f t="shared" si="231"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF31" s="8">
-        <f t="shared" ref="BF31" si="227">BF10/BE10-1</f>
+        <f t="shared" ref="BF31" si="232">BF10/BE10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG31" s="8">
-        <f t="shared" ref="BG31" si="228">BG10/BF10-1</f>
+        <f t="shared" ref="BG31" si="233">BG10/BF10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH31" s="8">
-        <f t="shared" ref="BH31" si="229">BH10/BG10-1</f>
+        <f t="shared" ref="BH31" si="234">BH10/BG10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI31" s="8">
-        <f t="shared" ref="BI31" si="230">BI10/BH10-1</f>
+        <f t="shared" ref="BI31" si="235">BI10/BH10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ31" s="8">
-        <f t="shared" ref="BJ31" si="231">BJ10/BI10-1</f>
+        <f t="shared" ref="BJ31" si="236">BJ10/BI10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BL31" t="s">
@@ -7116,143 +7097,143 @@
         <v>0.46141009595327492</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" ref="D32:R32" si="232">D11/D5</f>
+        <f t="shared" ref="D32:R32" si="237">D11/D5</f>
         <v>0.4474194800155219</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.43206219918548688</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.43455497382198954</v>
       </c>
       <c r="G32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.44211576846307388</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.45839683023468453</v>
       </c>
       <c r="I32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.46816037735849059</v>
       </c>
       <c r="J32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.45600888148764918</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.45410757291945408</v>
       </c>
       <c r="L32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.49787340505379035</v>
       </c>
       <c r="M32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.45712386439175717</v>
       </c>
       <c r="N32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.48361162646876932</v>
       </c>
       <c r="O32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.49126413155190135</v>
       </c>
       <c r="P32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.44166181324014753</v>
       </c>
       <c r="Q32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.43864181583317957</v>
       </c>
       <c r="R32" s="8">
-        <f t="shared" si="232"/>
+        <f t="shared" si="237"/>
         <v>0.45246690734055356</v>
       </c>
       <c r="S32" s="8">
-        <f t="shared" ref="S32:AL32" si="233">S11/S5</f>
+        <f t="shared" ref="S32:AL32" si="238">S11/S5</f>
         <v>0.42663089049136343</v>
       </c>
       <c r="T32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.43154574132492113</v>
       </c>
       <c r="U32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.45330030598863469</v>
       </c>
       <c r="V32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.47283647283647284</v>
       </c>
       <c r="W32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.45499932532721632</v>
       </c>
       <c r="X32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.44352331606217615</v>
       </c>
       <c r="Y32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.42682148781421464</v>
       </c>
       <c r="Z32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.4037452290076336</v>
       </c>
       <c r="AA32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.38244210015763308</v>
       </c>
       <c r="AB32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.36185051726142042</v>
       </c>
       <c r="AC32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.36387614678899083</v>
       </c>
       <c r="AD32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.37008721869279637</v>
       </c>
       <c r="AE32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.35464797985327934</v>
       </c>
       <c r="AF32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.34573726541554961</v>
       </c>
       <c r="AG32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.35186361711139347</v>
       </c>
       <c r="AH32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.34734314019813872</v>
       </c>
       <c r="AI32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
+        <v>0.34886560179061959</v>
+      </c>
+      <c r="AJ32" s="8">
+        <f t="shared" si="238"/>
+        <v>0.33636186010160218</v>
+      </c>
+      <c r="AK32" s="8">
+        <f t="shared" si="238"/>
         <v>0.34</v>
       </c>
-      <c r="AJ32" s="8">
-        <f t="shared" si="233"/>
-        <v>0.34</v>
-      </c>
-      <c r="AK32" s="8">
-        <f t="shared" si="233"/>
-        <v>0.34</v>
-      </c>
       <c r="AL32" s="8">
-        <f t="shared" si="233"/>
+        <f t="shared" si="238"/>
         <v>0.34</v>
       </c>
       <c r="AM32" s="8"/>
@@ -7260,87 +7241,87 @@
       <c r="AO32" s="8"/>
       <c r="AP32" s="8"/>
       <c r="AR32" s="8">
-        <f t="shared" ref="AR32:BE32" si="234">AR11/AR5</f>
+        <f t="shared" ref="AR32:BE32" si="239">AR11/AR5</f>
         <v>0.44316888045540798</v>
       </c>
       <c r="AS32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.45655774732720977</v>
       </c>
       <c r="AT32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.47350567317814951</v>
       </c>
       <c r="AU32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.45520421607378131</v>
       </c>
       <c r="AV32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.44749358296844333</v>
       </c>
       <c r="AW32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.43142383261035977</v>
       </c>
       <c r="AX32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.36942364517887366</v>
       </c>
       <c r="AY32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.34983507058978758</v>
       </c>
       <c r="AZ32" s="8">
-        <f t="shared" si="234"/>
-        <v>0.33965736506284749</v>
+        <f t="shared" si="239"/>
+        <v>0.34880799229250631</v>
       </c>
       <c r="BA32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.33</v>
       </c>
       <c r="BB32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.32</v>
       </c>
       <c r="BC32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.32</v>
       </c>
       <c r="BD32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.32</v>
       </c>
       <c r="BE32" s="8">
-        <f t="shared" si="234"/>
+        <f t="shared" si="239"/>
         <v>0.32</v>
       </c>
       <c r="BF32" s="8">
-        <f t="shared" ref="BF32:BJ32" si="235">BF11/BF5</f>
+        <f t="shared" ref="BF32:BJ32" si="240">BF11/BF5</f>
         <v>0.32</v>
       </c>
       <c r="BG32" s="8">
-        <f t="shared" si="235"/>
+        <f t="shared" si="240"/>
         <v>0.32</v>
       </c>
       <c r="BH32" s="8">
-        <f t="shared" si="235"/>
+        <f t="shared" si="240"/>
         <v>0.32</v>
       </c>
       <c r="BI32" s="8">
-        <f t="shared" si="235"/>
+        <f t="shared" si="240"/>
         <v>0.31999999999999995</v>
       </c>
       <c r="BJ32" s="8">
-        <f t="shared" si="235"/>
+        <f t="shared" si="240"/>
         <v>0.32</v>
       </c>
       <c r="BL32" t="s">
         <v>46</v>
       </c>
       <c r="BM32" s="5">
-        <f>NPV(BM31,AV20:GN20)</f>
-        <v>128858.44886436802</v>
+        <f>NPV(BM31,AZ20:GN20)</f>
+        <v>153823.13440534327</v>
       </c>
     </row>
     <row r="33" spans="2:65" x14ac:dyDescent="0.3">
@@ -7352,132 +7333,132 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
-        <f t="shared" ref="G33:R33" si="236">G12/C12-1</f>
+        <f t="shared" ref="G33:R33" si="241">G12/C12-1</f>
         <v>0.13461538461538458</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.23674911660777376</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.26199261992619927</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.30545454545454542</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.22711864406779658</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>7.1428571428571397E-2</v>
       </c>
       <c r="M33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.39473684210526305</v>
       </c>
       <c r="N33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.36490250696378834</v>
       </c>
       <c r="O33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.38674033149171261</v>
       </c>
       <c r="P33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.30400000000000005</v>
       </c>
       <c r="Q33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>9.4339622641509413E-2</v>
       </c>
       <c r="R33" s="8">
-        <f t="shared" si="236"/>
+        <f t="shared" si="241"/>
         <v>0.17142857142857149</v>
       </c>
       <c r="S33" s="8">
-        <f t="shared" ref="S33" si="237">S12/O12-1</f>
+        <f t="shared" ref="S33" si="242">S12/O12-1</f>
         <v>0.11354581673306763</v>
       </c>
       <c r="T33" s="8">
-        <f t="shared" ref="T33" si="238">T12/P12-1</f>
+        <f t="shared" ref="T33" si="243">T12/P12-1</f>
         <v>0.30674846625766872</v>
       </c>
       <c r="U33" s="8">
-        <f t="shared" ref="U33" si="239">U12/Q12-1</f>
+        <f t="shared" ref="U33" si="244">U12/Q12-1</f>
         <v>0.27777777777777768</v>
       </c>
       <c r="V33" s="8">
-        <f t="shared" ref="V33" si="240">V12/R12-1</f>
+        <f t="shared" ref="V33" si="245">V12/R12-1</f>
         <v>0.27700348432055755</v>
       </c>
       <c r="W33" s="8">
-        <f t="shared" ref="W33" si="241">W12/S12-1</f>
+        <f t="shared" ref="W33" si="246">W12/S12-1</f>
         <v>0.17352415026833623</v>
       </c>
       <c r="X33" s="8">
-        <f t="shared" ref="X33" si="242">X12/T12-1</f>
+        <f t="shared" ref="X33" si="247">X12/T12-1</f>
         <v>1.2519561815336422E-2</v>
       </c>
       <c r="Y33" s="8">
-        <f t="shared" ref="Y33" si="243">Y12/U12-1</f>
+        <f t="shared" ref="Y33" si="248">Y12/U12-1</f>
         <v>-4.4977511244377322E-3</v>
       </c>
       <c r="Z33" s="8">
-        <f t="shared" ref="Z33" si="244">Z12/V12-1</f>
+        <f t="shared" ref="Z33" si="249">Z12/V12-1</f>
         <v>-0.20054570259208726</v>
       </c>
       <c r="AA33" s="8">
-        <f t="shared" ref="AA33" si="245">AA12/W12-1</f>
+        <f t="shared" ref="AA33" si="250">AA12/W12-1</f>
         <v>-2.7439024390243927E-2</v>
       </c>
       <c r="AB33" s="8">
-        <f t="shared" ref="AB33" si="246">AB12/X12-1</f>
+        <f t="shared" ref="AB33" si="251">AB12/X12-1</f>
         <v>-2.3183925811437356E-2</v>
       </c>
       <c r="AC33" s="8">
-        <f t="shared" ref="AC33" si="247">AC12/Y12-1</f>
+        <f t="shared" ref="AC33" si="252">AC12/Y12-1</f>
         <v>-4.8192771084337394E-2</v>
       </c>
       <c r="AD33" s="8">
-        <f t="shared" ref="AD33" si="248">AD12/Z12-1</f>
+        <f t="shared" ref="AD33" si="253">AD12/Z12-1</f>
         <v>7.8498293515358419E-2</v>
       </c>
       <c r="AE33" s="8">
-        <f t="shared" ref="AE33" si="249">AE12/AA12-1</f>
+        <f t="shared" ref="AE33" si="254">AE12/AA12-1</f>
         <v>1.4106583072100332E-2</v>
       </c>
       <c r="AF33" s="8">
-        <f t="shared" ref="AF33" si="250">AF12/AB12-1</f>
+        <f t="shared" ref="AF33" si="255">AF12/AB12-1</f>
         <v>0.125</v>
       </c>
       <c r="AG33" s="8">
-        <f t="shared" ref="AG33" si="251">AG12/AC12-1</f>
+        <f t="shared" ref="AG33" si="256">AG12/AC12-1</f>
         <v>0.125</v>
       </c>
       <c r="AH33" s="8">
-        <f t="shared" ref="AH33" si="252">AH12/AD12-1</f>
+        <f t="shared" ref="AH33" si="257">AH12/AD12-1</f>
         <v>0.21360759493670889</v>
       </c>
       <c r="AI33" s="8">
-        <f t="shared" ref="AI33" si="253">AI12/AE12-1</f>
-        <v>0.25</v>
+        <f t="shared" ref="AI33" si="258">AI12/AE12-1</f>
+        <v>7.727975270479126E-2</v>
       </c>
       <c r="AJ33" s="8">
-        <f t="shared" ref="AJ33" si="254">AJ12/AF12-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="AJ33" si="259">AJ12/AF12-1</f>
+        <v>3.234880450070321E-2</v>
       </c>
       <c r="AK33" s="8">
-        <f t="shared" ref="AK33" si="255">AK12/AG12-1</f>
-        <v>0.15999999999999992</v>
+        <f t="shared" ref="AK33" si="260">AK12/AG12-1</f>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AL33" s="8">
-        <f t="shared" ref="AL33" si="256">AL12/AH12-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="AL33" si="261">AL12/AH12-1</f>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM33" s="8"/>
       <c r="AN33" s="8"/>
@@ -7485,75 +7466,75 @@
       <c r="AP33" s="8"/>
       <c r="AR33" s="8"/>
       <c r="AS33" s="8">
-        <f t="shared" ref="AS33:BE33" si="257">AS12/AR12-1</f>
+        <f t="shared" ref="AS33:BE33" si="262">AS12/AR12-1</f>
         <v>0.23599632690541772</v>
       </c>
       <c r="AT33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>0.26597325408618122</v>
       </c>
       <c r="AU33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>0.22476525821596249</v>
       </c>
       <c r="AV33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>0.24484906564446574</v>
       </c>
       <c r="AW33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>-1.7321016166281789E-2</v>
       </c>
       <c r="AX33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>-7.4422248335291874E-3</v>
       </c>
       <c r="AY33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>0.11917916337805834</v>
       </c>
       <c r="AZ33" s="8">
-        <f t="shared" si="257"/>
-        <v>0.16720733427362466</v>
+        <f t="shared" si="262"/>
+        <v>5.6812411847672717E-2</v>
       </c>
       <c r="BA33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE33" s="8">
-        <f t="shared" si="257"/>
+        <f t="shared" si="262"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF33" s="8">
-        <f t="shared" ref="BF33" si="258">BF12/BE12-1</f>
+        <f t="shared" ref="BF33" si="263">BF12/BE12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG33" s="8">
-        <f t="shared" ref="BG33" si="259">BG12/BF12-1</f>
+        <f t="shared" ref="BG33" si="264">BG12/BF12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH33" s="8">
-        <f t="shared" ref="BH33" si="260">BH12/BG12-1</f>
+        <f t="shared" ref="BH33" si="265">BH12/BG12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BI33" s="8">
-        <f t="shared" ref="BI33" si="261">BI12/BH12-1</f>
+        <f t="shared" ref="BI33" si="266">BI12/BH12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ33" s="8">
-        <f t="shared" ref="BJ33" si="262">BJ12/BI12-1</f>
+        <f t="shared" ref="BJ33" si="267">BJ12/BI12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BL33" t="s">
@@ -7561,7 +7542,7 @@
       </c>
       <c r="BM33" s="5">
         <f>Main!D8</f>
-        <v>10451</v>
+        <v>12021</v>
       </c>
     </row>
     <row r="34" spans="2:65" x14ac:dyDescent="0.3">
@@ -7573,143 +7554,143 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" ref="D34:R34" si="263">D19/D18</f>
+        <f t="shared" ref="D34:R34" si="268">D19/D18</f>
         <v>0.26984126984126983</v>
       </c>
       <c r="E34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>0.26712328767123289</v>
       </c>
       <c r="F34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>6.7873303167420809E-2</v>
       </c>
       <c r="G34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>0.10649350649350649</v>
       </c>
       <c r="H34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>-0.2943722943722944</v>
       </c>
       <c r="I34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>0.1796875</v>
       </c>
       <c r="J34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>-0.5146443514644351</v>
       </c>
       <c r="K34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>0.18672199170124482</v>
       </c>
       <c r="L34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>0.4451219512195122</v>
       </c>
       <c r="M34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>2.703125</v>
       </c>
       <c r="N34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>-61</v>
       </c>
       <c r="O34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>-1.1063829787234043</v>
       </c>
       <c r="P34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>-2.1287246722288438</v>
       </c>
       <c r="Q34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>0.13108396354469654</v>
       </c>
       <c r="R34" s="8">
-        <f t="shared" si="263"/>
+        <f t="shared" si="268"/>
         <v>0.37176470588235294</v>
       </c>
       <c r="S34" s="8">
-        <f t="shared" ref="S34:AL34" si="264">S19/S18</f>
+        <f t="shared" ref="S34:AL34" si="269">S19/S18</f>
         <v>0.22350993377483444</v>
       </c>
       <c r="T34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.35230024213075062</v>
       </c>
       <c r="U34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>-0.56521739130434778</v>
       </c>
       <c r="V34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.85786802030456855</v>
       </c>
       <c r="W34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>1.9655172413793103</v>
       </c>
       <c r="X34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.62430939226519333</v>
       </c>
       <c r="Y34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.55789473684210522</v>
       </c>
       <c r="Z34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>3.9696969696969697</v>
       </c>
       <c r="AA34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.38957055214723929</v>
       </c>
       <c r="AB34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.15080428954423591</v>
       </c>
       <c r="AC34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.17686617350369871</v>
       </c>
       <c r="AD34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.1209726443768997</v>
       </c>
       <c r="AE34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.17889662560257097</v>
       </c>
       <c r="AF34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.22210125204137179</v>
       </c>
       <c r="AG34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.12542955326460481</v>
       </c>
       <c r="AH34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.14084507042253522</v>
       </c>
       <c r="AI34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
+        <v>0.21935157041540021</v>
+      </c>
+      <c r="AJ34" s="8">
+        <f t="shared" si="269"/>
+        <v>0.21571072319201995</v>
+      </c>
+      <c r="AK34" s="8">
+        <f t="shared" si="269"/>
         <v>0.18</v>
       </c>
-      <c r="AJ34" s="8">
-        <f t="shared" si="264"/>
-        <v>0.18</v>
-      </c>
-      <c r="AK34" s="8">
-        <f t="shared" si="264"/>
-        <v>0.18</v>
-      </c>
       <c r="AL34" s="8">
-        <f t="shared" si="264"/>
+        <f t="shared" si="269"/>
         <v>0.18</v>
       </c>
       <c r="AM34" s="8"/>
@@ -7717,96 +7698,319 @@
       <c r="AO34" s="8"/>
       <c r="AP34" s="8"/>
       <c r="AR34" s="8">
-        <f t="shared" ref="AR34:BE34" si="265">AR19/AR18</f>
+        <f t="shared" ref="AR34:BE34" si="270">AR19/AR18</f>
         <v>0.14285714285714285</v>
       </c>
       <c r="AS34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>-0.12919633774160733</v>
       </c>
       <c r="AT34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>0.82152974504249288</v>
       </c>
       <c r="AU34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>-0.59000390472471687</v>
       </c>
       <c r="AV34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>4.5478036175710591E-2</v>
       </c>
       <c r="AW34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>0.68484848484848482</v>
       </c>
       <c r="AX34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>0.16444444444444445</v>
       </c>
       <c r="AY34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>0.16684592632428072</v>
       </c>
       <c r="AZ34" s="8">
-        <f t="shared" si="265"/>
-        <v>0.17909540113827205</v>
+        <f t="shared" si="270"/>
+        <v>0.220769776877733</v>
       </c>
       <c r="BA34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>0.18</v>
       </c>
       <c r="BB34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>0.18</v>
       </c>
       <c r="BC34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
         <v>0.18</v>
       </c>
       <c r="BD34" s="8">
-        <f t="shared" si="265"/>
+        <f t="shared" si="270"/>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="BE34" s="8">
+        <f t="shared" si="270"/>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="BF34" s="8">
+        <f t="shared" ref="BF34:BJ34" si="271">BF19/BF18</f>
         <v>0.18</v>
       </c>
-      <c r="BE34" s="8">
-        <f t="shared" si="265"/>
+      <c r="BG34" s="8">
+        <f t="shared" si="271"/>
+        <v>0.17999999999999997</v>
+      </c>
+      <c r="BH34" s="8">
+        <f t="shared" si="271"/>
         <v>0.18</v>
       </c>
-      <c r="BF34" s="8">
-        <f t="shared" ref="BF34:BJ34" si="266">BF19/BF18</f>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="BG34" s="8">
-        <f t="shared" si="266"/>
+      <c r="BI34" s="8">
+        <f t="shared" si="271"/>
         <v>0.18</v>
       </c>
-      <c r="BH34" s="8">
-        <f t="shared" si="266"/>
+      <c r="BJ34" s="8">
+        <f t="shared" si="271"/>
         <v>0.18</v>
-      </c>
-      <c r="BI34" s="8">
-        <f t="shared" si="266"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="BJ34" s="8">
-        <f t="shared" si="266"/>
-        <v>0.17999999999999997</v>
       </c>
       <c r="BL34" t="s">
         <v>48</v>
       </c>
       <c r="BM34" s="5">
         <f>BM32+BM33</f>
-        <v>139309.44886436802</v>
+        <v>165844.13440534327</v>
       </c>
     </row>
     <row r="35" spans="2:65" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="8">
+        <f>C20/C5</f>
+        <v>4.1718815185648727E-4</v>
+      </c>
+      <c r="D35" s="8">
+        <f t="shared" ref="D35:AL35" si="272">D20/D5</f>
+        <v>1.7850213426464881E-2</v>
+      </c>
+      <c r="E35" s="8">
+        <f t="shared" si="272"/>
+        <v>3.9614957423176604E-2</v>
+      </c>
+      <c r="F35" s="8">
+        <f t="shared" si="272"/>
+        <v>7.1902268760907509E-2</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.11443779108449767</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" si="272"/>
+        <v>9.1130752819262417E-2</v>
+      </c>
+      <c r="I35" s="8">
+        <f t="shared" si="272"/>
+        <v>3.0955188679245283E-2</v>
+      </c>
+      <c r="J35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.10047182903136276</v>
+      </c>
+      <c r="K35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.1048969761841049</v>
+      </c>
+      <c r="L35" s="8">
+        <f t="shared" si="272"/>
+        <v>2.276707530647986E-2</v>
+      </c>
+      <c r="M35" s="8">
+        <f t="shared" si="272"/>
+        <v>-2.415244848216264E-2</v>
+      </c>
+      <c r="N35" s="8">
+        <f t="shared" si="272"/>
+        <v>-5.1123479694908269E-2</v>
+      </c>
+      <c r="O35" s="8">
+        <f t="shared" si="272"/>
+        <v>2.0349434737923947E-2</v>
+      </c>
+      <c r="P35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.50960978450786254</v>
+      </c>
+      <c r="Q35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.20672633327182138</v>
+      </c>
+      <c r="R35" s="8">
+        <f t="shared" si="272"/>
+        <v>4.5899948427024238E-2</v>
+      </c>
+      <c r="S35" s="8">
+        <f t="shared" si="272"/>
+        <v>7.8651685393258425E-2</v>
+      </c>
+      <c r="T35" s="8">
+        <f t="shared" si="272"/>
+        <v>8.4384858044164041E-2</v>
+      </c>
+      <c r="U35" s="8">
+        <f t="shared" si="272"/>
+        <v>6.8191752877750256E-2</v>
+      </c>
+      <c r="V35" s="8">
+        <f t="shared" si="272"/>
+        <v>-3.8220038220038218E-3</v>
+      </c>
+      <c r="W35" s="8">
+        <f t="shared" si="272"/>
+        <v>3.778167588719471E-3</v>
+      </c>
+      <c r="X35" s="8">
+        <f t="shared" si="272"/>
+        <v>8.8082901554404139E-3</v>
+      </c>
+      <c r="Y35" s="8">
+        <f t="shared" si="272"/>
+        <v>2.6795967844838585E-2</v>
+      </c>
+      <c r="Z35" s="8">
+        <f t="shared" si="272"/>
+        <v>-1.1688931297709924E-2</v>
+      </c>
+      <c r="AA35" s="8">
+        <f t="shared" si="272"/>
+        <v>2.4129986661816417E-2</v>
+      </c>
+      <c r="AB35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.14727420667209112</v>
+      </c>
+      <c r="AC35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.14036697247706423</v>
+      </c>
+      <c r="AD35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.15570151825131906</v>
+      </c>
+      <c r="AE35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.16785284134457462</v>
+      </c>
+      <c r="AF35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.15324396782841823</v>
+      </c>
+      <c r="AG35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.16168996188055909</v>
+      </c>
+      <c r="AH35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.17091964375062543</v>
+      </c>
+      <c r="AI35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.15678095431885239</v>
+      </c>
+      <c r="AJ35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.18434935521688159</v>
+      </c>
+      <c r="AK35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.18120250542923608</v>
+      </c>
+      <c r="AL35" s="8">
+        <f t="shared" si="272"/>
+        <v>0.16835196562098098</v>
+      </c>
+      <c r="AR35" s="8">
+        <f t="shared" ref="AR35:BJ35" si="273">AR20/AR5</f>
+        <v>3.4155597722960153E-2</v>
+      </c>
+      <c r="AS35" s="8">
+        <f t="shared" si="273"/>
+        <v>8.3571751242282791E-2</v>
+      </c>
+      <c r="AT35" s="8">
+        <f t="shared" si="273"/>
+        <v>7.3692829570710027E-3</v>
+      </c>
+      <c r="AU35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.19160549595332205</v>
+      </c>
+      <c r="AV35" s="8">
+        <f t="shared" si="273"/>
+        <v>6.9719160501283406E-2</v>
+      </c>
+      <c r="AW35" s="8">
+        <f t="shared" si="273"/>
+        <v>6.6343454963000764E-3</v>
+      </c>
+      <c r="AX35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.11865622400091803</v>
+      </c>
+      <c r="AY35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.16353080881382767</v>
+      </c>
+      <c r="AZ35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.15439833078989376</v>
+      </c>
+      <c r="BA35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.18710703396520426</v>
+      </c>
+      <c r="BB35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.19780505375538388</v>
+      </c>
+      <c r="BC35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.19888948878374668</v>
+      </c>
+      <c r="BD35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.20076206470038849</v>
+      </c>
+      <c r="BE35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.20243134935160581</v>
+      </c>
+      <c r="BF35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.20348475748515343</v>
+      </c>
+      <c r="BG35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.20448988145983729</v>
+      </c>
+      <c r="BH35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.20547021635435242</v>
+      </c>
+      <c r="BI35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.20643710374199237</v>
+      </c>
+      <c r="BJ35" s="8">
+        <f t="shared" si="273"/>
+        <v>0.20739593839939366</v>
+      </c>
       <c r="BL35" t="s">
         <v>49</v>
       </c>
       <c r="BM35" s="11">
         <f>BM34/BE21</f>
-        <v>144.96300610236005</v>
+        <v>174.20602353502446</v>
       </c>
     </row>
     <row r="36" spans="2:65" x14ac:dyDescent="0.3">
@@ -7815,7 +8019,7 @@
       </c>
       <c r="BM36" s="11">
         <f>Main!D3</f>
-        <v>277.49</v>
+        <v>252.92</v>
       </c>
     </row>
     <row r="37" spans="2:65" x14ac:dyDescent="0.3">
@@ -7824,7 +8028,7 @@
       </c>
       <c r="BM37" s="10">
         <f>BM35/BM36-1</f>
-        <v>-0.47759196330548825</v>
+        <v>-0.31122084637425085</v>
       </c>
     </row>
     <row r="38" spans="2:65" x14ac:dyDescent="0.3">
@@ -7833,11 +8037,6 @@
       </c>
       <c r="BM38" s="6" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="2:65" x14ac:dyDescent="0.3">
-      <c r="BL40" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/CRM.xlsx
+++ b/Financial Analysis/CRM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA365E78-2AF7-4F26-BFD5-DB3E6C7A0273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D7507A-EA28-4929-AA4F-B7E98EF35AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{A12E68CC-70F9-45A5-9F33-23BEFCB58B54}"/>
   </bookViews>
@@ -155,9 +155,6 @@
     <t>Finance income</t>
   </si>
   <si>
-    <t>Finance expense</t>
-  </si>
-  <si>
     <t>Pretax profit</t>
   </si>
   <si>
@@ -230,9 +227,6 @@
     <t>G&amp;A y/y</t>
   </si>
   <si>
-    <t>Overvalued</t>
-  </si>
-  <si>
     <t>Q424</t>
   </si>
   <si>
@@ -321,6 +315,12 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Other income</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -487,13 +487,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -511,7 +511,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26974800" y="15240"/>
+          <a:off x="27713940" y="15240"/>
           <a:ext cx="0" cy="7772400"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -849,7 +849,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
@@ -860,17 +860,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="11">
-        <v>252.92</v>
+        <v>213.02</v>
       </c>
       <c r="E3" s="4">
-        <v>45909</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="4">
-        <v>46000</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -878,10 +878,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -890,7 +890,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>240779.84</v>
+        <v>201942.96000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -898,11 +898,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>10365+5007+5085</f>
-        <v>20457</v>
+        <f>8978+2345+6410</f>
+        <v>17733</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -910,11 +910,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>8436</f>
-        <v>8436</v>
+        <f>8438</f>
+        <v>8438</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>12021</v>
+        <v>9295</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -932,7 +932,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>228758.84</v>
+        <v>192647.96000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1126,16 +1126,16 @@
     </row>
     <row r="2" spans="2:62" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>11</v>
@@ -1174,64 +1174,64 @@
         <v>22</v>
       </c>
       <c r="S2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="U2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="W2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="X2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="AA2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="AB2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AA2" s="6" t="s">
+      <c r="AC2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AD2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AE2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AF2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AG2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AH2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AG2" s="6" t="s">
+      <c r="AJ2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="AH2" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AI2" s="6" t="s">
+      <c r="AK2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AJ2" s="6" t="s">
+      <c r="AL2" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="AK2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL2" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="3" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1372,12 +1372,11 @@
         <v>9690</v>
       </c>
       <c r="AK3" s="12">
-        <f>AG3*1.1</f>
-        <v>9766.9000000000015</v>
+        <v>9726</v>
       </c>
       <c r="AL3" s="12">
-        <f>AH3*1.07</f>
-        <v>10112.57</v>
+        <f>AH3*1.11</f>
+        <v>10490.61</v>
       </c>
       <c r="AM3" s="6"/>
       <c r="AN3" s="6"/>
@@ -1401,52 +1400,52 @@
       </c>
       <c r="AZ3" s="5">
         <f>SUM(AI3:AL3)</f>
-        <v>38866.47</v>
+        <v>39203.61</v>
       </c>
       <c r="BA3" s="5">
         <f>AZ3*1.06</f>
-        <v>41198.458200000001</v>
+        <v>41555.8266</v>
       </c>
       <c r="BB3" s="5">
         <f>BA3*1.05</f>
-        <v>43258.381110000002</v>
+        <v>43633.61793</v>
       </c>
       <c r="BC3" s="5">
         <f>BB3*1.03</f>
-        <v>44556.132543300002</v>
+        <v>44942.626467900001</v>
       </c>
       <c r="BD3" s="5">
         <f t="shared" ref="BD3" si="0">BC3*1.02</f>
-        <v>45447.255194166006</v>
+        <v>45841.478997258004</v>
       </c>
       <c r="BE3" s="5">
         <f t="shared" ref="BE3" si="1">BD3*1.02</f>
-        <v>46356.200298049327</v>
+        <v>46758.308577203163</v>
       </c>
       <c r="BF3" s="5">
         <f t="shared" ref="BF3" si="2">BE3*1.02</f>
-        <v>47283.324304010312</v>
+        <v>47693.474748747227</v>
       </c>
       <c r="BG3" s="5">
         <f t="shared" ref="BG3" si="3">BF3*1.02</f>
-        <v>48228.990790090516</v>
+        <v>48647.344243722175</v>
       </c>
       <c r="BH3" s="5">
         <f t="shared" ref="BH3" si="4">BG3*1.02</f>
-        <v>49193.570605892324</v>
+        <v>49620.291128596618</v>
       </c>
       <c r="BI3" s="5">
         <f t="shared" ref="BI3" si="5">BH3*1.02</f>
-        <v>50177.442018010173</v>
+        <v>50612.696951168553</v>
       </c>
       <c r="BJ3" s="5">
         <f t="shared" ref="BJ3" si="6">BI3*1.02</f>
-        <v>51180.99085837038</v>
+        <v>51624.950890191925</v>
       </c>
     </row>
     <row r="4" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -1521,12 +1520,11 @@
         <v>546</v>
       </c>
       <c r="AK4" s="12">
-        <f t="shared" ref="AK4:AL4" si="7">AG4*1.01</f>
-        <v>570.65</v>
+        <v>533</v>
       </c>
       <c r="AL4" s="12">
-        <f t="shared" si="7"/>
-        <v>547.41999999999996</v>
+        <f>AH4*1.02</f>
+        <v>552.84</v>
       </c>
       <c r="AM4" s="6"/>
       <c r="AN4" s="6"/>
@@ -1550,47 +1548,47 @@
       </c>
       <c r="AZ4" s="5">
         <f>SUM(AI4:AL4)</f>
-        <v>2196.0700000000002</v>
+        <v>2163.84</v>
       </c>
       <c r="BA4" s="5">
         <f>AZ4*1.01</f>
-        <v>2218.0307000000003</v>
+        <v>2185.4784</v>
       </c>
       <c r="BB4" s="5">
-        <f t="shared" ref="BB4:BJ4" si="8">BA4*1.01</f>
-        <v>2240.2110070000003</v>
+        <f t="shared" ref="BB4:BJ4" si="7">BA4*1.01</f>
+        <v>2207.3331840000001</v>
       </c>
       <c r="BC4" s="5">
-        <f t="shared" si="8"/>
-        <v>2262.6131170700005</v>
+        <f t="shared" si="7"/>
+        <v>2229.4065158399999</v>
       </c>
       <c r="BD4" s="5">
-        <f t="shared" si="8"/>
-        <v>2285.2392482407004</v>
+        <f t="shared" si="7"/>
+        <v>2251.7005809983998</v>
       </c>
       <c r="BE4" s="5">
-        <f t="shared" si="8"/>
-        <v>2308.0916407231075</v>
+        <f t="shared" si="7"/>
+        <v>2274.2175868083837</v>
       </c>
       <c r="BF4" s="5">
-        <f t="shared" si="8"/>
-        <v>2331.1725571303386</v>
+        <f t="shared" si="7"/>
+        <v>2296.9597626764676</v>
       </c>
       <c r="BG4" s="5">
-        <f t="shared" si="8"/>
-        <v>2354.4842827016419</v>
+        <f t="shared" si="7"/>
+        <v>2319.9293603032324</v>
       </c>
       <c r="BH4" s="5">
-        <f t="shared" si="8"/>
-        <v>2378.0291255286584</v>
+        <f t="shared" si="7"/>
+        <v>2343.1286539062648</v>
       </c>
       <c r="BI4" s="5">
-        <f t="shared" si="8"/>
-        <v>2401.8094167839449</v>
+        <f t="shared" si="7"/>
+        <v>2366.5599404453274</v>
       </c>
       <c r="BJ4" s="5">
-        <f t="shared" si="8"/>
-        <v>2425.8275109517845</v>
+        <f t="shared" si="7"/>
+        <v>2390.2255398497805</v>
       </c>
     </row>
     <row r="5" spans="2:62" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1647,84 +1645,84 @@
         <v>5817</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" ref="S5:AH5" si="9">S3+S4</f>
+        <f t="shared" ref="S5:AH5" si="8">S3+S4</f>
         <v>5963</v>
       </c>
       <c r="T5" s="9">
+        <f t="shared" si="8"/>
+        <v>6340</v>
+      </c>
+      <c r="U5" s="9">
+        <f t="shared" si="8"/>
+        <v>6863</v>
+      </c>
+      <c r="V5" s="9">
+        <f t="shared" si="8"/>
+        <v>7326</v>
+      </c>
+      <c r="W5" s="9">
+        <f t="shared" si="8"/>
+        <v>7411</v>
+      </c>
+      <c r="X5" s="9">
+        <f t="shared" si="8"/>
+        <v>7720</v>
+      </c>
+      <c r="Y5" s="9">
+        <f t="shared" si="8"/>
+        <v>7837</v>
+      </c>
+      <c r="Z5" s="9">
+        <f t="shared" si="8"/>
+        <v>8384</v>
+      </c>
+      <c r="AA5" s="9">
+        <f t="shared" si="8"/>
+        <v>8247</v>
+      </c>
+      <c r="AB5" s="9">
+        <f t="shared" si="8"/>
+        <v>8603</v>
+      </c>
+      <c r="AC5" s="9">
+        <f t="shared" si="8"/>
+        <v>8720</v>
+      </c>
+      <c r="AD5" s="9">
+        <f t="shared" si="8"/>
+        <v>9287</v>
+      </c>
+      <c r="AE5" s="9">
+        <f t="shared" si="8"/>
+        <v>9133</v>
+      </c>
+      <c r="AF5" s="9">
+        <f t="shared" si="8"/>
+        <v>9325</v>
+      </c>
+      <c r="AG5" s="9">
+        <f t="shared" si="8"/>
+        <v>9444</v>
+      </c>
+      <c r="AH5" s="9">
+        <f t="shared" si="8"/>
+        <v>9993</v>
+      </c>
+      <c r="AI5" s="9">
+        <f t="shared" ref="AI5:AL5" si="9">AI3+AI4</f>
+        <v>9829</v>
+      </c>
+      <c r="AJ5" s="9">
         <f t="shared" si="9"/>
-        <v>6340</v>
-      </c>
-      <c r="U5" s="9">
+        <v>10236</v>
+      </c>
+      <c r="AK5" s="9">
         <f t="shared" si="9"/>
-        <v>6863</v>
-      </c>
-      <c r="V5" s="9">
+        <v>10259</v>
+      </c>
+      <c r="AL5" s="9">
         <f t="shared" si="9"/>
-        <v>7326</v>
-      </c>
-      <c r="W5" s="9">
-        <f t="shared" si="9"/>
-        <v>7411</v>
-      </c>
-      <c r="X5" s="9">
-        <f t="shared" si="9"/>
-        <v>7720</v>
-      </c>
-      <c r="Y5" s="9">
-        <f t="shared" si="9"/>
-        <v>7837</v>
-      </c>
-      <c r="Z5" s="9">
-        <f t="shared" si="9"/>
-        <v>8384</v>
-      </c>
-      <c r="AA5" s="9">
-        <f t="shared" si="9"/>
-        <v>8247</v>
-      </c>
-      <c r="AB5" s="9">
-        <f t="shared" si="9"/>
-        <v>8603</v>
-      </c>
-      <c r="AC5" s="9">
-        <f t="shared" si="9"/>
-        <v>8720</v>
-      </c>
-      <c r="AD5" s="9">
-        <f t="shared" si="9"/>
-        <v>9287</v>
-      </c>
-      <c r="AE5" s="9">
-        <f t="shared" si="9"/>
-        <v>9133</v>
-      </c>
-      <c r="AF5" s="9">
-        <f t="shared" si="9"/>
-        <v>9325</v>
-      </c>
-      <c r="AG5" s="9">
-        <f t="shared" si="9"/>
-        <v>9444</v>
-      </c>
-      <c r="AH5" s="9">
-        <f t="shared" si="9"/>
-        <v>9993</v>
-      </c>
-      <c r="AI5" s="9">
-        <f t="shared" ref="AI5:AL5" si="10">AI3+AI4</f>
-        <v>9829</v>
-      </c>
-      <c r="AJ5" s="9">
-        <f t="shared" si="10"/>
-        <v>10236</v>
-      </c>
-      <c r="AK5" s="9">
-        <f t="shared" si="10"/>
-        <v>10337.550000000001</v>
-      </c>
-      <c r="AL5" s="9">
-        <f t="shared" si="10"/>
-        <v>10659.99</v>
+        <v>11043.45</v>
       </c>
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
@@ -1747,11 +1745,11 @@
         <v>21252</v>
       </c>
       <c r="AV5" s="9">
-        <f t="shared" ref="AV5:AW5" si="11">AV3+AV4</f>
+        <f t="shared" ref="AV5:AW5" si="10">AV3+AV4</f>
         <v>26492</v>
       </c>
       <c r="AW5" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>31352</v>
       </c>
       <c r="AX5" s="9">
@@ -1779,11 +1777,11 @@
         <v>45180.147012000016</v>
       </c>
       <c r="BD5" s="9">
-        <f t="shared" ref="BD5:BE5" si="12">BC5*1.03</f>
+        <f t="shared" ref="BD5:BE5" si="11">BC5*1.03</f>
         <v>46535.551422360018</v>
       </c>
       <c r="BE5" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>47931.617965030819</v>
       </c>
       <c r="BF5" s="9">
@@ -1791,25 +1789,25 @@
         <v>48890.250324331435</v>
       </c>
       <c r="BG5" s="9">
-        <f t="shared" ref="BG5:BJ5" si="13">BF5*1.02</f>
+        <f t="shared" ref="BG5:BJ5" si="12">BF5*1.02</f>
         <v>49868.055330818068</v>
       </c>
       <c r="BH5" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>50865.416437434433</v>
       </c>
       <c r="BI5" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>51882.724766183121</v>
       </c>
       <c r="BJ5" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>52920.379261506787</v>
       </c>
     </row>
     <row r="6" spans="2:62" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1884,12 +1882,11 @@
         <v>1645</v>
       </c>
       <c r="AK6" s="5">
-        <f t="shared" ref="AK6:AL6" si="14">AK3*0.17</f>
-        <v>1660.3730000000003</v>
+        <v>1665</v>
       </c>
       <c r="AL6" s="5">
-        <f t="shared" si="14"/>
-        <v>1719.1369</v>
+        <f t="shared" ref="AL6" si="13">AL3*0.17</f>
+        <v>1783.4037000000003</v>
       </c>
       <c r="AM6" s="9"/>
       <c r="AN6" s="9"/>
@@ -1917,7 +1914,7 @@
       </c>
       <c r="AZ6" s="5">
         <f>SUM(AI6:AL6)</f>
-        <v>6635.5099000000009</v>
+        <v>6704.4037000000008</v>
       </c>
       <c r="BA6" s="9"/>
       <c r="BB6" s="9"/>
@@ -1932,7 +1929,7 @@
     </row>
     <row r="7" spans="2:62" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -2007,12 +2004,11 @@
         <v>597</v>
       </c>
       <c r="AK7" s="5">
-        <f>AK4*1.08</f>
-        <v>616.30200000000002</v>
+        <v>590</v>
       </c>
       <c r="AL7" s="5">
-        <f t="shared" ref="AL7" si="15">AL4*1.15</f>
-        <v>629.5329999999999</v>
+        <f t="shared" ref="AL7" si="14">AL4*1.15</f>
+        <v>635.76599999999996</v>
       </c>
       <c r="AM7" s="9"/>
       <c r="AN7" s="9"/>
@@ -2040,7 +2036,7 @@
       </c>
       <c r="AZ7" s="5">
         <f>SUM(AI7:AL7)</f>
-        <v>2496.835</v>
+        <v>2476.7660000000001</v>
       </c>
       <c r="BA7" s="9"/>
       <c r="BB7" s="9"/>
@@ -2107,84 +2103,84 @@
         <v>1479</v>
       </c>
       <c r="S8" s="5">
-        <f t="shared" ref="S8:AH8" si="16">S6+S7</f>
+        <f t="shared" ref="S8:AH8" si="15">S6+S7</f>
         <v>1555</v>
       </c>
       <c r="T8" s="5">
+        <f t="shared" si="15"/>
+        <v>1613</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" si="15"/>
+        <v>1844</v>
+      </c>
+      <c r="V8" s="5">
+        <f t="shared" si="15"/>
+        <v>2014</v>
+      </c>
+      <c r="W8" s="5">
+        <f t="shared" si="15"/>
+        <v>2045</v>
+      </c>
+      <c r="X8" s="5">
+        <f t="shared" si="15"/>
+        <v>2127</v>
+      </c>
+      <c r="Y8" s="5">
+        <f t="shared" si="15"/>
+        <v>2088</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" si="15"/>
+        <v>2100</v>
+      </c>
+      <c r="AA8" s="5">
+        <f t="shared" si="15"/>
+        <v>2125</v>
+      </c>
+      <c r="AB8" s="5">
+        <f t="shared" si="15"/>
+        <v>2113</v>
+      </c>
+      <c r="AC8" s="5">
+        <f t="shared" si="15"/>
+        <v>2155</v>
+      </c>
+      <c r="AD8" s="5">
+        <f t="shared" si="15"/>
+        <v>2148</v>
+      </c>
+      <c r="AE8" s="5">
+        <f t="shared" si="15"/>
+        <v>2162</v>
+      </c>
+      <c r="AF8" s="5">
+        <f t="shared" si="15"/>
+        <v>2159</v>
+      </c>
+      <c r="AG8" s="5">
+        <f t="shared" si="15"/>
+        <v>2105</v>
+      </c>
+      <c r="AH8" s="5">
+        <f t="shared" si="15"/>
+        <v>2217</v>
+      </c>
+      <c r="AI8" s="5">
+        <f t="shared" ref="AI8:AL8" si="16">AI6+AI7</f>
+        <v>2265</v>
+      </c>
+      <c r="AJ8" s="5">
         <f t="shared" si="16"/>
-        <v>1613</v>
-      </c>
-      <c r="U8" s="5">
+        <v>2242</v>
+      </c>
+      <c r="AK8" s="5">
         <f t="shared" si="16"/>
-        <v>1844</v>
-      </c>
-      <c r="V8" s="5">
+        <v>2255</v>
+      </c>
+      <c r="AL8" s="5">
         <f t="shared" si="16"/>
-        <v>2014</v>
-      </c>
-      <c r="W8" s="5">
-        <f t="shared" si="16"/>
-        <v>2045</v>
-      </c>
-      <c r="X8" s="5">
-        <f t="shared" si="16"/>
-        <v>2127</v>
-      </c>
-      <c r="Y8" s="5">
-        <f t="shared" si="16"/>
-        <v>2088</v>
-      </c>
-      <c r="Z8" s="5">
-        <f t="shared" si="16"/>
-        <v>2100</v>
-      </c>
-      <c r="AA8" s="5">
-        <f t="shared" si="16"/>
-        <v>2125</v>
-      </c>
-      <c r="AB8" s="5">
-        <f t="shared" si="16"/>
-        <v>2113</v>
-      </c>
-      <c r="AC8" s="5">
-        <f t="shared" si="16"/>
-        <v>2155</v>
-      </c>
-      <c r="AD8" s="5">
-        <f t="shared" si="16"/>
-        <v>2148</v>
-      </c>
-      <c r="AE8" s="5">
-        <f t="shared" si="16"/>
-        <v>2162</v>
-      </c>
-      <c r="AF8" s="5">
-        <f t="shared" si="16"/>
-        <v>2159</v>
-      </c>
-      <c r="AG8" s="5">
-        <f t="shared" si="16"/>
-        <v>2105</v>
-      </c>
-      <c r="AH8" s="5">
-        <f t="shared" si="16"/>
-        <v>2217</v>
-      </c>
-      <c r="AI8" s="5">
-        <f t="shared" ref="AI8:AL8" si="17">AI6+AI7</f>
-        <v>2265</v>
-      </c>
-      <c r="AJ8" s="5">
-        <f t="shared" si="17"/>
-        <v>2242</v>
-      </c>
-      <c r="AK8" s="5">
-        <f t="shared" si="17"/>
-        <v>2276.6750000000002</v>
-      </c>
-      <c r="AL8" s="5">
-        <f t="shared" si="17"/>
-        <v>2348.6698999999999</v>
+        <v>2419.1697000000004</v>
       </c>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
@@ -2224,47 +2220,47 @@
       </c>
       <c r="AZ8" s="5">
         <f>AZ6+AZ7</f>
-        <v>9132.3449000000001</v>
+        <v>9181.1697000000004</v>
       </c>
       <c r="BA8" s="5">
-        <f t="shared" ref="BA8:BE8" si="18">BA5-BA9</f>
-        <v>9278.9697000000015</v>
+        <f t="shared" ref="BA8:BE8" si="17">BA5-BA9</f>
+        <v>9700.7410500000005</v>
       </c>
       <c r="BB8" s="5">
+        <f t="shared" si="17"/>
+        <v>10088.770692000006</v>
+      </c>
+      <c r="BC8" s="5">
+        <f t="shared" si="17"/>
+        <v>10391.433812760006</v>
+      </c>
+      <c r="BD8" s="5">
+        <f t="shared" si="17"/>
+        <v>10703.176827142801</v>
+      </c>
+      <c r="BE8" s="5">
+        <f t="shared" si="17"/>
+        <v>11024.272131957085</v>
+      </c>
+      <c r="BF8" s="5">
+        <f t="shared" ref="BF8:BJ8" si="18">BF5-BF9</f>
+        <v>11244.757574596231</v>
+      </c>
+      <c r="BG8" s="5">
         <f t="shared" si="18"/>
-        <v>9650.1284880000021</v>
-      </c>
-      <c r="BC8" s="5">
+        <v>11469.652726088156</v>
+      </c>
+      <c r="BH8" s="5">
         <f t="shared" si="18"/>
-        <v>9939.6323426400049</v>
-      </c>
-      <c r="BD8" s="5">
+        <v>11699.045780609922</v>
+      </c>
+      <c r="BI8" s="5">
         <f t="shared" si="18"/>
-        <v>10237.821312919201</v>
-      </c>
-      <c r="BE8" s="5">
+        <v>11933.026696222114</v>
+      </c>
+      <c r="BJ8" s="5">
         <f t="shared" si="18"/>
-        <v>10544.95595230678</v>
-      </c>
-      <c r="BF8" s="5">
-        <f t="shared" ref="BF8:BJ8" si="19">BF5-BF9</f>
-        <v>10755.855071352911</v>
-      </c>
-      <c r="BG8" s="5">
-        <f t="shared" si="19"/>
-        <v>10970.972172779977</v>
-      </c>
-      <c r="BH8" s="5">
-        <f t="shared" si="19"/>
-        <v>11190.391616235574</v>
-      </c>
-      <c r="BI8" s="5">
-        <f t="shared" si="19"/>
-        <v>11414.199448560285</v>
-      </c>
-      <c r="BJ8" s="5">
-        <f t="shared" si="19"/>
-        <v>11642.483437531489</v>
+        <v>12171.687230146563</v>
       </c>
     </row>
     <row r="9" spans="2:62" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2272,59 +2268,59 @@
         <v>24</v>
       </c>
       <c r="C9" s="9">
-        <f t="shared" ref="C9:S9" si="20">C5-C8</f>
+        <f t="shared" ref="C9:S9" si="19">C5-C8</f>
         <v>1746</v>
       </c>
       <c r="D9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1907</v>
       </c>
       <c r="E9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1987</v>
       </c>
       <c r="F9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2127</v>
       </c>
       <c r="G9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2239</v>
       </c>
       <c r="H9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2432</v>
       </c>
       <c r="I9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2503</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2657</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2823</v>
       </c>
       <c r="L9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3030</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3379</v>
       </c>
       <c r="N9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3631</v>
       </c>
       <c r="O9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3611</v>
       </c>
       <c r="P9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3840</v>
       </c>
       <c r="Q9" s="9">
@@ -2332,88 +2328,88 @@
         <v>4064.25</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>4338</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>4408</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" ref="T9" si="21">T5-T8</f>
+        <f t="shared" ref="T9" si="20">T5-T8</f>
         <v>4727</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" ref="U9" si="22">U5-U8</f>
+        <f t="shared" ref="U9" si="21">U5-U8</f>
         <v>5019</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" ref="V9:W9" si="23">V5-V8</f>
+        <f t="shared" ref="V9:W9" si="22">V5-V8</f>
         <v>5312</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>5366</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" ref="X9" si="24">X5-X8</f>
+        <f t="shared" ref="X9" si="23">X5-X8</f>
         <v>5593</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" ref="Y9" si="25">Y5-Y8</f>
+        <f t="shared" ref="Y9" si="24">Y5-Y8</f>
         <v>5749</v>
       </c>
       <c r="Z9" s="9">
-        <f t="shared" ref="Z9:AA9" si="26">Z5-Z8</f>
+        <f t="shared" ref="Z9:AA9" si="25">Z5-Z8</f>
         <v>6284</v>
       </c>
       <c r="AA9" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>6122</v>
       </c>
       <c r="AB9" s="9">
-        <f t="shared" ref="AB9" si="27">AB5-AB8</f>
+        <f t="shared" ref="AB9" si="26">AB5-AB8</f>
         <v>6490</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" ref="AC9" si="28">AC5-AC8</f>
+        <f t="shared" ref="AC9" si="27">AC5-AC8</f>
         <v>6565</v>
       </c>
       <c r="AD9" s="9">
-        <f t="shared" ref="AD9:AE9" si="29">AD5-AD8</f>
+        <f t="shared" ref="AD9:AE9" si="28">AD5-AD8</f>
         <v>7139</v>
       </c>
       <c r="AE9" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>6971</v>
       </c>
       <c r="AF9" s="9">
-        <f t="shared" ref="AF9" si="30">AF5-AF8</f>
+        <f t="shared" ref="AF9" si="29">AF5-AF8</f>
         <v>7166</v>
       </c>
       <c r="AG9" s="9">
-        <f t="shared" ref="AG9" si="31">AG5-AG8</f>
+        <f t="shared" ref="AG9" si="30">AG5-AG8</f>
         <v>7339</v>
       </c>
       <c r="AH9" s="9">
-        <f t="shared" ref="AH9:AL9" si="32">AH5-AH8</f>
+        <f t="shared" ref="AH9:AL9" si="31">AH5-AH8</f>
         <v>7776</v>
       </c>
       <c r="AI9" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>7564</v>
       </c>
       <c r="AJ9" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>7994</v>
       </c>
       <c r="AK9" s="9">
-        <f t="shared" si="32"/>
-        <v>8060.8750000000009</v>
+        <f t="shared" si="31"/>
+        <v>8004</v>
       </c>
       <c r="AL9" s="9">
-        <f t="shared" si="32"/>
-        <v>8311.3201000000008</v>
+        <f t="shared" si="31"/>
+        <v>8624.2803000000004</v>
       </c>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
@@ -2452,48 +2448,48 @@
         <v>29252</v>
       </c>
       <c r="AZ9" s="9">
-        <f t="shared" ref="AZ9" si="33">AZ5-AZ8</f>
-        <v>31036.355100000004</v>
+        <f t="shared" ref="AZ9" si="32">AZ5-AZ8</f>
+        <v>30987.530300000006</v>
       </c>
       <c r="BA9" s="9">
-        <f>BA5*0.78</f>
-        <v>32898.165300000008</v>
+        <f>BA5*0.77</f>
+        <v>32476.393950000009</v>
       </c>
       <c r="BB9" s="9">
-        <f t="shared" ref="BB9:BJ9" si="34">BB5*0.78</f>
-        <v>34214.091912000011</v>
+        <f t="shared" ref="BB9:BJ9" si="33">BB5*0.77</f>
+        <v>33775.449708000007</v>
       </c>
       <c r="BC9" s="9">
-        <f t="shared" si="34"/>
-        <v>35240.514669360011</v>
+        <f t="shared" si="33"/>
+        <v>34788.71319924001</v>
       </c>
       <c r="BD9" s="9">
-        <f t="shared" si="34"/>
-        <v>36297.730109440818</v>
+        <f t="shared" si="33"/>
+        <v>35832.374595217218</v>
       </c>
       <c r="BE9" s="9">
-        <f t="shared" si="34"/>
-        <v>37386.662012724039</v>
+        <f t="shared" si="33"/>
+        <v>36907.345833073734</v>
       </c>
       <c r="BF9" s="9">
-        <f t="shared" si="34"/>
-        <v>38134.395252978524</v>
+        <f t="shared" si="33"/>
+        <v>37645.492749735204</v>
       </c>
       <c r="BG9" s="9">
-        <f t="shared" si="34"/>
-        <v>38897.083158038091</v>
+        <f t="shared" si="33"/>
+        <v>38398.402604729912</v>
       </c>
       <c r="BH9" s="9">
-        <f t="shared" si="34"/>
-        <v>39675.024821198858</v>
+        <f t="shared" si="33"/>
+        <v>39166.370656824511</v>
       </c>
       <c r="BI9" s="9">
-        <f t="shared" si="34"/>
-        <v>40468.525317622836</v>
+        <f t="shared" si="33"/>
+        <v>39949.698069961007</v>
       </c>
       <c r="BJ9" s="9">
-        <f t="shared" si="34"/>
-        <v>41277.895823975297</v>
+        <f t="shared" si="33"/>
+        <v>40748.692031360224</v>
       </c>
     </row>
     <row r="10" spans="2:62" x14ac:dyDescent="0.3">
@@ -2603,12 +2599,11 @@
         <v>1481</v>
       </c>
       <c r="AK10" s="5">
-        <f>AG10*1.11</f>
-        <v>1505.16</v>
+        <v>1433</v>
       </c>
       <c r="AL10" s="5">
-        <f>AH10*1.07</f>
-        <v>1519.4</v>
+        <f>AH10*1.05</f>
+        <v>1491</v>
       </c>
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
@@ -2648,47 +2643,47 @@
       </c>
       <c r="AZ10" s="5">
         <f>SUM(AI10:AL10)</f>
-        <v>5965.5599999999995</v>
+        <v>5865</v>
       </c>
       <c r="BA10" s="5">
         <f>AZ10*1.06</f>
-        <v>6323.4935999999998</v>
+        <v>6216.9000000000005</v>
       </c>
       <c r="BB10" s="5">
         <f>BA10*1.04</f>
-        <v>6576.433344</v>
+        <v>6465.5760000000009</v>
       </c>
       <c r="BC10" s="5">
-        <f t="shared" ref="BC10" si="35">BB10*1.03</f>
-        <v>6773.72634432</v>
+        <f t="shared" ref="BC10" si="34">BB10*1.03</f>
+        <v>6659.5432800000008</v>
       </c>
       <c r="BD10" s="5">
         <f>BC10*1.02</f>
-        <v>6909.2008712063998</v>
+        <v>6792.7341456000013</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10*1.02</f>
-        <v>7047.3848886305277</v>
+        <v>6928.5888285120018</v>
       </c>
       <c r="BF10" s="5">
         <f>BE10*1.01</f>
-        <v>7117.8587375168327</v>
+        <v>6997.8747167971214</v>
       </c>
       <c r="BG10" s="5">
-        <f t="shared" ref="BG10:BJ10" si="36">BF10*1.01</f>
-        <v>7189.0373248920014</v>
+        <f t="shared" ref="BG10:BJ10" si="35">BF10*1.01</f>
+        <v>7067.8534639650925</v>
       </c>
       <c r="BH10" s="5">
-        <f t="shared" si="36"/>
-        <v>7260.9276981409212</v>
+        <f t="shared" si="35"/>
+        <v>7138.5319986047434</v>
       </c>
       <c r="BI10" s="5">
-        <f t="shared" si="36"/>
-        <v>7333.5369751223307</v>
+        <f t="shared" si="35"/>
+        <v>7209.9173185907912</v>
       </c>
       <c r="BJ10" s="5">
-        <f t="shared" si="36"/>
-        <v>7406.8723448735536</v>
+        <f t="shared" si="35"/>
+        <v>7282.0164917766988</v>
       </c>
     </row>
     <row r="11" spans="2:62" x14ac:dyDescent="0.3">
@@ -2799,12 +2794,11 @@
         <v>3443</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" ref="AK11:AL11" si="37">AK5*0.34</f>
-        <v>3514.7670000000007</v>
+        <v>3456</v>
       </c>
       <c r="AL11" s="5">
-        <f t="shared" si="37"/>
-        <v>3624.3966</v>
+        <f t="shared" ref="AL11" si="36">AL5*0.34</f>
+        <v>3754.7730000000006</v>
       </c>
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
@@ -2844,47 +2838,47 @@
       </c>
       <c r="AZ11" s="5">
         <f>SUM(AI11:AL11)</f>
-        <v>14011.1636</v>
+        <v>14082.773000000001</v>
       </c>
       <c r="BA11" s="5">
-        <f>BA5*0.33</f>
-        <v>13918.454550000004</v>
+        <f>BA5*0.34</f>
+        <v>14340.225900000005</v>
       </c>
       <c r="BB11" s="5">
-        <f>BB5*0.32</f>
-        <v>14036.550528000005</v>
+        <f>BB5*0.33</f>
+        <v>14475.192732000005</v>
       </c>
       <c r="BC11" s="5">
-        <f>BC5*0.32</f>
-        <v>14457.647043840005</v>
+        <f t="shared" ref="BC11:BJ11" si="37">BC5*0.33</f>
+        <v>14909.448513960006</v>
       </c>
       <c r="BD11" s="5">
-        <f t="shared" ref="BD11:BJ11" si="38">BD5*0.32</f>
-        <v>14891.376455155207</v>
+        <f t="shared" si="37"/>
+        <v>15356.731969378807</v>
       </c>
       <c r="BE11" s="5">
-        <f t="shared" si="38"/>
-        <v>15338.117748809862</v>
+        <f t="shared" si="37"/>
+        <v>15817.43392846017</v>
       </c>
       <c r="BF11" s="5">
-        <f t="shared" si="38"/>
-        <v>15644.880103786059</v>
+        <f t="shared" si="37"/>
+        <v>16133.782607029374</v>
       </c>
       <c r="BG11" s="5">
-        <f t="shared" si="38"/>
-        <v>15957.777705861781</v>
+        <f t="shared" si="37"/>
+        <v>16456.458259169962</v>
       </c>
       <c r="BH11" s="5">
-        <f t="shared" si="38"/>
-        <v>16276.93325997902</v>
+        <f t="shared" si="37"/>
+        <v>16785.587424353365</v>
       </c>
       <c r="BI11" s="5">
-        <f t="shared" si="38"/>
-        <v>16602.471925178597</v>
+        <f t="shared" si="37"/>
+        <v>17121.29917284043</v>
       </c>
       <c r="BJ11" s="5">
-        <f t="shared" si="38"/>
-        <v>16934.521363682172</v>
+        <f t="shared" si="37"/>
+        <v>17463.725156297241</v>
       </c>
     </row>
     <row r="12" spans="2:62" x14ac:dyDescent="0.3">
@@ -2994,12 +2988,11 @@
         <v>734</v>
       </c>
       <c r="AK12" s="5">
-        <f>AG12*1.07</f>
-        <v>760.7700000000001</v>
+        <v>667</v>
       </c>
       <c r="AL12" s="5">
-        <f>AH12*1.05</f>
-        <v>805.35</v>
+        <f>AH12*0.98</f>
+        <v>751.66</v>
       </c>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
@@ -3039,52 +3032,52 @@
       </c>
       <c r="AZ12" s="5">
         <f>SUM(AI12:AL12)</f>
-        <v>2997.12</v>
+        <v>2849.66</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" ref="BA12" si="39">AZ12*1.03</f>
-        <v>3087.0335999999998</v>
+        <f t="shared" ref="BA12" si="38">AZ12*1.03</f>
+        <v>2935.1498000000001</v>
       </c>
       <c r="BB12" s="5">
         <f>BA12*1.02</f>
-        <v>3148.7742719999997</v>
+        <v>2993.8527960000001</v>
       </c>
       <c r="BC12" s="5">
         <f>BB12*1.02</f>
-        <v>3211.7497574399995</v>
+        <v>3053.7298519200003</v>
       </c>
       <c r="BD12" s="5">
-        <f t="shared" ref="BD12:BE12" si="40">BC12*1.02</f>
-        <v>3275.9847525887994</v>
+        <f t="shared" ref="BD12:BE12" si="39">BC12*1.02</f>
+        <v>3114.8044489584004</v>
       </c>
       <c r="BE12" s="5">
-        <f t="shared" si="40"/>
-        <v>3341.5044476405756</v>
+        <f t="shared" si="39"/>
+        <v>3177.1005379375683</v>
       </c>
       <c r="BF12" s="5">
-        <f t="shared" ref="BF12" si="41">BE12*1.02</f>
-        <v>3408.3345365933869</v>
+        <f t="shared" ref="BF12" si="40">BE12*1.02</f>
+        <v>3240.6425486963199</v>
       </c>
       <c r="BG12" s="5">
-        <f t="shared" ref="BG12" si="42">BF12*1.02</f>
-        <v>3476.5012273252546</v>
+        <f t="shared" ref="BG12" si="41">BF12*1.02</f>
+        <v>3305.4553996702462</v>
       </c>
       <c r="BH12" s="5">
-        <f t="shared" ref="BH12" si="43">BG12*1.02</f>
-        <v>3546.0312518717597</v>
+        <f t="shared" ref="BH12" si="42">BG12*1.02</f>
+        <v>3371.5645076636511</v>
       </c>
       <c r="BI12" s="5">
-        <f t="shared" ref="BI12" si="44">BH12*1.02</f>
-        <v>3616.9518769091951</v>
+        <f t="shared" ref="BI12" si="43">BH12*1.02</f>
+        <v>3438.9957978169241</v>
       </c>
       <c r="BJ12" s="5">
-        <f t="shared" ref="BJ12" si="45">BI12*1.02</f>
-        <v>3689.2909144473792</v>
+        <f t="shared" ref="BJ12" si="44">BI12*1.02</f>
+        <v>3507.7757137732629</v>
       </c>
     </row>
     <row r="13" spans="2:62" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -3157,12 +3150,10 @@
         <v>4</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" ref="AK13" si="46">AG13*1.05</f>
-        <v>58.800000000000004</v>
+        <v>260</v>
       </c>
       <c r="AL13" s="5">
-        <f>AH13*0.8</f>
-        <v>238.4</v>
+        <v>50</v>
       </c>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
@@ -3190,47 +3181,47 @@
       </c>
       <c r="AZ13" s="5">
         <f>SUM(AI13:AL13)</f>
-        <v>337.20000000000005</v>
+        <v>350</v>
       </c>
       <c r="BA13" s="5">
-        <f t="shared" ref="BA13:BE13" si="47">AZ13*0.5</f>
-        <v>168.60000000000002</v>
+        <f t="shared" ref="BA13:BE13" si="45">AZ13*0.5</f>
+        <v>175</v>
       </c>
       <c r="BB13" s="5">
-        <f t="shared" si="47"/>
-        <v>84.300000000000011</v>
+        <f t="shared" si="45"/>
+        <v>87.5</v>
       </c>
       <c r="BC13" s="5">
-        <f t="shared" si="47"/>
-        <v>42.150000000000006</v>
+        <f t="shared" si="45"/>
+        <v>43.75</v>
       </c>
       <c r="BD13" s="5">
-        <f t="shared" si="47"/>
-        <v>21.075000000000003</v>
+        <f t="shared" si="45"/>
+        <v>21.875</v>
       </c>
       <c r="BE13" s="5">
-        <f t="shared" si="47"/>
-        <v>10.537500000000001</v>
+        <f t="shared" si="45"/>
+        <v>10.9375</v>
       </c>
       <c r="BF13" s="5">
-        <f t="shared" ref="BF13:BJ13" si="48">BE13*0.5</f>
-        <v>5.2687500000000007</v>
+        <f t="shared" ref="BF13:BJ13" si="46">BE13*0.5</f>
+        <v>5.46875</v>
       </c>
       <c r="BG13" s="5">
-        <f t="shared" si="48"/>
-        <v>2.6343750000000004</v>
+        <f t="shared" si="46"/>
+        <v>2.734375</v>
       </c>
       <c r="BH13" s="5">
-        <f t="shared" si="48"/>
-        <v>1.3171875000000002</v>
+        <f t="shared" si="46"/>
+        <v>1.3671875</v>
       </c>
       <c r="BI13" s="5">
-        <f t="shared" si="48"/>
-        <v>0.65859375000000009</v>
+        <f t="shared" si="46"/>
+        <v>0.68359375</v>
       </c>
       <c r="BJ13" s="5">
-        <f t="shared" si="48"/>
-        <v>0.32929687500000004</v>
+        <f t="shared" si="46"/>
+        <v>0.341796875</v>
       </c>
     </row>
     <row r="14" spans="2:62" x14ac:dyDescent="0.3">
@@ -3238,148 +3229,148 @@
         <v>28</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" ref="C14:P14" si="49">SUM(C10:C12)</f>
+        <f t="shared" ref="C14:P14" si="47">SUM(C10:C12)</f>
         <v>1742</v>
       </c>
       <c r="D14" s="5">
+        <f t="shared" si="47"/>
+        <v>1823</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="47"/>
+        <v>1832</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="47"/>
+        <v>1916</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="47"/>
+        <v>2048</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="47"/>
+        <v>2317</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="47"/>
+        <v>2411</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="47"/>
+        <v>2520</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="47"/>
+        <v>2613</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="47"/>
+        <v>2972</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" si="47"/>
+        <v>3314</v>
+      </c>
+      <c r="N14" s="5">
+        <f t="shared" si="47"/>
+        <v>3667</v>
+      </c>
+      <c r="O14" s="5">
+        <f t="shared" si="47"/>
+        <v>3751</v>
+      </c>
+      <c r="P14" s="5">
+        <f t="shared" si="47"/>
+        <v>3662</v>
+      </c>
+      <c r="Q14" s="5">
+        <f t="shared" ref="Q14:R14" si="48">SUM(Q10:Q12)</f>
+        <v>3801</v>
+      </c>
+      <c r="R14" s="5">
+        <f t="shared" si="48"/>
+        <v>4145</v>
+      </c>
+      <c r="S14" s="5">
+        <f t="shared" ref="S14:AH14" si="49">SUM(S10:S13)</f>
+        <v>4054</v>
+      </c>
+      <c r="T14" s="5">
         <f t="shared" si="49"/>
-        <v>1823</v>
-      </c>
-      <c r="E14" s="5">
+        <v>4395</v>
+      </c>
+      <c r="U14" s="5">
         <f t="shared" si="49"/>
-        <v>1832</v>
-      </c>
-      <c r="F14" s="5">
+        <v>4981</v>
+      </c>
+      <c r="V14" s="5">
         <f t="shared" si="49"/>
-        <v>1916</v>
-      </c>
-      <c r="G14" s="5">
+        <v>5488</v>
+      </c>
+      <c r="W14" s="5">
         <f t="shared" si="49"/>
-        <v>2048</v>
-      </c>
-      <c r="H14" s="5">
+        <v>5346</v>
+      </c>
+      <c r="X14" s="5">
         <f t="shared" si="49"/>
-        <v>2317</v>
-      </c>
-      <c r="I14" s="5">
+        <v>5400</v>
+      </c>
+      <c r="Y14" s="5">
         <f t="shared" si="49"/>
-        <v>2411</v>
-      </c>
-      <c r="J14" s="5">
+        <v>5289</v>
+      </c>
+      <c r="Z14" s="5">
         <f t="shared" si="49"/>
-        <v>2520</v>
-      </c>
-      <c r="K14" s="5">
+        <v>5927</v>
+      </c>
+      <c r="AA14" s="5">
         <f t="shared" si="49"/>
-        <v>2613</v>
-      </c>
-      <c r="L14" s="5">
+        <v>5710</v>
+      </c>
+      <c r="AB14" s="5">
         <f t="shared" si="49"/>
-        <v>2972</v>
-      </c>
-      <c r="M14" s="5">
+        <v>5014</v>
+      </c>
+      <c r="AC14" s="5">
         <f t="shared" si="49"/>
-        <v>3314</v>
-      </c>
-      <c r="N14" s="5">
+        <v>5064</v>
+      </c>
+      <c r="AD14" s="5">
         <f t="shared" si="49"/>
-        <v>3667</v>
-      </c>
-      <c r="O14" s="5">
+        <v>5517</v>
+      </c>
+      <c r="AE14" s="5">
         <f t="shared" si="49"/>
-        <v>3751</v>
-      </c>
-      <c r="P14" s="5">
+        <v>5262</v>
+      </c>
+      <c r="AF14" s="5">
         <f t="shared" si="49"/>
-        <v>3662</v>
-      </c>
-      <c r="Q14" s="5">
-        <f t="shared" ref="Q14:R14" si="50">SUM(Q10:Q12)</f>
-        <v>3801</v>
-      </c>
-      <c r="R14" s="5">
+        <v>5383</v>
+      </c>
+      <c r="AG14" s="5">
+        <f t="shared" si="49"/>
+        <v>5446</v>
+      </c>
+      <c r="AH14" s="5">
+        <f t="shared" si="49"/>
+        <v>5956</v>
+      </c>
+      <c r="AI14" s="5">
+        <f t="shared" ref="AI14:AL14" si="50">SUM(AI10:AI13)</f>
+        <v>5622</v>
+      </c>
+      <c r="AJ14" s="5">
         <f t="shared" si="50"/>
-        <v>4145</v>
-      </c>
-      <c r="S14" s="5">
-        <f t="shared" ref="S14:AH14" si="51">SUM(S10:S13)</f>
-        <v>4054</v>
-      </c>
-      <c r="T14" s="5">
-        <f t="shared" si="51"/>
-        <v>4395</v>
-      </c>
-      <c r="U14" s="5">
-        <f t="shared" si="51"/>
-        <v>4981</v>
-      </c>
-      <c r="V14" s="5">
-        <f t="shared" si="51"/>
-        <v>5488</v>
-      </c>
-      <c r="W14" s="5">
-        <f t="shared" si="51"/>
-        <v>5346</v>
-      </c>
-      <c r="X14" s="5">
-        <f t="shared" si="51"/>
-        <v>5400</v>
-      </c>
-      <c r="Y14" s="5">
-        <f t="shared" si="51"/>
-        <v>5289</v>
-      </c>
-      <c r="Z14" s="5">
-        <f t="shared" si="51"/>
-        <v>5927</v>
-      </c>
-      <c r="AA14" s="5">
-        <f t="shared" si="51"/>
-        <v>5710</v>
-      </c>
-      <c r="AB14" s="5">
-        <f t="shared" si="51"/>
-        <v>5014</v>
-      </c>
-      <c r="AC14" s="5">
-        <f t="shared" si="51"/>
-        <v>5064</v>
-      </c>
-      <c r="AD14" s="5">
-        <f t="shared" si="51"/>
-        <v>5517</v>
-      </c>
-      <c r="AE14" s="5">
-        <f t="shared" si="51"/>
-        <v>5262</v>
-      </c>
-      <c r="AF14" s="5">
-        <f t="shared" si="51"/>
-        <v>5383</v>
-      </c>
-      <c r="AG14" s="5">
-        <f t="shared" si="51"/>
-        <v>5446</v>
-      </c>
-      <c r="AH14" s="5">
-        <f t="shared" si="51"/>
-        <v>5956</v>
-      </c>
-      <c r="AI14" s="5">
-        <f t="shared" ref="AI14:AL14" si="52">SUM(AI10:AI13)</f>
-        <v>5622</v>
-      </c>
-      <c r="AJ14" s="5">
-        <f t="shared" si="52"/>
         <v>5662</v>
       </c>
       <c r="AK14" s="5">
-        <f t="shared" si="52"/>
-        <v>5839.4970000000012</v>
+        <f t="shared" si="50"/>
+        <v>5816</v>
       </c>
       <c r="AL14" s="5">
-        <f t="shared" si="52"/>
-        <v>6187.5465999999997</v>
+        <f t="shared" si="50"/>
+        <v>6047.4330000000009</v>
       </c>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
@@ -3406,60 +3397,60 @@
         <v>18918</v>
       </c>
       <c r="AW14" s="5">
-        <f t="shared" ref="AW14:BE14" si="53">SUM(AW10:AW13)</f>
+        <f t="shared" ref="AW14:BE14" si="51">SUM(AW10:AW13)</f>
         <v>21962</v>
       </c>
       <c r="AX14" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>21305</v>
       </c>
       <c r="AY14" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>22047</v>
       </c>
       <c r="AZ14" s="5">
-        <f t="shared" si="53"/>
-        <v>23311.043599999997</v>
+        <f t="shared" si="51"/>
+        <v>23147.433000000001</v>
       </c>
       <c r="BA14" s="5">
-        <f t="shared" si="53"/>
-        <v>23497.581750000001</v>
+        <f t="shared" si="51"/>
+        <v>23667.275700000006</v>
       </c>
       <c r="BB14" s="5">
-        <f t="shared" si="53"/>
-        <v>23846.058144000002</v>
+        <f t="shared" si="51"/>
+        <v>24022.121528000003</v>
       </c>
       <c r="BC14" s="5">
-        <f t="shared" si="53"/>
-        <v>24485.273145600007</v>
+        <f t="shared" si="51"/>
+        <v>24666.471645880007</v>
       </c>
       <c r="BD14" s="5">
-        <f t="shared" si="53"/>
-        <v>25097.637078950407</v>
+        <f t="shared" si="51"/>
+        <v>25286.145563937207</v>
       </c>
       <c r="BE14" s="5">
-        <f t="shared" si="53"/>
-        <v>25737.544585080963</v>
+        <f t="shared" si="51"/>
+        <v>25934.060794909739</v>
       </c>
       <c r="BF14" s="5">
-        <f t="shared" ref="BF14" si="54">SUM(BF10:BF13)</f>
-        <v>26176.342127896278</v>
+        <f t="shared" ref="BF14" si="52">SUM(BF10:BF13)</f>
+        <v>26377.768622522817</v>
       </c>
       <c r="BG14" s="5">
-        <f t="shared" ref="BG14" si="55">SUM(BG10:BG13)</f>
-        <v>26625.950633079039</v>
+        <f t="shared" ref="BG14" si="53">SUM(BG10:BG13)</f>
+        <v>26832.5014978053</v>
       </c>
       <c r="BH14" s="5">
-        <f t="shared" ref="BH14" si="56">SUM(BH10:BH13)</f>
-        <v>27085.209397491701</v>
+        <f t="shared" ref="BH14" si="54">SUM(BH10:BH13)</f>
+        <v>27297.051118121759</v>
       </c>
       <c r="BI14" s="5">
-        <f t="shared" ref="BI14" si="57">SUM(BI10:BI13)</f>
-        <v>27553.619370960121</v>
+        <f t="shared" ref="BI14" si="55">SUM(BI10:BI13)</f>
+        <v>27770.895882998149</v>
       </c>
       <c r="BJ14" s="5">
-        <f t="shared" ref="BJ14" si="58">SUM(BJ10:BJ13)</f>
-        <v>28031.013919878103</v>
+        <f t="shared" ref="BJ14" si="56">SUM(BJ10:BJ13)</f>
+        <v>28253.859158722204</v>
       </c>
     </row>
     <row r="15" spans="2:62" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3467,148 +3458,148 @@
         <v>29</v>
       </c>
       <c r="C15" s="9">
-        <f t="shared" ref="C15:P15" si="59">C9-C14</f>
+        <f t="shared" ref="C15:P15" si="57">C9-C14</f>
         <v>4</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>84</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>155</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>211</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>191</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>115</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>92</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>137</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>210</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>58</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>65</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>-36</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>-140</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>178</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" ref="Q15:S15" si="60">Q9-Q14</f>
+        <f t="shared" ref="Q15:S15" si="58">Q9-Q14</f>
         <v>263.25</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>193</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>354</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" ref="T15" si="61">T9-T14</f>
+        <f t="shared" ref="T15" si="59">T9-T14</f>
         <v>332</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" ref="U15" si="62">U9-U14</f>
+        <f t="shared" ref="U15" si="60">U9-U14</f>
         <v>38</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" ref="V15:W15" si="63">V9-V14</f>
+        <f t="shared" ref="V15:W15" si="61">V9-V14</f>
         <v>-176</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" ref="X15" si="64">X9-X14</f>
+        <f t="shared" ref="X15" si="62">X9-X14</f>
         <v>193</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" ref="Y15" si="65">Y9-Y14</f>
+        <f t="shared" ref="Y15" si="63">Y9-Y14</f>
         <v>460</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" ref="Z15:AA15" si="66">Z9-Z14</f>
+        <f t="shared" ref="Z15:AA15" si="64">Z9-Z14</f>
         <v>357</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>412</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" ref="AB15" si="67">AB9-AB14</f>
+        <f t="shared" ref="AB15" si="65">AB9-AB14</f>
         <v>1476</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" ref="AC15" si="68">AC9-AC14</f>
+        <f t="shared" ref="AC15" si="66">AC9-AC14</f>
         <v>1501</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" ref="AD15:AE15" si="69">AD9-AD14</f>
+        <f t="shared" ref="AD15:AE15" si="67">AD9-AD14</f>
         <v>1622</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1709</v>
       </c>
       <c r="AF15" s="9">
-        <f t="shared" ref="AF15" si="70">AF9-AF14</f>
+        <f t="shared" ref="AF15" si="68">AF9-AF14</f>
         <v>1783</v>
       </c>
       <c r="AG15" s="9">
-        <f t="shared" ref="AG15" si="71">AG9-AG14</f>
+        <f t="shared" ref="AG15" si="69">AG9-AG14</f>
         <v>1893</v>
       </c>
       <c r="AH15" s="9">
-        <f t="shared" ref="AH15:AL15" si="72">AH9-AH14</f>
+        <f t="shared" ref="AH15:AL15" si="70">AH9-AH14</f>
         <v>1820</v>
       </c>
       <c r="AI15" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1942</v>
       </c>
       <c r="AJ15" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>2332</v>
       </c>
       <c r="AK15" s="9">
-        <f t="shared" si="72"/>
-        <v>2221.3779999999997</v>
+        <f t="shared" si="70"/>
+        <v>2188</v>
       </c>
       <c r="AL15" s="9">
-        <f t="shared" si="72"/>
-        <v>2123.7735000000011</v>
+        <f t="shared" si="70"/>
+        <v>2576.8472999999994</v>
       </c>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
@@ -3631,64 +3622,64 @@
         <v>455</v>
       </c>
       <c r="AV15" s="9">
-        <f t="shared" ref="AV15:BE15" si="73">AV9-AV14</f>
+        <f t="shared" ref="AV15:BE15" si="71">AV9-AV14</f>
         <v>951</v>
       </c>
       <c r="AW15" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>1030</v>
       </c>
       <c r="AX15" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>5011</v>
       </c>
       <c r="AY15" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>7205</v>
       </c>
       <c r="AZ15" s="9">
-        <f t="shared" si="73"/>
-        <v>7725.3115000000071</v>
+        <f t="shared" si="71"/>
+        <v>7840.0973000000049</v>
       </c>
       <c r="BA15" s="9">
-        <f t="shared" si="73"/>
-        <v>9400.5835500000067</v>
+        <f t="shared" si="71"/>
+        <v>8809.1182500000032</v>
       </c>
       <c r="BB15" s="9">
-        <f t="shared" si="73"/>
-        <v>10368.033768000008</v>
+        <f t="shared" si="71"/>
+        <v>9753.3281800000041</v>
       </c>
       <c r="BC15" s="9">
-        <f t="shared" si="73"/>
-        <v>10755.241523760003</v>
+        <f t="shared" si="71"/>
+        <v>10122.241553360003</v>
       </c>
       <c r="BD15" s="9">
-        <f t="shared" si="73"/>
-        <v>11200.09303049041</v>
+        <f t="shared" si="71"/>
+        <v>10546.229031280011</v>
       </c>
       <c r="BE15" s="9">
-        <f t="shared" si="73"/>
-        <v>11649.117427643076</v>
+        <f t="shared" si="71"/>
+        <v>10973.285038163995</v>
       </c>
       <c r="BF15" s="9">
-        <f t="shared" ref="BF15:BJ15" si="74">BF9-BF14</f>
-        <v>11958.053125082246</v>
+        <f t="shared" ref="BF15:BJ15" si="72">BF9-BF14</f>
+        <v>11267.724127212387</v>
       </c>
       <c r="BG15" s="9">
-        <f t="shared" si="74"/>
-        <v>12271.132524959052</v>
+        <f t="shared" si="72"/>
+        <v>11565.901106924612</v>
       </c>
       <c r="BH15" s="9">
-        <f t="shared" si="74"/>
-        <v>12589.815423707158</v>
+        <f t="shared" si="72"/>
+        <v>11869.319538702752</v>
       </c>
       <c r="BI15" s="9">
-        <f t="shared" si="74"/>
-        <v>12914.905946662715</v>
+        <f t="shared" si="72"/>
+        <v>12178.802186962857</v>
       </c>
       <c r="BJ15" s="9">
-        <f t="shared" si="74"/>
-        <v>13246.881904097194</v>
+        <f t="shared" si="72"/>
+        <v>12494.83287263802</v>
       </c>
     </row>
     <row r="16" spans="2:62" x14ac:dyDescent="0.3">
@@ -3803,7 +3794,7 @@
         <v>-6</v>
       </c>
       <c r="AK16" s="5">
-        <v>0</v>
+        <v>-263</v>
       </c>
       <c r="AL16" s="5">
         <v>0</v>
@@ -3846,52 +3837,52 @@
       </c>
       <c r="AZ16" s="5">
         <f>SUM(AI16:AL16)</f>
-        <v>57</v>
+        <v>-206</v>
       </c>
       <c r="BA16" s="5">
-        <f t="shared" ref="BA16:BE16" si="75">AZ16*1.03</f>
-        <v>58.71</v>
+        <f t="shared" ref="BA16:BE16" si="73">AZ16*1.03</f>
+        <v>-212.18</v>
       </c>
       <c r="BB16" s="5">
-        <f t="shared" si="75"/>
-        <v>60.471299999999999</v>
+        <f t="shared" si="73"/>
+        <v>-218.5454</v>
       </c>
       <c r="BC16" s="5">
-        <f t="shared" si="75"/>
-        <v>62.285439000000004</v>
+        <f t="shared" si="73"/>
+        <v>-225.10176200000001</v>
       </c>
       <c r="BD16" s="5">
-        <f t="shared" si="75"/>
-        <v>64.154002170000012</v>
+        <f t="shared" si="73"/>
+        <v>-231.85481486</v>
       </c>
       <c r="BE16" s="5">
-        <f t="shared" si="75"/>
-        <v>66.078622235100013</v>
+        <f t="shared" si="73"/>
+        <v>-238.81045930580001</v>
       </c>
       <c r="BF16" s="5">
-        <f t="shared" ref="BF16" si="76">BE16*1.03</f>
-        <v>68.06098090215302</v>
+        <f t="shared" ref="BF16" si="74">BE16*1.03</f>
+        <v>-245.974773084974</v>
       </c>
       <c r="BG16" s="5">
-        <f t="shared" ref="BG16" si="77">BF16*1.03</f>
-        <v>70.102810329217618</v>
+        <f t="shared" ref="BG16" si="75">BF16*1.03</f>
+        <v>-253.35401627752324</v>
       </c>
       <c r="BH16" s="5">
-        <f t="shared" ref="BH16" si="78">BG16*1.03</f>
-        <v>72.205894639094154</v>
+        <f t="shared" ref="BH16" si="76">BG16*1.03</f>
+        <v>-260.95463676584893</v>
       </c>
       <c r="BI16" s="5">
-        <f t="shared" ref="BI16" si="79">BH16*1.03</f>
-        <v>74.372071478266975</v>
+        <f t="shared" ref="BI16" si="77">BH16*1.03</f>
+        <v>-268.78327586882443</v>
       </c>
       <c r="BJ16" s="5">
-        <f t="shared" ref="BJ16" si="80">BI16*1.03</f>
-        <v>76.603233622614979</v>
+        <f t="shared" ref="BJ16" si="78">BI16*1.03</f>
+        <v>-276.8467741448892</v>
       </c>
     </row>
     <row r="17" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="C17" s="5">
         <v>22</v>
@@ -3996,11 +3987,10 @@
         <v>-68</v>
       </c>
       <c r="AK17" s="5">
-        <f t="shared" ref="AK17:AL17" si="81">AG17*0.9</f>
-        <v>-63</v>
+        <v>-61</v>
       </c>
       <c r="AL17" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" ref="AL17" si="79">AH17*0.9</f>
         <v>-64.8</v>
       </c>
       <c r="AM17" s="5"/>
@@ -4041,196 +4031,196 @@
       </c>
       <c r="AZ17" s="5">
         <f>SUM(AI17:AL17)</f>
-        <v>-290.8</v>
+        <v>-288.8</v>
       </c>
       <c r="BA17" s="5">
-        <f t="shared" ref="BA17:BE17" si="82">AZ17*0.97</f>
-        <v>-282.07600000000002</v>
+        <f t="shared" ref="BA17:BE17" si="80">AZ17*0.97</f>
+        <v>-280.13600000000002</v>
       </c>
       <c r="BB17" s="5">
-        <f t="shared" si="82"/>
-        <v>-273.61372</v>
+        <f t="shared" si="80"/>
+        <v>-271.73192</v>
       </c>
       <c r="BC17" s="5">
-        <f t="shared" si="82"/>
-        <v>-265.40530839999997</v>
+        <f t="shared" si="80"/>
+        <v>-263.5799624</v>
       </c>
       <c r="BD17" s="5">
-        <f t="shared" si="82"/>
-        <v>-257.44314914799997</v>
+        <f t="shared" si="80"/>
+        <v>-255.67256352799998</v>
       </c>
       <c r="BE17" s="5">
-        <f t="shared" si="82"/>
-        <v>-249.71985467355998</v>
+        <f t="shared" si="80"/>
+        <v>-248.00238662215997</v>
       </c>
       <c r="BF17" s="5">
-        <f t="shared" ref="BF17" si="83">BE17*0.97</f>
-        <v>-242.22825903335317</v>
+        <f t="shared" ref="BF17" si="81">BE17*0.97</f>
+        <v>-240.56231502349516</v>
       </c>
       <c r="BG17" s="5">
-        <f t="shared" ref="BG17" si="84">BF17*0.97</f>
-        <v>-234.96141126235256</v>
+        <f t="shared" ref="BG17" si="82">BF17*0.97</f>
+        <v>-233.34544557279031</v>
       </c>
       <c r="BH17" s="5">
-        <f t="shared" ref="BH17" si="85">BG17*0.97</f>
-        <v>-227.91256892448197</v>
+        <f t="shared" ref="BH17" si="83">BG17*0.97</f>
+        <v>-226.34508220560659</v>
       </c>
       <c r="BI17" s="5">
-        <f t="shared" ref="BI17" si="86">BH17*0.97</f>
-        <v>-221.07519185674749</v>
+        <f t="shared" ref="BI17" si="84">BH17*0.97</f>
+        <v>-219.55472973943839</v>
       </c>
       <c r="BJ17" s="5">
-        <f t="shared" ref="BJ17" si="87">BI17*0.97</f>
-        <v>-214.44293610104506</v>
+        <f t="shared" ref="BJ17" si="85">BI17*0.97</f>
+        <v>-212.96808784725522</v>
       </c>
     </row>
     <row r="18" spans="2:196" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:P18" si="88">C15-C16-C17</f>
+        <f t="shared" ref="C18:P18" si="86">C15-C16-C17</f>
         <v>-10</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>63</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>146</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>221</v>
       </c>
       <c r="G18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>385</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>231</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>128</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>239</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>482</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>164</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>64</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-4</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>47</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>839</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" ref="Q18:S18" si="89">Q15-Q16-Q17</f>
+        <f t="shared" ref="Q18:S18" si="87">Q15-Q16-Q17</f>
         <v>1289.25</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>425</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>604</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18" si="90">T15-T16-T17</f>
+        <f t="shared" ref="T18" si="88">T15-T16-T17</f>
         <v>826</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" ref="U18" si="91">U15-U16-U17</f>
+        <f t="shared" ref="U18" si="89">U15-U16-U17</f>
         <v>299</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" ref="V18:W18" si="92">V15-V16-V17</f>
+        <f t="shared" ref="V18:W18" si="90">V15-V16-V17</f>
         <v>-197</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-29</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" ref="X18" si="93">X15-X16-X17</f>
+        <f t="shared" ref="X18" si="91">X15-X16-X17</f>
         <v>181</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="94">Y15-Y16-Y17</f>
+        <f t="shared" ref="Y18" si="92">Y15-Y16-Y17</f>
         <v>475</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18:AA18" si="95">Z15-Z16-Z17</f>
+        <f t="shared" ref="Z18:AA18" si="93">Z15-Z16-Z17</f>
         <v>33</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>326</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" ref="AB18" si="96">AB15-AB16-AB17</f>
+        <f t="shared" ref="AB18" si="94">AB15-AB16-AB17</f>
         <v>1492</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" ref="AC18" si="97">AC15-AC16-AC17</f>
+        <f t="shared" ref="AC18" si="95">AC15-AC16-AC17</f>
         <v>1487</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" ref="AD18:AE18" si="98">AD15-AD16-AD17</f>
+        <f t="shared" ref="AD18:AE18" si="96">AD15-AD16-AD17</f>
         <v>1645</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>1867</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18" si="99">AF15-AF16-AF17</f>
+        <f t="shared" ref="AF18" si="97">AF15-AF16-AF17</f>
         <v>1837</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" ref="AG18" si="100">AG15-AG16-AG17</f>
+        <f t="shared" ref="AG18" si="98">AG15-AG16-AG17</f>
         <v>1746</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" ref="AH18:AL18" si="101">AH15-AH16-AH17</f>
+        <f t="shared" ref="AH18:AL18" si="99">AH15-AH16-AH17</f>
         <v>1988</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>1974</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>2406</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="101"/>
-        <v>2284.3779999999997</v>
+        <f t="shared" si="99"/>
+        <v>2512</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="101"/>
-        <v>2188.5735000000013</v>
+        <f t="shared" si="99"/>
+        <v>2641.6472999999996</v>
       </c>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
@@ -4253,69 +4243,69 @@
         <v>2561</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" ref="AV18:BE18" si="102">AV15-AV16-AV17</f>
+        <f t="shared" ref="AV18:BE18" si="100">AV15-AV16-AV17</f>
         <v>1935</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>660</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>4950</v>
       </c>
       <c r="AY18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>7438</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" si="102"/>
-        <v>7959.1115000000073</v>
+        <f t="shared" si="100"/>
+        <v>8334.8973000000042</v>
       </c>
       <c r="BA18" s="9">
-        <f t="shared" si="102"/>
-        <v>9623.9495500000085</v>
+        <f t="shared" si="100"/>
+        <v>9301.4342500000039</v>
       </c>
       <c r="BB18" s="9">
-        <f t="shared" si="102"/>
-        <v>10581.176188000009</v>
+        <f t="shared" si="100"/>
+        <v>10243.605500000005</v>
       </c>
       <c r="BC18" s="9">
-        <f t="shared" si="102"/>
-        <v>10958.361393160005</v>
+        <f t="shared" si="100"/>
+        <v>10610.923277760003</v>
       </c>
       <c r="BD18" s="9">
-        <f t="shared" si="102"/>
-        <v>11393.382177468411</v>
+        <f t="shared" si="100"/>
+        <v>11033.756409668011</v>
       </c>
       <c r="BE18" s="9">
-        <f t="shared" si="102"/>
-        <v>11832.758660081536</v>
+        <f t="shared" si="100"/>
+        <v>11460.097884091954</v>
       </c>
       <c r="BF18" s="9">
-        <f t="shared" ref="BF18:BJ18" si="103">BF15-BF16-BF17</f>
-        <v>12132.220403213445</v>
+        <f t="shared" ref="BF18:BJ18" si="101">BF15-BF16-BF17</f>
+        <v>11754.261215320856</v>
       </c>
       <c r="BG18" s="9">
-        <f t="shared" si="103"/>
-        <v>12435.991125892187</v>
+        <f t="shared" si="101"/>
+        <v>12052.600568774924</v>
       </c>
       <c r="BH18" s="9">
-        <f t="shared" si="103"/>
-        <v>12745.522097992545</v>
+        <f t="shared" si="101"/>
+        <v>12356.619257674209</v>
       </c>
       <c r="BI18" s="9">
-        <f t="shared" si="103"/>
-        <v>13061.609067041196</v>
+        <f t="shared" si="101"/>
+        <v>12667.14019257112</v>
       </c>
       <c r="BJ18" s="9">
-        <f t="shared" si="103"/>
-        <v>13384.721606575624</v>
+        <f t="shared" si="101"/>
+        <v>12984.647734630165</v>
       </c>
     </row>
     <row r="19" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="5">
         <v>-11</v>
@@ -4420,12 +4410,11 @@
         <v>519</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" ref="AK19:AL19" si="104">AK18*0.18</f>
-        <v>411.18803999999994</v>
+        <v>426</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" si="104"/>
-        <v>393.9432300000002</v>
+        <f t="shared" ref="AL19" si="102">AL18*0.18</f>
+        <v>475.49651399999993</v>
       </c>
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
@@ -4465,196 +4454,196 @@
       </c>
       <c r="AZ19" s="5">
         <f>SUM(AI19:AL19)</f>
-        <v>1757.1312700000003</v>
+        <v>1853.4965139999999</v>
       </c>
       <c r="BA19" s="5">
         <f>BA18*0.18</f>
-        <v>1732.3109190000014</v>
+        <v>1674.2581650000006</v>
       </c>
       <c r="BB19" s="5">
-        <f t="shared" ref="BB19:BJ19" si="105">BB18*0.18</f>
-        <v>1904.6117138400014</v>
+        <f t="shared" ref="BB19:BJ19" si="103">BB18*0.18</f>
+        <v>1843.8489900000009</v>
       </c>
       <c r="BC19" s="5">
-        <f t="shared" si="105"/>
-        <v>1972.5050507688009</v>
+        <f t="shared" si="103"/>
+        <v>1909.9661899968005</v>
       </c>
       <c r="BD19" s="5">
-        <f t="shared" si="105"/>
-        <v>2050.8087919443137</v>
+        <f t="shared" si="103"/>
+        <v>1986.0761537402418</v>
       </c>
       <c r="BE19" s="5">
-        <f t="shared" si="105"/>
-        <v>2129.8965588146762</v>
+        <f t="shared" si="103"/>
+        <v>2062.8176191365519</v>
       </c>
       <c r="BF19" s="5">
-        <f t="shared" si="105"/>
-        <v>2183.7996725784201</v>
+        <f t="shared" si="103"/>
+        <v>2115.7670187577542</v>
       </c>
       <c r="BG19" s="5">
-        <f t="shared" si="105"/>
-        <v>2238.4784026605935</v>
+        <f t="shared" si="103"/>
+        <v>2169.468102379486</v>
       </c>
       <c r="BH19" s="5">
-        <f t="shared" si="105"/>
-        <v>2294.193977638658</v>
+        <f t="shared" si="103"/>
+        <v>2224.1914663813573</v>
       </c>
       <c r="BI19" s="5">
-        <f t="shared" si="105"/>
-        <v>2351.0896320674151</v>
+        <f t="shared" si="103"/>
+        <v>2280.0852346628017</v>
       </c>
       <c r="BJ19" s="5">
-        <f t="shared" si="105"/>
-        <v>2409.2498891836121</v>
+        <f t="shared" si="103"/>
+        <v>2337.2365922334297</v>
       </c>
     </row>
     <row r="20" spans="2:196" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:P20" si="106">C18-C19</f>
+        <f t="shared" ref="C20:P20" si="104">C18-C19</f>
         <v>1</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>46</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>107</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>206</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>344</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>299</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>105</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>362</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>392</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>91</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>-109</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>-248</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>99</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>2625</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20:S20" si="107">Q18-Q19</f>
+        <f t="shared" ref="Q20:S20" si="105">Q18-Q19</f>
         <v>1120.25</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>267</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>469</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20" si="108">T18-T19</f>
+        <f t="shared" ref="T20" si="106">T18-T19</f>
         <v>535</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" ref="U20" si="109">U18-U19</f>
+        <f t="shared" ref="U20" si="107">U18-U19</f>
         <v>468</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" ref="V20:W20" si="110">V18-V19</f>
+        <f t="shared" ref="V20:W20" si="108">V18-V19</f>
         <v>-28</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>28</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20" si="111">X18-X19</f>
+        <f t="shared" ref="X20" si="109">X18-X19</f>
         <v>68</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="112">Y18-Y19</f>
+        <f t="shared" ref="Y20" si="110">Y18-Y19</f>
         <v>210</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20:AA20" si="113">Z18-Z19</f>
+        <f t="shared" ref="Z20:AA20" si="111">Z18-Z19</f>
         <v>-98</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>199</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" ref="AB20" si="114">AB18-AB19</f>
+        <f t="shared" ref="AB20" si="112">AB18-AB19</f>
         <v>1267</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="115">AC18-AC19</f>
+        <f t="shared" ref="AC20" si="113">AC18-AC19</f>
         <v>1224</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20:AE20" si="116">AD18-AD19</f>
+        <f t="shared" ref="AD20:AE20" si="114">AD18-AD19</f>
         <v>1446</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>1533</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" ref="AF20" si="117">AF18-AF19</f>
+        <f t="shared" ref="AF20" si="115">AF18-AF19</f>
         <v>1429</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" ref="AG20" si="118">AG18-AG19</f>
+        <f t="shared" ref="AG20" si="116">AG18-AG19</f>
         <v>1527</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" ref="AH20:AL20" si="119">AH18-AH19</f>
+        <f t="shared" ref="AH20:AL20" si="117">AH18-AH19</f>
         <v>1708</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="117"/>
         <v>1541</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="117"/>
         <v>1887</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" si="119"/>
-        <v>1873.1899599999997</v>
+        <f t="shared" si="117"/>
+        <v>2086</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" si="119"/>
-        <v>1794.630270000001</v>
+        <f t="shared" si="117"/>
+        <v>2166.1507859999997</v>
       </c>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
@@ -4677,600 +4666,600 @@
         <v>4072</v>
       </c>
       <c r="AV20" s="9">
-        <f t="shared" ref="AV20:BE20" si="120">AV18-AV19</f>
+        <f t="shared" ref="AV20:BE20" si="118">AV18-AV19</f>
         <v>1847</v>
       </c>
       <c r="AW20" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>208</v>
       </c>
       <c r="AX20" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>4136</v>
       </c>
       <c r="AY20" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>6197</v>
       </c>
       <c r="AZ20" s="9">
-        <f t="shared" si="120"/>
-        <v>6201.9802300000065</v>
+        <f t="shared" si="118"/>
+        <v>6481.4007860000038</v>
       </c>
       <c r="BA20" s="9">
-        <f t="shared" si="120"/>
-        <v>7891.6386310000071</v>
+        <f t="shared" si="118"/>
+        <v>7627.1760850000028</v>
       </c>
       <c r="BB20" s="9">
-        <f t="shared" si="120"/>
-        <v>8676.5644741600081</v>
+        <f t="shared" si="118"/>
+        <v>8399.7565100000047</v>
       </c>
       <c r="BC20" s="9">
-        <f t="shared" si="120"/>
-        <v>8985.8563423912037</v>
+        <f t="shared" si="118"/>
+        <v>8700.9570877632032</v>
       </c>
       <c r="BD20" s="9">
-        <f t="shared" si="120"/>
-        <v>9342.5733855240978</v>
+        <f t="shared" si="118"/>
+        <v>9047.6802559277694</v>
       </c>
       <c r="BE20" s="9">
-        <f t="shared" si="120"/>
-        <v>9702.8621012668591</v>
+        <f t="shared" si="118"/>
+        <v>9397.2802649554033</v>
       </c>
       <c r="BF20" s="9">
-        <f t="shared" ref="BF20:BJ20" si="121">BF18-BF19</f>
-        <v>9948.4207306350254</v>
+        <f t="shared" ref="BF20:BJ20" si="119">BF18-BF19</f>
+        <v>9638.4941965631006</v>
       </c>
       <c r="BG20" s="9">
-        <f t="shared" si="121"/>
-        <v>10197.512723231594</v>
+        <f t="shared" si="119"/>
+        <v>9883.1324663954383</v>
       </c>
       <c r="BH20" s="9">
-        <f t="shared" si="121"/>
-        <v>10451.328120353886</v>
+        <f t="shared" si="119"/>
+        <v>10132.427791292852</v>
       </c>
       <c r="BI20" s="9">
-        <f t="shared" si="121"/>
-        <v>10710.519434973781</v>
+        <f t="shared" si="119"/>
+        <v>10387.054957908318</v>
       </c>
       <c r="BJ20" s="9">
-        <f t="shared" si="121"/>
-        <v>10975.471717392011</v>
+        <f t="shared" si="119"/>
+        <v>10647.411142396735</v>
       </c>
       <c r="BK20" s="1">
         <f>BJ20*(1+$BM$30)</f>
-        <v>10865.71700021809</v>
+        <v>10540.937030972767</v>
       </c>
       <c r="BL20" s="1">
-        <f t="shared" ref="BL20:DW20" si="122">BK20*(1+$BM$30)</f>
-        <v>10757.059830215909</v>
+        <f t="shared" ref="BL20:DW20" si="120">BK20*(1+$BM$30)</f>
+        <v>10435.52766066304</v>
       </c>
       <c r="BM20" s="1">
+        <f t="shared" si="120"/>
+        <v>10331.172384056408</v>
+      </c>
+      <c r="BN20" s="1">
+        <f t="shared" si="120"/>
+        <v>10227.860660215843</v>
+      </c>
+      <c r="BO20" s="1">
+        <f t="shared" si="120"/>
+        <v>10125.582053613685</v>
+      </c>
+      <c r="BP20" s="1">
+        <f t="shared" si="120"/>
+        <v>10024.326233077549</v>
+      </c>
+      <c r="BQ20" s="1">
+        <f t="shared" si="120"/>
+        <v>9924.0829707467728</v>
+      </c>
+      <c r="BR20" s="1">
+        <f t="shared" si="120"/>
+        <v>9824.8421410393057</v>
+      </c>
+      <c r="BS20" s="1">
+        <f t="shared" si="120"/>
+        <v>9726.5937196289124</v>
+      </c>
+      <c r="BT20" s="1">
+        <f t="shared" si="120"/>
+        <v>9629.3277824326233</v>
+      </c>
+      <c r="BU20" s="1">
+        <f t="shared" si="120"/>
+        <v>9533.0345046082966</v>
+      </c>
+      <c r="BV20" s="1">
+        <f t="shared" si="120"/>
+        <v>9437.704159562214</v>
+      </c>
+      <c r="BW20" s="1">
+        <f t="shared" si="120"/>
+        <v>9343.3271179665917</v>
+      </c>
+      <c r="BX20" s="1">
+        <f t="shared" si="120"/>
+        <v>9249.8938467869266</v>
+      </c>
+      <c r="BY20" s="1">
+        <f t="shared" si="120"/>
+        <v>9157.3949083190564</v>
+      </c>
+      <c r="BZ20" s="1">
+        <f t="shared" si="120"/>
+        <v>9065.8209592358653</v>
+      </c>
+      <c r="CA20" s="1">
+        <f t="shared" si="120"/>
+        <v>8975.1627496435067</v>
+      </c>
+      <c r="CB20" s="1">
+        <f t="shared" si="120"/>
+        <v>8885.4111221470721</v>
+      </c>
+      <c r="CC20" s="1">
+        <f t="shared" si="120"/>
+        <v>8796.5570109256005</v>
+      </c>
+      <c r="CD20" s="1">
+        <f t="shared" si="120"/>
+        <v>8708.5914408163444</v>
+      </c>
+      <c r="CE20" s="1">
+        <f t="shared" si="120"/>
+        <v>8621.5055264081802</v>
+      </c>
+      <c r="CF20" s="1">
+        <f t="shared" si="120"/>
+        <v>8535.2904711440988</v>
+      </c>
+      <c r="CG20" s="1">
+        <f t="shared" si="120"/>
+        <v>8449.9375664326581</v>
+      </c>
+      <c r="CH20" s="1">
+        <f t="shared" si="120"/>
+        <v>8365.438190768331</v>
+      </c>
+      <c r="CI20" s="1">
+        <f t="shared" si="120"/>
+        <v>8281.7838088606477</v>
+      </c>
+      <c r="CJ20" s="1">
+        <f t="shared" si="120"/>
+        <v>8198.9659707720402</v>
+      </c>
+      <c r="CK20" s="1">
+        <f t="shared" si="120"/>
+        <v>8116.9763110643198</v>
+      </c>
+      <c r="CL20" s="1">
+        <f t="shared" si="120"/>
+        <v>8035.8065479536763</v>
+      </c>
+      <c r="CM20" s="1">
+        <f t="shared" si="120"/>
+        <v>7955.4484824741394</v>
+      </c>
+      <c r="CN20" s="1">
+        <f t="shared" si="120"/>
+        <v>7875.8939976493975</v>
+      </c>
+      <c r="CO20" s="1">
+        <f t="shared" si="120"/>
+        <v>7797.1350576729037</v>
+      </c>
+      <c r="CP20" s="1">
+        <f t="shared" si="120"/>
+        <v>7719.1637070961742</v>
+      </c>
+      <c r="CQ20" s="1">
+        <f t="shared" si="120"/>
+        <v>7641.9720700252128</v>
+      </c>
+      <c r="CR20" s="1">
+        <f t="shared" si="120"/>
+        <v>7565.5523493249602</v>
+      </c>
+      <c r="CS20" s="1">
+        <f t="shared" si="120"/>
+        <v>7489.8968258317109</v>
+      </c>
+      <c r="CT20" s="1">
+        <f t="shared" si="120"/>
+        <v>7414.997857573394</v>
+      </c>
+      <c r="CU20" s="1">
+        <f t="shared" si="120"/>
+        <v>7340.8478789976598</v>
+      </c>
+      <c r="CV20" s="1">
+        <f t="shared" si="120"/>
+        <v>7267.4394002076833</v>
+      </c>
+      <c r="CW20" s="1">
+        <f t="shared" si="120"/>
+        <v>7194.7650062056064</v>
+      </c>
+      <c r="CX20" s="1">
+        <f t="shared" si="120"/>
+        <v>7122.8173561435506</v>
+      </c>
+      <c r="CY20" s="1">
+        <f t="shared" si="120"/>
+        <v>7051.5891825821154</v>
+      </c>
+      <c r="CZ20" s="1">
+        <f t="shared" si="120"/>
+        <v>6981.0732907562942</v>
+      </c>
+      <c r="DA20" s="1">
+        <f t="shared" si="120"/>
+        <v>6911.2625578487314</v>
+      </c>
+      <c r="DB20" s="1">
+        <f t="shared" si="120"/>
+        <v>6842.1499322702439</v>
+      </c>
+      <c r="DC20" s="1">
+        <f t="shared" si="120"/>
+        <v>6773.7284329475415</v>
+      </c>
+      <c r="DD20" s="1">
+        <f t="shared" si="120"/>
+        <v>6705.9911486180663</v>
+      </c>
+      <c r="DE20" s="1">
+        <f t="shared" si="120"/>
+        <v>6638.9312371318856</v>
+      </c>
+      <c r="DF20" s="1">
+        <f t="shared" si="120"/>
+        <v>6572.5419247605669</v>
+      </c>
+      <c r="DG20" s="1">
+        <f t="shared" si="120"/>
+        <v>6506.8165055129612</v>
+      </c>
+      <c r="DH20" s="1">
+        <f t="shared" si="120"/>
+        <v>6441.7483404578315</v>
+      </c>
+      <c r="DI20" s="1">
+        <f t="shared" si="120"/>
+        <v>6377.3308570532536</v>
+      </c>
+      <c r="DJ20" s="1">
+        <f t="shared" si="120"/>
+        <v>6313.5575484827214</v>
+      </c>
+      <c r="DK20" s="1">
+        <f t="shared" si="120"/>
+        <v>6250.421972997894</v>
+      </c>
+      <c r="DL20" s="1">
+        <f t="shared" si="120"/>
+        <v>6187.917753267915</v>
+      </c>
+      <c r="DM20" s="1">
+        <f t="shared" si="120"/>
+        <v>6126.038575735236</v>
+      </c>
+      <c r="DN20" s="1">
+        <f t="shared" si="120"/>
+        <v>6064.7781899778838</v>
+      </c>
+      <c r="DO20" s="1">
+        <f t="shared" si="120"/>
+        <v>6004.1304080781047</v>
+      </c>
+      <c r="DP20" s="1">
+        <f t="shared" si="120"/>
+        <v>5944.0891039973239</v>
+      </c>
+      <c r="DQ20" s="1">
+        <f t="shared" si="120"/>
+        <v>5884.6482129573506</v>
+      </c>
+      <c r="DR20" s="1">
+        <f t="shared" si="120"/>
+        <v>5825.8017308277767</v>
+      </c>
+      <c r="DS20" s="1">
+        <f t="shared" si="120"/>
+        <v>5767.5437135194989</v>
+      </c>
+      <c r="DT20" s="1">
+        <f t="shared" si="120"/>
+        <v>5709.8682763843035</v>
+      </c>
+      <c r="DU20" s="1">
+        <f t="shared" si="120"/>
+        <v>5652.76959362046</v>
+      </c>
+      <c r="DV20" s="1">
+        <f t="shared" si="120"/>
+        <v>5596.2418976842555</v>
+      </c>
+      <c r="DW20" s="1">
+        <f t="shared" si="120"/>
+        <v>5540.2794787074126</v>
+      </c>
+      <c r="DX20" s="1">
+        <f t="shared" ref="DX20:GI20" si="121">DW20*(1+$BM$30)</f>
+        <v>5484.8766839203381</v>
+      </c>
+      <c r="DY20" s="1">
+        <f t="shared" si="121"/>
+        <v>5430.0279170811345</v>
+      </c>
+      <c r="DZ20" s="1">
+        <f t="shared" si="121"/>
+        <v>5375.7276379103232</v>
+      </c>
+      <c r="EA20" s="1">
+        <f t="shared" si="121"/>
+        <v>5321.9703615312201</v>
+      </c>
+      <c r="EB20" s="1">
+        <f t="shared" si="121"/>
+        <v>5268.7506579159081</v>
+      </c>
+      <c r="EC20" s="1">
+        <f t="shared" si="121"/>
+        <v>5216.0631513367489</v>
+      </c>
+      <c r="ED20" s="1">
+        <f t="shared" si="121"/>
+        <v>5163.9025198233812</v>
+      </c>
+      <c r="EE20" s="1">
+        <f t="shared" si="121"/>
+        <v>5112.2634946251474</v>
+      </c>
+      <c r="EF20" s="1">
+        <f t="shared" si="121"/>
+        <v>5061.140859678896</v>
+      </c>
+      <c r="EG20" s="1">
+        <f t="shared" si="121"/>
+        <v>5010.5294510821068</v>
+      </c>
+      <c r="EH20" s="1">
+        <f t="shared" si="121"/>
+        <v>4960.4241565712855</v>
+      </c>
+      <c r="EI20" s="1">
+        <f t="shared" si="121"/>
+        <v>4910.8199150055725</v>
+      </c>
+      <c r="EJ20" s="1">
+        <f t="shared" si="121"/>
+        <v>4861.7117158555166</v>
+      </c>
+      <c r="EK20" s="1">
+        <f t="shared" si="121"/>
+        <v>4813.0945986969609</v>
+      </c>
+      <c r="EL20" s="1">
+        <f t="shared" si="121"/>
+        <v>4764.963652709991</v>
+      </c>
+      <c r="EM20" s="1">
+        <f t="shared" si="121"/>
+        <v>4717.3140161828915</v>
+      </c>
+      <c r="EN20" s="1">
+        <f t="shared" si="121"/>
+        <v>4670.1408760210625</v>
+      </c>
+      <c r="EO20" s="1">
+        <f t="shared" si="121"/>
+        <v>4623.4394672608514</v>
+      </c>
+      <c r="EP20" s="1">
+        <f t="shared" si="121"/>
+        <v>4577.2050725882427</v>
+      </c>
+      <c r="EQ20" s="1">
+        <f t="shared" si="121"/>
+        <v>4531.43302186236</v>
+      </c>
+      <c r="ER20" s="1">
+        <f t="shared" si="121"/>
+        <v>4486.1186916437364</v>
+      </c>
+      <c r="ES20" s="1">
+        <f t="shared" si="121"/>
+        <v>4441.2575047272994</v>
+      </c>
+      <c r="ET20" s="1">
+        <f t="shared" si="121"/>
+        <v>4396.8449296800263</v>
+      </c>
+      <c r="EU20" s="1">
+        <f t="shared" si="121"/>
+        <v>4352.8764803832264</v>
+      </c>
+      <c r="EV20" s="1">
+        <f t="shared" si="121"/>
+        <v>4309.3477155793944</v>
+      </c>
+      <c r="EW20" s="1">
+        <f t="shared" si="121"/>
+        <v>4266.2542384236003</v>
+      </c>
+      <c r="EX20" s="1">
+        <f t="shared" si="121"/>
+        <v>4223.5916960393643</v>
+      </c>
+      <c r="EY20" s="1">
+        <f t="shared" si="121"/>
+        <v>4181.355779078971</v>
+      </c>
+      <c r="EZ20" s="1">
+        <f t="shared" si="121"/>
+        <v>4139.5422212881813</v>
+      </c>
+      <c r="FA20" s="1">
+        <f t="shared" si="121"/>
+        <v>4098.146799075299</v>
+      </c>
+      <c r="FB20" s="1">
+        <f t="shared" si="121"/>
+        <v>4057.1653310845459</v>
+      </c>
+      <c r="FC20" s="1">
+        <f t="shared" si="121"/>
+        <v>4016.5936777737002</v>
+      </c>
+      <c r="FD20" s="1">
+        <f t="shared" si="121"/>
+        <v>3976.4277409959632</v>
+      </c>
+      <c r="FE20" s="1">
+        <f t="shared" si="121"/>
+        <v>3936.6634635860037</v>
+      </c>
+      <c r="FF20" s="1">
+        <f t="shared" si="121"/>
+        <v>3897.2968289501437</v>
+      </c>
+      <c r="FG20" s="1">
+        <f t="shared" si="121"/>
+        <v>3858.3238606606424</v>
+      </c>
+      <c r="FH20" s="1">
+        <f t="shared" si="121"/>
+        <v>3819.7406220540361</v>
+      </c>
+      <c r="FI20" s="1">
+        <f t="shared" si="121"/>
+        <v>3781.5432158334957</v>
+      </c>
+      <c r="FJ20" s="1">
+        <f t="shared" si="121"/>
+        <v>3743.7277836751605</v>
+      </c>
+      <c r="FK20" s="1">
+        <f t="shared" si="121"/>
+        <v>3706.290505838409</v>
+      </c>
+      <c r="FL20" s="1">
+        <f t="shared" si="121"/>
+        <v>3669.2276007800247</v>
+      </c>
+      <c r="FM20" s="1">
+        <f t="shared" si="121"/>
+        <v>3632.5353247722242</v>
+      </c>
+      <c r="FN20" s="1">
+        <f t="shared" si="121"/>
+        <v>3596.2099715245017</v>
+      </c>
+      <c r="FO20" s="1">
+        <f t="shared" si="121"/>
+        <v>3560.2478718092566</v>
+      </c>
+      <c r="FP20" s="1">
+        <f t="shared" si="121"/>
+        <v>3524.6453930911639</v>
+      </c>
+      <c r="FQ20" s="1">
+        <f t="shared" si="121"/>
+        <v>3489.3989391602522</v>
+      </c>
+      <c r="FR20" s="1">
+        <f t="shared" si="121"/>
+        <v>3454.5049497686496</v>
+      </c>
+      <c r="FS20" s="1">
+        <f t="shared" si="121"/>
+        <v>3419.9599002709629</v>
+      </c>
+      <c r="FT20" s="1">
+        <f t="shared" si="121"/>
+        <v>3385.760301268253</v>
+      </c>
+      <c r="FU20" s="1">
+        <f t="shared" si="121"/>
+        <v>3351.9026982555706</v>
+      </c>
+      <c r="FV20" s="1">
+        <f t="shared" si="121"/>
+        <v>3318.3836712730149</v>
+      </c>
+      <c r="FW20" s="1">
+        <f t="shared" si="121"/>
+        <v>3285.1998345602847</v>
+      </c>
+      <c r="FX20" s="1">
+        <f t="shared" si="121"/>
+        <v>3252.3478362146816</v>
+      </c>
+      <c r="FY20" s="1">
+        <f t="shared" si="121"/>
+        <v>3219.8243578525348</v>
+      </c>
+      <c r="FZ20" s="1">
+        <f t="shared" si="121"/>
+        <v>3187.6261142740095</v>
+      </c>
+      <c r="GA20" s="1">
+        <f t="shared" si="121"/>
+        <v>3155.7498531312694</v>
+      </c>
+      <c r="GB20" s="1">
+        <f t="shared" si="121"/>
+        <v>3124.1923545999566</v>
+      </c>
+      <c r="GC20" s="1">
+        <f t="shared" si="121"/>
+        <v>3092.9504310539569</v>
+      </c>
+      <c r="GD20" s="1">
+        <f t="shared" si="121"/>
+        <v>3062.0209267434175</v>
+      </c>
+      <c r="GE20" s="1">
+        <f t="shared" si="121"/>
+        <v>3031.4007174759831</v>
+      </c>
+      <c r="GF20" s="1">
+        <f t="shared" si="121"/>
+        <v>3001.0867103012233</v>
+      </c>
+      <c r="GG20" s="1">
+        <f t="shared" si="121"/>
+        <v>2971.0758431982113</v>
+      </c>
+      <c r="GH20" s="1">
+        <f t="shared" si="121"/>
+        <v>2941.3650847662293</v>
+      </c>
+      <c r="GI20" s="1">
+        <f t="shared" si="121"/>
+        <v>2911.9514339185671</v>
+      </c>
+      <c r="GJ20" s="1">
+        <f t="shared" ref="GJ20:GN20" si="122">GI20*(1+$BM$30)</f>
+        <v>2882.8319195793815</v>
+      </c>
+      <c r="GK20" s="1">
         <f t="shared" si="122"/>
-        <v>10649.489231913749</v>
-      </c>
-      <c r="BN20" s="1">
+        <v>2854.0036003835876</v>
+      </c>
+      <c r="GL20" s="1">
         <f t="shared" si="122"/>
-        <v>10542.994339594612</v>
-      </c>
-      <c r="BO20" s="1">
+        <v>2825.4635643797515</v>
+      </c>
+      <c r="GM20" s="1">
         <f t="shared" si="122"/>
-        <v>10437.564396198666</v>
-      </c>
-      <c r="BP20" s="1">
+        <v>2797.208928735954</v>
+      </c>
+      <c r="GN20" s="1">
         <f t="shared" si="122"/>
-        <v>10333.18875223668</v>
-      </c>
-      <c r="BQ20" s="1">
-        <f t="shared" si="122"/>
-        <v>10229.856864714313</v>
-      </c>
-      <c r="BR20" s="1">
-        <f t="shared" si="122"/>
-        <v>10127.558296067169</v>
-      </c>
-      <c r="BS20" s="1">
-        <f t="shared" si="122"/>
-        <v>10026.282713106497</v>
-      </c>
-      <c r="BT20" s="1">
-        <f t="shared" si="122"/>
-        <v>9926.019885975431</v>
-      </c>
-      <c r="BU20" s="1">
-        <f t="shared" si="122"/>
-        <v>9826.7596871156766</v>
-      </c>
-      <c r="BV20" s="1">
-        <f t="shared" si="122"/>
-        <v>9728.4920902445192</v>
-      </c>
-      <c r="BW20" s="1">
-        <f t="shared" si="122"/>
-        <v>9631.207169342073</v>
-      </c>
-      <c r="BX20" s="1">
-        <f t="shared" si="122"/>
-        <v>9534.8950976486522</v>
-      </c>
-      <c r="BY20" s="1">
-        <f t="shared" si="122"/>
-        <v>9439.5461466721663</v>
-      </c>
-      <c r="BZ20" s="1">
-        <f t="shared" si="122"/>
-        <v>9345.1506852054445</v>
-      </c>
-      <c r="CA20" s="1">
-        <f t="shared" si="122"/>
-        <v>9251.6991783533904</v>
-      </c>
-      <c r="CB20" s="1">
-        <f t="shared" si="122"/>
-        <v>9159.1821865698566</v>
-      </c>
-      <c r="CC20" s="1">
-        <f t="shared" si="122"/>
-        <v>9067.5903647041578</v>
-      </c>
-      <c r="CD20" s="1">
-        <f t="shared" si="122"/>
-        <v>8976.9144610571166</v>
-      </c>
-      <c r="CE20" s="1">
-        <f t="shared" si="122"/>
-        <v>8887.1453164465456</v>
-      </c>
-      <c r="CF20" s="1">
-        <f t="shared" si="122"/>
-        <v>8798.2738632820801</v>
-      </c>
-      <c r="CG20" s="1">
-        <f t="shared" si="122"/>
-        <v>8710.2911246492586</v>
-      </c>
-      <c r="CH20" s="1">
-        <f t="shared" si="122"/>
-        <v>8623.1882134027655</v>
-      </c>
-      <c r="CI20" s="1">
-        <f t="shared" si="122"/>
-        <v>8536.9563312687369</v>
-      </c>
-      <c r="CJ20" s="1">
-        <f t="shared" si="122"/>
-        <v>8451.5867679560488</v>
-      </c>
-      <c r="CK20" s="1">
-        <f t="shared" si="122"/>
-        <v>8367.0709002764888</v>
-      </c>
-      <c r="CL20" s="1">
-        <f t="shared" si="122"/>
-        <v>8283.400191273724</v>
-      </c>
-      <c r="CM20" s="1">
-        <f t="shared" si="122"/>
-        <v>8200.5661893609868</v>
-      </c>
-      <c r="CN20" s="1">
-        <f t="shared" si="122"/>
-        <v>8118.5605274673771</v>
-      </c>
-      <c r="CO20" s="1">
-        <f t="shared" si="122"/>
-        <v>8037.3749221927037</v>
-      </c>
-      <c r="CP20" s="1">
-        <f t="shared" si="122"/>
-        <v>7957.0011729707767</v>
-      </c>
-      <c r="CQ20" s="1">
-        <f t="shared" si="122"/>
-        <v>7877.4311612410693</v>
-      </c>
-      <c r="CR20" s="1">
-        <f t="shared" si="122"/>
-        <v>7798.6568496286582</v>
-      </c>
-      <c r="CS20" s="1">
-        <f t="shared" si="122"/>
-        <v>7720.6702811323712</v>
-      </c>
-      <c r="CT20" s="1">
-        <f t="shared" si="122"/>
-        <v>7643.4635783210479</v>
-      </c>
-      <c r="CU20" s="1">
-        <f t="shared" si="122"/>
-        <v>7567.0289425378369</v>
-      </c>
-      <c r="CV20" s="1">
-        <f t="shared" si="122"/>
-        <v>7491.3586531124583</v>
-      </c>
-      <c r="CW20" s="1">
-        <f t="shared" si="122"/>
-        <v>7416.4450665813338</v>
-      </c>
-      <c r="CX20" s="1">
-        <f t="shared" si="122"/>
-        <v>7342.2806159155207</v>
-      </c>
-      <c r="CY20" s="1">
-        <f t="shared" si="122"/>
-        <v>7268.857809756365</v>
-      </c>
-      <c r="CZ20" s="1">
-        <f t="shared" si="122"/>
-        <v>7196.1692316588014</v>
-      </c>
-      <c r="DA20" s="1">
-        <f t="shared" si="122"/>
-        <v>7124.2075393422137</v>
-      </c>
-      <c r="DB20" s="1">
-        <f t="shared" si="122"/>
-        <v>7052.9654639487917</v>
-      </c>
-      <c r="DC20" s="1">
-        <f t="shared" si="122"/>
-        <v>6982.4358093093033</v>
-      </c>
-      <c r="DD20" s="1">
-        <f t="shared" si="122"/>
-        <v>6912.6114512162103</v>
-      </c>
-      <c r="DE20" s="1">
-        <f t="shared" si="122"/>
-        <v>6843.4853367040478</v>
-      </c>
-      <c r="DF20" s="1">
-        <f t="shared" si="122"/>
-        <v>6775.0504833370069</v>
-      </c>
-      <c r="DG20" s="1">
-        <f t="shared" si="122"/>
-        <v>6707.2999785036363</v>
-      </c>
-      <c r="DH20" s="1">
-        <f t="shared" si="122"/>
-        <v>6640.2269787185996</v>
-      </c>
-      <c r="DI20" s="1">
-        <f t="shared" si="122"/>
-        <v>6573.8247089314136</v>
-      </c>
-      <c r="DJ20" s="1">
-        <f t="shared" si="122"/>
-        <v>6508.0864618420992</v>
-      </c>
-      <c r="DK20" s="1">
-        <f t="shared" si="122"/>
-        <v>6443.0055972236778</v>
-      </c>
-      <c r="DL20" s="1">
-        <f t="shared" si="122"/>
-        <v>6378.5755412514409</v>
-      </c>
-      <c r="DM20" s="1">
-        <f t="shared" si="122"/>
-        <v>6314.789785838926</v>
-      </c>
-      <c r="DN20" s="1">
-        <f t="shared" si="122"/>
-        <v>6251.6418879805369</v>
-      </c>
-      <c r="DO20" s="1">
-        <f t="shared" si="122"/>
-        <v>6189.1254691007316</v>
-      </c>
-      <c r="DP20" s="1">
-        <f t="shared" si="122"/>
-        <v>6127.2342144097238</v>
-      </c>
-      <c r="DQ20" s="1">
-        <f t="shared" si="122"/>
-        <v>6065.9618722656269</v>
-      </c>
-      <c r="DR20" s="1">
-        <f t="shared" si="122"/>
-        <v>6005.3022535429709</v>
-      </c>
-      <c r="DS20" s="1">
-        <f t="shared" si="122"/>
-        <v>5945.2492310075413</v>
-      </c>
-      <c r="DT20" s="1">
-        <f t="shared" si="122"/>
-        <v>5885.796738697466</v>
-      </c>
-      <c r="DU20" s="1">
-        <f t="shared" si="122"/>
-        <v>5826.9387713104916</v>
-      </c>
-      <c r="DV20" s="1">
-        <f t="shared" si="122"/>
-        <v>5768.6693835973865</v>
-      </c>
-      <c r="DW20" s="1">
-        <f t="shared" si="122"/>
-        <v>5710.982689761413</v>
-      </c>
-      <c r="DX20" s="1">
-        <f t="shared" ref="DX20:GI20" si="123">DW20*(1+$BM$30)</f>
-        <v>5653.8728628637991</v>
-      </c>
-      <c r="DY20" s="1">
-        <f t="shared" si="123"/>
-        <v>5597.3341342351614</v>
-      </c>
-      <c r="DZ20" s="1">
-        <f t="shared" si="123"/>
-        <v>5541.3607928928095</v>
-      </c>
-      <c r="EA20" s="1">
-        <f t="shared" si="123"/>
-        <v>5485.9471849638812</v>
-      </c>
-      <c r="EB20" s="1">
-        <f t="shared" si="123"/>
-        <v>5431.0877131142424</v>
-      </c>
-      <c r="EC20" s="1">
-        <f t="shared" si="123"/>
-        <v>5376.7768359830998</v>
-      </c>
-      <c r="ED20" s="1">
-        <f t="shared" si="123"/>
-        <v>5323.0090676232685</v>
-      </c>
-      <c r="EE20" s="1">
-        <f t="shared" si="123"/>
-        <v>5269.7789769470355</v>
-      </c>
-      <c r="EF20" s="1">
-        <f t="shared" si="123"/>
-        <v>5217.081187177565</v>
-      </c>
-      <c r="EG20" s="1">
-        <f t="shared" si="123"/>
-        <v>5164.9103753057889</v>
-      </c>
-      <c r="EH20" s="1">
-        <f t="shared" si="123"/>
-        <v>5113.2612715527312</v>
-      </c>
-      <c r="EI20" s="1">
-        <f t="shared" si="123"/>
-        <v>5062.1286588372041</v>
-      </c>
-      <c r="EJ20" s="1">
-        <f t="shared" si="123"/>
-        <v>5011.5073722488323</v>
-      </c>
-      <c r="EK20" s="1">
-        <f t="shared" si="123"/>
-        <v>4961.3922985263443</v>
-      </c>
-      <c r="EL20" s="1">
-        <f t="shared" si="123"/>
-        <v>4911.778375541081</v>
-      </c>
-      <c r="EM20" s="1">
-        <f t="shared" si="123"/>
-        <v>4862.6605917856705</v>
-      </c>
-      <c r="EN20" s="1">
-        <f t="shared" si="123"/>
-        <v>4814.0339858678135</v>
-      </c>
-      <c r="EO20" s="1">
-        <f t="shared" si="123"/>
-        <v>4765.8936460091354</v>
-      </c>
-      <c r="EP20" s="1">
-        <f t="shared" si="123"/>
-        <v>4718.2347095490441</v>
-      </c>
-      <c r="EQ20" s="1">
-        <f t="shared" si="123"/>
-        <v>4671.0523624535535</v>
-      </c>
-      <c r="ER20" s="1">
-        <f t="shared" si="123"/>
-        <v>4624.3418388290183</v>
-      </c>
-      <c r="ES20" s="1">
-        <f t="shared" si="123"/>
-        <v>4578.0984204407278</v>
-      </c>
-      <c r="ET20" s="1">
-        <f t="shared" si="123"/>
-        <v>4532.3174362363206</v>
-      </c>
-      <c r="EU20" s="1">
-        <f t="shared" si="123"/>
-        <v>4486.9942618739578</v>
-      </c>
-      <c r="EV20" s="1">
-        <f t="shared" si="123"/>
-        <v>4442.1243192552183</v>
-      </c>
-      <c r="EW20" s="1">
-        <f t="shared" si="123"/>
-        <v>4397.7030760626658</v>
-      </c>
-      <c r="EX20" s="1">
-        <f t="shared" si="123"/>
-        <v>4353.726045302039</v>
-      </c>
-      <c r="EY20" s="1">
-        <f t="shared" si="123"/>
-        <v>4310.1887848490187</v>
-      </c>
-      <c r="EZ20" s="1">
-        <f t="shared" si="123"/>
-        <v>4267.0868970005286</v>
-      </c>
-      <c r="FA20" s="1">
-        <f t="shared" si="123"/>
-        <v>4224.4160280305232</v>
-      </c>
-      <c r="FB20" s="1">
-        <f t="shared" si="123"/>
-        <v>4182.1718677502176</v>
-      </c>
-      <c r="FC20" s="1">
-        <f t="shared" si="123"/>
-        <v>4140.3501490727158</v>
-      </c>
-      <c r="FD20" s="1">
-        <f t="shared" si="123"/>
-        <v>4098.9466475819881</v>
-      </c>
-      <c r="FE20" s="1">
-        <f t="shared" si="123"/>
-        <v>4057.9571811061683</v>
-      </c>
-      <c r="FF20" s="1">
-        <f t="shared" si="123"/>
-        <v>4017.3776092951066</v>
-      </c>
-      <c r="FG20" s="1">
-        <f t="shared" si="123"/>
-        <v>3977.2038332021557</v>
-      </c>
-      <c r="FH20" s="1">
-        <f t="shared" si="123"/>
-        <v>3937.4317948701341</v>
-      </c>
-      <c r="FI20" s="1">
-        <f t="shared" si="123"/>
-        <v>3898.0574769214327</v>
-      </c>
-      <c r="FJ20" s="1">
-        <f t="shared" si="123"/>
-        <v>3859.0769021522183</v>
-      </c>
-      <c r="FK20" s="1">
-        <f t="shared" si="123"/>
-        <v>3820.4861331306961</v>
-      </c>
-      <c r="FL20" s="1">
-        <f t="shared" si="123"/>
-        <v>3782.2812717993893</v>
-      </c>
-      <c r="FM20" s="1">
-        <f t="shared" si="123"/>
-        <v>3744.4584590813952</v>
-      </c>
-      <c r="FN20" s="1">
-        <f t="shared" si="123"/>
-        <v>3707.0138744905812</v>
-      </c>
-      <c r="FO20" s="1">
-        <f t="shared" si="123"/>
-        <v>3669.9437357456754</v>
-      </c>
-      <c r="FP20" s="1">
-        <f t="shared" si="123"/>
-        <v>3633.2442983882188</v>
-      </c>
-      <c r="FQ20" s="1">
-        <f t="shared" si="123"/>
-        <v>3596.9118554043366</v>
-      </c>
-      <c r="FR20" s="1">
-        <f t="shared" si="123"/>
-        <v>3560.9427368502934</v>
-      </c>
-      <c r="FS20" s="1">
-        <f t="shared" si="123"/>
-        <v>3525.3333094817904</v>
-      </c>
-      <c r="FT20" s="1">
-        <f t="shared" si="123"/>
-        <v>3490.0799763869722</v>
-      </c>
-      <c r="FU20" s="1">
-        <f t="shared" si="123"/>
-        <v>3455.1791766231026</v>
-      </c>
-      <c r="FV20" s="1">
-        <f t="shared" si="123"/>
-        <v>3420.6273848568717</v>
-      </c>
-      <c r="FW20" s="1">
-        <f t="shared" si="123"/>
-        <v>3386.4211110083029</v>
-      </c>
-      <c r="FX20" s="1">
-        <f t="shared" si="123"/>
-        <v>3352.5568998982199</v>
-      </c>
-      <c r="FY20" s="1">
-        <f t="shared" si="123"/>
-        <v>3319.0313308992377</v>
-      </c>
-      <c r="FZ20" s="1">
-        <f t="shared" si="123"/>
-        <v>3285.8410175902454</v>
-      </c>
-      <c r="GA20" s="1">
-        <f t="shared" si="123"/>
-        <v>3252.982607414343</v>
-      </c>
-      <c r="GB20" s="1">
-        <f t="shared" si="123"/>
-        <v>3220.4527813401996</v>
-      </c>
-      <c r="GC20" s="1">
-        <f t="shared" si="123"/>
-        <v>3188.2482535267977</v>
-      </c>
-      <c r="GD20" s="1">
-        <f t="shared" si="123"/>
-        <v>3156.3657709915296</v>
-      </c>
-      <c r="GE20" s="1">
-        <f t="shared" si="123"/>
-        <v>3124.8021132816143</v>
-      </c>
-      <c r="GF20" s="1">
-        <f t="shared" si="123"/>
-        <v>3093.5540921487982</v>
-      </c>
-      <c r="GG20" s="1">
-        <f t="shared" si="123"/>
-        <v>3062.61855122731</v>
-      </c>
-      <c r="GH20" s="1">
-        <f t="shared" si="123"/>
-        <v>3031.9923657150371</v>
-      </c>
-      <c r="GI20" s="1">
-        <f t="shared" si="123"/>
-        <v>3001.6724420578867</v>
-      </c>
-      <c r="GJ20" s="1">
-        <f t="shared" ref="GJ20:GN20" si="124">GI20*(1+$BM$30)</f>
-        <v>2971.6557176373076</v>
-      </c>
-      <c r="GK20" s="1">
-        <f t="shared" si="124"/>
-        <v>2941.9391604609345</v>
-      </c>
-      <c r="GL20" s="1">
-        <f t="shared" si="124"/>
-        <v>2912.5197688563253</v>
-      </c>
-      <c r="GM20" s="1">
-        <f t="shared" si="124"/>
-        <v>2883.394571167762</v>
-      </c>
-      <c r="GN20" s="1">
-        <f t="shared" si="124"/>
-        <v>2854.5606254560844</v>
+        <v>2769.2368394485943</v>
       </c>
     </row>
     <row r="21" spans="2:196" x14ac:dyDescent="0.3">
@@ -5381,10 +5370,10 @@
         <v>952</v>
       </c>
       <c r="AK21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="AL21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
@@ -5415,186 +5404,186 @@
         <v>961</v>
       </c>
       <c r="AZ21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BA21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BB21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BC21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BD21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BE21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BF21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BG21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BH21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BI21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="BJ21" s="5">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="22" spans="2:196" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:P22" si="125">C20/C21</f>
+        <f t="shared" ref="C22:P22" si="123">C20/C21</f>
         <v>1.0989010989010989E-3</v>
       </c>
       <c r="D22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>5.054945054945055E-2</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.11758241758241758</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.22637362637362637</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.37802197802197801</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.32857142857142857</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.39780219780219778</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.43076923076923079</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.1</v>
       </c>
       <c r="M22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>-0.11978021978021978</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>-0.2725274725274725</v>
       </c>
       <c r="O22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>0.10879120879120879</v>
       </c>
       <c r="P22" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>2.8846153846153846</v>
       </c>
       <c r="Q22" s="7">
-        <f t="shared" ref="Q22:S22" si="126">Q20/Q21</f>
+        <f t="shared" ref="Q22:S22" si="124">Q20/Q21</f>
         <v>1.2296926454445665</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.29308452250274425</v>
       </c>
       <c r="S22" s="7">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.50922909880564604</v>
       </c>
       <c r="T22" s="7">
-        <f t="shared" ref="T22" si="127">T20/T21</f>
+        <f t="shared" ref="T22" si="125">T20/T21</f>
         <v>0.57341907824222937</v>
       </c>
       <c r="U22" s="7">
-        <f t="shared" ref="U22" si="128">U20/U21</f>
+        <f t="shared" ref="U22" si="126">U20/U21</f>
         <v>0.47755102040816327</v>
       </c>
       <c r="V22" s="7">
-        <f t="shared" ref="V22:W22" si="129">V20/V21</f>
+        <f t="shared" ref="V22:W22" si="127">V20/V21</f>
         <v>-2.8397565922920892E-2</v>
       </c>
       <c r="W22" s="7">
-        <f t="shared" si="129"/>
+        <f t="shared" si="127"/>
         <v>3.0010718113612004E-2</v>
       </c>
       <c r="X22" s="7">
-        <f t="shared" ref="X22" si="130">X20/X21</f>
+        <f t="shared" ref="X22" si="128">X20/X21</f>
         <v>6.820461384152457E-2</v>
       </c>
       <c r="Y22" s="7">
-        <f t="shared" ref="Y22" si="131">Y20/Y21</f>
+        <f t="shared" ref="Y22" si="129">Y20/Y21</f>
         <v>0.21063189568706117</v>
       </c>
       <c r="Z22" s="7">
-        <f t="shared" ref="Z22:AA22" si="132">Z20/Z21</f>
+        <f t="shared" ref="Z22:AA22" si="130">Z20/Z21</f>
         <v>-9.959349593495935E-2</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.20306122448979591</v>
       </c>
       <c r="AB22" s="7">
-        <f t="shared" ref="AB22" si="133">AB20/AB21</f>
+        <f t="shared" ref="AB22" si="131">AB20/AB21</f>
         <v>1.2994871794871794</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" ref="AC22" si="134">AC20/AC21</f>
+        <f t="shared" ref="AC22" si="132">AC20/AC21</f>
         <v>1.2592592592592593</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" ref="AD22:AE22" si="135">AD20/AD21</f>
+        <f t="shared" ref="AD22:AE22" si="133">AD20/AD21</f>
         <v>1.4907216494845361</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" si="135"/>
+        <f t="shared" si="133"/>
         <v>1.5804123711340206</v>
       </c>
       <c r="AF22" s="7">
-        <f t="shared" ref="AF22" si="136">AF20/AF21</f>
+        <f t="shared" ref="AF22" si="134">AF20/AF21</f>
         <v>1.4823651452282158</v>
       </c>
       <c r="AG22" s="7">
-        <f t="shared" ref="AG22" si="137">AG20/AG21</f>
+        <f t="shared" ref="AG22" si="135">AG20/AG21</f>
         <v>1.5972803347280335</v>
       </c>
       <c r="AH22" s="7">
-        <f t="shared" ref="AH22:AL22" si="138">AH20/AH21</f>
+        <f t="shared" ref="AH22:AL22" si="136">AH20/AH21</f>
         <v>1.777315296566077</v>
       </c>
       <c r="AI22" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>1.6052083333333333</v>
       </c>
       <c r="AJ22" s="7">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>1.9821428571428572</v>
       </c>
       <c r="AK22" s="7">
-        <f t="shared" si="138"/>
-        <v>1.9676365126050417</v>
+        <f t="shared" si="136"/>
+        <v>2.2004219409282699</v>
       </c>
       <c r="AL22" s="7">
-        <f t="shared" si="138"/>
-        <v>1.8851158298319339</v>
+        <f t="shared" si="136"/>
+        <v>2.2849691835443036</v>
       </c>
       <c r="AM22" s="7"/>
       <c r="AN22" s="7"/>
@@ -5617,447 +5606,447 @@
         <v>4.4698133918770582</v>
       </c>
       <c r="AV22" s="7">
-        <f t="shared" ref="AV22:BE22" si="139">AV20/AV21</f>
+        <f t="shared" ref="AV22:BE22" si="137">AV20/AV21</f>
         <v>1.8732251521298176</v>
       </c>
       <c r="AW22" s="7">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>0.21138211382113822</v>
       </c>
       <c r="AX22" s="7">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>4.2639175257731958</v>
       </c>
       <c r="AY22" s="7">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>6.4484911550468258</v>
       </c>
       <c r="AZ22" s="7">
-        <f t="shared" si="139"/>
-        <v>6.5146851155462251</v>
+        <f t="shared" si="137"/>
+        <v>6.8369206603375563</v>
       </c>
       <c r="BA22" s="7">
-        <f t="shared" si="139"/>
-        <v>8.2895363771008483</v>
+        <f t="shared" si="137"/>
+        <v>8.0455443934599185</v>
       </c>
       <c r="BB22" s="7">
-        <f t="shared" si="139"/>
-        <v>9.1140383131932854</v>
+        <f t="shared" si="137"/>
+        <v>8.8605026476793292</v>
       </c>
       <c r="BC22" s="7">
-        <f t="shared" si="139"/>
-        <v>9.4389247294025242</v>
+        <f t="shared" si="137"/>
+        <v>9.1782247761215228</v>
       </c>
       <c r="BD22" s="7">
-        <f t="shared" si="139"/>
-        <v>9.8136275058026232</v>
+        <f t="shared" si="137"/>
+        <v>9.5439665146917392</v>
       </c>
       <c r="BE22" s="7">
-        <f t="shared" si="139"/>
-        <v>10.192082039145861</v>
+        <f t="shared" si="137"/>
+        <v>9.9127428955225767</v>
       </c>
       <c r="BF22" s="7">
-        <f t="shared" ref="BF22:BJ22" si="140">BF20/BF21</f>
-        <v>10.450021775877127</v>
+        <f t="shared" ref="BF22:BJ22" si="138">BF20/BF21</f>
+        <v>10.167187971058123</v>
       </c>
       <c r="BG22" s="7">
-        <f t="shared" si="140"/>
-        <v>10.711673028604615</v>
+        <f t="shared" si="138"/>
+        <v>10.425245217716707</v>
       </c>
       <c r="BH22" s="7">
-        <f t="shared" si="140"/>
-        <v>10.978285840707864</v>
+        <f t="shared" si="138"/>
+        <v>10.688214969718198</v>
       </c>
       <c r="BI22" s="7">
-        <f t="shared" si="140"/>
-        <v>11.250545624972458</v>
+        <f t="shared" si="138"/>
+        <v>10.956809027329449</v>
       </c>
       <c r="BJ22" s="7">
-        <f t="shared" si="140"/>
-        <v>11.528856846000011</v>
+        <f t="shared" si="138"/>
+        <v>11.231446352739171</v>
       </c>
     </row>
     <row r="24" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="W24" s="8">
-        <f t="shared" ref="W24:W25" si="141">W3/S3-1</f>
+        <f t="shared" ref="W24:W25" si="139">W3/S3-1</f>
         <v>0.2384393063583814</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" ref="X24:X25" si="142">X3/T3-1</f>
+        <f t="shared" ref="X24:X25" si="140">X3/T3-1</f>
         <v>0.2078119715928306</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" ref="Y24:Y25" si="143">Y3/U3-1</f>
+        <f t="shared" ref="Y24:Y25" si="141">Y3/U3-1</f>
         <v>0.13387678319485818</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" ref="Z24:Z25" si="144">Z3/V3-1</f>
+        <f t="shared" ref="Z24:Z25" si="142">Z3/V3-1</f>
         <v>0.1407439953134153</v>
       </c>
       <c r="AA24" s="8">
-        <f t="shared" ref="AA24:AA25" si="145">AA3/W3-1</f>
+        <f t="shared" ref="AA24:AA25" si="143">AA3/W3-1</f>
         <v>0.11464410735122521</v>
       </c>
       <c r="AB24" s="8">
-        <f t="shared" ref="AB24:AB25" si="146">AB3/X3-1</f>
+        <f t="shared" ref="AB24:AB25" si="144">AB3/X3-1</f>
         <v>0.12081758364832695</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" ref="AC24:AC25" si="147">AC3/Y3-1</f>
+        <f t="shared" ref="AC24:AC25" si="145">AC3/Y3-1</f>
         <v>0.12553573897414627</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" ref="AD24:AD25" si="148">AD3/Z3-1</f>
+        <f t="shared" ref="AD24:AD25" si="146">AD3/Z3-1</f>
         <v>0.12312235203492095</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" ref="AE24:AE25" si="149">AE3/AA3-1</f>
+        <f t="shared" ref="AE24:AE25" si="147">AE3/AA3-1</f>
         <v>0.12339701648783041</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" ref="AF24:AF25" si="150">AF3/AB3-1</f>
+        <f t="shared" ref="AF24:AF25" si="148">AF3/AB3-1</f>
         <v>9.4678990756932313E-2</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" ref="AG24:AG25" si="151">AG3/AC3-1</f>
+        <f t="shared" ref="AG24:AG25" si="149">AG3/AC3-1</f>
         <v>9.0652254022847378E-2</v>
       </c>
       <c r="AH24" s="8">
-        <f t="shared" ref="AH24:AH25" si="152">AH3/AD3-1</f>
+        <f t="shared" ref="AH24:AH25" si="150">AH3/AD3-1</f>
         <v>8.0361225422953764E-2</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" ref="AI24:AI25" si="153">AI3/AE3-1</f>
+        <f t="shared" ref="AI24:AI25" si="151">AI3/AE3-1</f>
         <v>8.2935352358765257E-2</v>
       </c>
       <c r="AJ24" s="8">
-        <f t="shared" ref="AJ24:AJ26" si="154">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ24:AJ26" si="152">AJ3/AF3-1</f>
         <v>0.10565951620264724</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" ref="AK24:AK26" si="155">AK3/AG3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AK24:AK26" si="153">AK3/AG3-1</f>
+        <v>9.5393625408266791E-2</v>
       </c>
       <c r="AL24" s="8">
-        <f t="shared" ref="AL24:AL26" si="156">AL3/AH3-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AL24:AL26" si="154">AL3/AH3-1</f>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AW24" s="8">
-        <f t="shared" ref="AW24:AW25" si="157">AW3/AV3-1</f>
+        <f t="shared" ref="AW24:AW25" si="155">AW3/AV3-1</f>
         <v>0.17698827919049354</v>
       </c>
       <c r="AX24" s="8">
-        <f t="shared" ref="AX24:AX25" si="158">AX3/AW3-1</f>
+        <f t="shared" ref="AX24:AX25" si="156">AX3/AW3-1</f>
         <v>0.12115364735880907</v>
       </c>
       <c r="AY24" s="8">
-        <f t="shared" ref="AY24:AY25" si="159">AY3/AX3-1</f>
+        <f t="shared" ref="AY24:AY25" si="157">AY3/AX3-1</f>
         <v>9.6566985278298656E-2</v>
       </c>
       <c r="AZ24" s="8">
-        <f t="shared" ref="AT24:BE26" si="160">AZ3/AY3-1</f>
-        <v>8.9337425376271762E-2</v>
+        <f t="shared" ref="AT24:BE26" si="158">AZ3/AY3-1</f>
+        <v>9.8786681241066265E-2</v>
       </c>
       <c r="BA24" s="8">
-        <f t="shared" ref="BA24:BA25" si="161">BA3/AZ3-1</f>
+        <f t="shared" ref="BA24:BA25" si="159">BA3/AZ3-1</f>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BB24" s="8">
-        <f t="shared" ref="BB24:BB25" si="162">BB3/BA3-1</f>
+        <f t="shared" ref="BB24:BB25" si="160">BB3/BA3-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BC24" s="8">
-        <f t="shared" ref="BC24:BC25" si="163">BC3/BB3-1</f>
+        <f t="shared" ref="BC24:BC25" si="161">BC3/BB3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BD24" s="8">
-        <f t="shared" ref="BD24:BD25" si="164">BD3/BC3-1</f>
+        <f t="shared" ref="BD24:BD25" si="162">BD3/BC3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE24" s="8">
-        <f t="shared" ref="BE24:BE25" si="165">BE3/BD3-1</f>
+        <f t="shared" ref="BE24:BE25" si="163">BE3/BD3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF24" s="8">
-        <f t="shared" ref="BF24:BF25" si="166">BF3/BE3-1</f>
+        <f t="shared" ref="BF24:BF25" si="164">BF3/BE3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG24" s="8">
-        <f t="shared" ref="BG24:BG25" si="167">BG3/BF3-1</f>
+        <f t="shared" ref="BG24:BG25" si="165">BG3/BF3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH24" s="8">
-        <f t="shared" ref="BH24:BH25" si="168">BH3/BG3-1</f>
+        <f t="shared" ref="BH24:BH25" si="166">BH3/BG3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BI24" s="8">
-        <f t="shared" ref="BI24:BI25" si="169">BI3/BH3-1</f>
+        <f t="shared" ref="BI24:BI25" si="167">BI3/BH3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ24" s="8">
-        <f t="shared" ref="BJ24:BJ25" si="170">BJ3/BI3-1</f>
+        <f t="shared" ref="BJ24:BJ25" si="168">BJ3/BI3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="25" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="W25" s="8">
+        <f t="shared" si="139"/>
+        <v>0.29976580796252938</v>
+      </c>
+      <c r="X25" s="8">
+        <f t="shared" si="140"/>
+        <v>0.35446009389671351</v>
+      </c>
+      <c r="Y25" s="8">
         <f t="shared" si="141"/>
-        <v>0.29976580796252938</v>
-      </c>
-      <c r="X25" s="8">
+        <v>0.24793388429752072</v>
+      </c>
+      <c r="Z25" s="8">
         <f t="shared" si="142"/>
-        <v>0.35446009389671351</v>
-      </c>
-      <c r="Y25" s="8">
+        <v>0.19477911646586343</v>
+      </c>
+      <c r="AA25" s="8">
         <f t="shared" si="143"/>
-        <v>0.24793388429752072</v>
-      </c>
-      <c r="Z25" s="8">
+        <v>9.0090090090090058E-2</v>
+      </c>
+      <c r="AB25" s="8">
         <f t="shared" si="144"/>
-        <v>0.19477911646586343</v>
-      </c>
-      <c r="AA25" s="8">
+        <v>3.4662045060658508E-2</v>
+      </c>
+      <c r="AC25" s="8">
         <f t="shared" si="145"/>
-        <v>9.0090090090090058E-2</v>
-      </c>
-      <c r="AB25" s="8">
+        <v>-4.1390728476821237E-2</v>
+      </c>
+      <c r="AD25" s="8">
         <f t="shared" si="146"/>
-        <v>3.4662045060658508E-2</v>
-      </c>
-      <c r="AC25" s="8">
+        <v>-9.4117647058823528E-2</v>
+      </c>
+      <c r="AE25" s="8">
         <f t="shared" si="147"/>
-        <v>-4.1390728476821237E-2</v>
-      </c>
-      <c r="AD25" s="8">
+        <v>-9.4214876033057893E-2</v>
+      </c>
+      <c r="AF25" s="8">
         <f t="shared" si="148"/>
-        <v>-9.4117647058823528E-2</v>
-      </c>
-      <c r="AE25" s="8">
+        <v>-6.0301507537688481E-2</v>
+      </c>
+      <c r="AG25" s="8">
         <f t="shared" si="149"/>
-        <v>-9.4214876033057893E-2</v>
-      </c>
-      <c r="AF25" s="8">
+        <v>-2.4179620034542326E-2</v>
+      </c>
+      <c r="AH25" s="8">
         <f t="shared" si="150"/>
-        <v>-6.0301507537688481E-2</v>
-      </c>
-      <c r="AG25" s="8">
+        <v>5.5658627087198376E-3</v>
+      </c>
+      <c r="AI25" s="8">
         <f t="shared" si="151"/>
-        <v>-2.4179620034542326E-2</v>
-      </c>
-      <c r="AH25" s="8">
+        <v>-2.9197080291970767E-2</v>
+      </c>
+      <c r="AJ25" s="8">
         <f t="shared" si="152"/>
-        <v>5.5658627087198376E-3</v>
-      </c>
-      <c r="AI25" s="8">
+        <v>-2.6737967914438499E-2</v>
+      </c>
+      <c r="AK25" s="8">
         <f t="shared" si="153"/>
-        <v>-2.9197080291970767E-2</v>
-      </c>
-      <c r="AJ25" s="8">
+        <v>-5.663716814159292E-2</v>
+      </c>
+      <c r="AL25" s="8">
         <f t="shared" si="154"/>
-        <v>-2.6737967914438499E-2</v>
-      </c>
-      <c r="AK25" s="8">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AW25" s="8">
         <f t="shared" si="155"/>
+        <v>0.27029972752043596</v>
+      </c>
+      <c r="AX25" s="8">
+        <f t="shared" si="156"/>
+        <v>-4.7190047190047713E-3</v>
+      </c>
+      <c r="AY25" s="8">
+        <f t="shared" si="157"/>
+        <v>-4.482758620689653E-2</v>
+      </c>
+      <c r="AZ25" s="8">
+        <f t="shared" si="158"/>
+        <v>-2.3537906137184095E-2</v>
+      </c>
+      <c r="BA25" s="8">
+        <f t="shared" si="159"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AL25" s="8">
-        <f t="shared" si="156"/>
+      <c r="BB25" s="8">
+        <f t="shared" si="160"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW25" s="8">
-        <f t="shared" si="157"/>
-        <v>0.27029972752043596</v>
-      </c>
-      <c r="AX25" s="8">
-        <f t="shared" si="158"/>
-        <v>-4.7190047190047713E-3</v>
-      </c>
-      <c r="AY25" s="8">
-        <f t="shared" si="159"/>
-        <v>-4.482758620689653E-2</v>
-      </c>
-      <c r="AZ25" s="8">
-        <f t="shared" si="160"/>
-        <v>-8.9936823104692643E-3</v>
-      </c>
-      <c r="BA25" s="8">
+      <c r="BC25" s="8">
         <f t="shared" si="161"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BB25" s="8">
+      <c r="BD25" s="8">
         <f t="shared" si="162"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BC25" s="8">
+      <c r="BE25" s="8">
         <f t="shared" si="163"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BD25" s="8">
+      <c r="BF25" s="8">
         <f t="shared" si="164"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BE25" s="8">
+      <c r="BG25" s="8">
         <f t="shared" si="165"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BF25" s="8">
+      <c r="BH25" s="8">
         <f t="shared" si="166"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BG25" s="8">
+      <c r="BI25" s="8">
         <f t="shared" si="167"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH25" s="8">
+      <c r="BJ25" s="8">
         <f t="shared" si="168"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BI25" s="8">
-        <f t="shared" si="169"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BJ25" s="8">
-        <f t="shared" si="170"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
     <row r="26" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26" s="8">
         <f>G5/C5-1</f>
         <v>0.25406758448060085</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" ref="H26:R26" si="171">H5/D5-1</f>
+        <f t="shared" ref="H26:R26" si="169">H5/D5-1</f>
         <v>0.27318587504850611</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.25583117363939278</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.25759162303664929</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.24318030605455765</v>
       </c>
       <c r="L26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.21822615056385253</v>
       </c>
       <c r="M26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.33048349056603765</v>
       </c>
       <c r="N26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.34637801831806825</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.30184640085630177</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.28871653740305225</v>
       </c>
       <c r="Q26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.20075337912696645</v>
       </c>
       <c r="R26" s="8">
-        <f t="shared" si="171"/>
+        <f t="shared" si="169"/>
         <v>0.19913419913419905</v>
       </c>
       <c r="S26" s="8">
-        <f t="shared" ref="S26" si="172">S5/O5-1</f>
+        <f t="shared" ref="S26" si="170">S5/O5-1</f>
         <v>0.225693730729702</v>
       </c>
       <c r="T26" s="8">
-        <f t="shared" ref="T26" si="173">T5/P5-1</f>
+        <f t="shared" ref="T26" si="171">T5/P5-1</f>
         <v>0.23082896524946617</v>
       </c>
       <c r="U26" s="8">
-        <f t="shared" ref="U26" si="174">U5/Q5-1</f>
+        <f t="shared" ref="U26" si="172">U5/Q5-1</f>
         <v>0.26646982838162026</v>
       </c>
       <c r="V26" s="8">
-        <f t="shared" ref="V26" si="175">V5/R5-1</f>
+        <f t="shared" ref="V26" si="173">V5/R5-1</f>
         <v>0.25941206807632811</v>
       </c>
       <c r="W26" s="8">
-        <f t="shared" ref="W26" si="176">W5/S5-1</f>
+        <f t="shared" ref="W26" si="174">W5/S5-1</f>
         <v>0.24283078987087037</v>
       </c>
       <c r="X26" s="8">
-        <f t="shared" ref="X26" si="177">X5/T5-1</f>
+        <f t="shared" ref="X26" si="175">X5/T5-1</f>
         <v>0.21766561514195581</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" ref="Y26" si="178">Y5/U5-1</f>
+        <f t="shared" ref="Y26" si="176">Y5/U5-1</f>
         <v>0.14192044295497586</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" ref="Z26" si="179">Z5/V5-1</f>
+        <f t="shared" ref="Z26" si="177">Z5/V5-1</f>
         <v>0.14441714441714448</v>
       </c>
       <c r="AA26" s="8">
-        <f t="shared" ref="AA26" si="180">AA5/W5-1</f>
+        <f t="shared" ref="AA26" si="178">AA5/W5-1</f>
         <v>0.11280528943462431</v>
       </c>
       <c r="AB26" s="8">
-        <f t="shared" ref="AB26" si="181">AB5/X5-1</f>
+        <f t="shared" ref="AB26" si="179">AB5/X5-1</f>
         <v>0.11437823834196892</v>
       </c>
       <c r="AC26" s="8">
-        <f t="shared" ref="AC26" si="182">AC5/Y5-1</f>
+        <f t="shared" ref="AC26" si="180">AC5/Y5-1</f>
         <v>0.11267066479520227</v>
       </c>
       <c r="AD26" s="8">
-        <f t="shared" ref="AD26" si="183">AD5/Z5-1</f>
+        <f t="shared" ref="AD26" si="181">AD5/Z5-1</f>
         <v>0.10770515267175562</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" ref="AE26" si="184">AE5/AA5-1</f>
+        <f t="shared" ref="AE26" si="182">AE5/AA5-1</f>
         <v>0.10743300594155447</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" ref="AF26" si="185">AF5/AB5-1</f>
+        <f t="shared" ref="AF26" si="183">AF5/AB5-1</f>
         <v>8.3924212484017158E-2</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" ref="AG26" si="186">AG5/AC5-1</f>
+        <f t="shared" ref="AG26" si="184">AG5/AC5-1</f>
         <v>8.3027522935779752E-2</v>
       </c>
       <c r="AH26" s="8">
-        <f t="shared" ref="AH26" si="187">AH5/AD5-1</f>
+        <f t="shared" ref="AH26" si="185">AH5/AD5-1</f>
         <v>7.6020243350920724E-2</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" ref="AI26" si="188">AI5/AE5-1</f>
+        <f t="shared" ref="AI26" si="186">AI5/AE5-1</f>
         <v>7.6207160845286337E-2</v>
       </c>
       <c r="AJ26" s="8">
+        <f t="shared" si="152"/>
+        <v>9.7694369973190254E-2</v>
+      </c>
+      <c r="AK26" s="8">
+        <f t="shared" si="153"/>
+        <v>8.6298178737822973E-2</v>
+      </c>
+      <c r="AL26" s="8">
         <f t="shared" si="154"/>
-        <v>9.7694369973190254E-2</v>
-      </c>
-      <c r="AK26" s="8">
-        <f t="shared" si="155"/>
-        <v>9.4615628970775134E-2</v>
-      </c>
-      <c r="AL26" s="8">
-        <f t="shared" si="156"/>
-        <v>6.674572200540374E-2</v>
+        <v>0.10511858300810584</v>
       </c>
       <c r="AM26" s="8"/>
       <c r="AN26" s="8"/>
@@ -6068,77 +6057,77 @@
         <v>0.26015180265654658</v>
       </c>
       <c r="AT26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>0.28730612859509108</v>
       </c>
       <c r="AU26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>0.24295239209264241</v>
       </c>
       <c r="AV26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>0.24656502917372491</v>
       </c>
       <c r="AW26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>0.18345160803261362</v>
       </c>
       <c r="AX26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>0.11179510079101806</v>
       </c>
       <c r="AY26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>8.7156094902028247E-2</v>
       </c>
       <c r="AZ26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BA26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BB26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BC26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BD26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BE26" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BF26" s="8">
-        <f t="shared" ref="BF26" si="189">BF5/BE5-1</f>
+        <f t="shared" ref="BF26" si="187">BF5/BE5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG26" s="8">
-        <f t="shared" ref="BG26" si="190">BG5/BF5-1</f>
+        <f t="shared" ref="BG26" si="188">BG5/BF5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH26" s="8">
-        <f t="shared" ref="BH26" si="191">BH5/BG5-1</f>
+        <f t="shared" ref="BH26" si="189">BH5/BG5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BI26" s="8">
-        <f t="shared" ref="BI26" si="192">BI5/BH5-1</f>
+        <f t="shared" ref="BI26" si="190">BI5/BH5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ26" s="8">
-        <f t="shared" ref="BJ26" si="193">BJ5/BI5-1</f>
+        <f t="shared" ref="BJ26" si="191">BJ5/BI5-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="27" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
@@ -6153,63 +6142,63 @@
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="8">
-        <f t="shared" ref="S27:AG27" si="194">(S3-S6)/S3</f>
+        <f t="shared" ref="S27:AG27" si="192">(S3-S6)/S3</f>
         <v>0.79732658959537572</v>
       </c>
       <c r="T27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.80622252282718976</v>
       </c>
       <c r="U27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.79071954851857662</v>
       </c>
       <c r="V27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.78676039835969536</v>
       </c>
       <c r="W27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.78996499416569432</v>
       </c>
       <c r="X27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.79140417191656165</v>
       </c>
       <c r="Y27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.79939167703580816</v>
       </c>
       <c r="Z27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.81512389266914875</v>
       </c>
       <c r="AA27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.80240774666317716</v>
       </c>
       <c r="AB27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.81076692480639523</v>
       </c>
       <c r="AC27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.80702616386193338</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.81927297668038412</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.81828771112405363</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.82245549977179366</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="194"/>
+        <f t="shared" si="192"/>
         <v>0.83094943124225706</v>
       </c>
       <c r="AH27" s="8">
@@ -6217,20 +6206,20 @@
         <v>0.83271611469685747</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" ref="AI27:AL27" si="195">(AI3-AI6)/AI3</f>
+        <f t="shared" ref="AI27:AL27" si="193">(AI3-AI6)/AI3</f>
         <v>0.82671829622458859</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="195"/>
+        <f t="shared" si="193"/>
         <v>0.83023735810113519</v>
       </c>
       <c r="AK27" s="8">
-        <f t="shared" si="195"/>
+        <f t="shared" si="193"/>
+        <v>0.82880937692782231</v>
+      </c>
+      <c r="AL27" s="8">
+        <f t="shared" si="193"/>
         <v>0.83</v>
-      </c>
-      <c r="AL27" s="8">
-        <f t="shared" si="195"/>
-        <v>0.83000000000000007</v>
       </c>
       <c r="AM27" s="8"/>
       <c r="AN27" s="8"/>
@@ -6240,24 +6229,24 @@
       <c r="AT27" s="8"/>
       <c r="AU27" s="8"/>
       <c r="AV27" s="8">
-        <f t="shared" ref="AV27:AY27" si="196">(AV3-AV6)/AV3</f>
+        <f t="shared" ref="AV27:AY27" si="194">(AV3-AV6)/AV3</f>
         <v>0.79482499898608916</v>
       </c>
       <c r="AW27" s="8">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>0.79942110885221052</v>
       </c>
       <c r="AX27" s="8">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>0.81015459323232009</v>
       </c>
       <c r="AY27" s="8">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>0.82628436895652901</v>
       </c>
       <c r="AZ27" s="8">
-        <f t="shared" ref="AZ27" si="197">(AZ3-AZ6)/AZ3</f>
-        <v>0.82927418157604738</v>
+        <f t="shared" ref="AZ27" si="195">(AZ3-AZ6)/AZ3</f>
+        <v>0.82898504244889681</v>
       </c>
       <c r="BA27" s="8"/>
       <c r="BB27" s="8"/>
@@ -6272,7 +6261,7 @@
     </row>
     <row r="28" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -6287,63 +6276,63 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="8">
-        <f t="shared" ref="S28:AG28" si="198">(S4-S7)/S4</f>
+        <f t="shared" ref="S28:AG28" si="196">(S4-S7)/S4</f>
         <v>-1.405152224824356E-2</v>
       </c>
       <c r="T28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-9.6244131455399062E-2</v>
       </c>
       <c r="U28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-5.1652892561983473E-2</v>
       </c>
       <c r="V28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-0.12048192771084337</v>
       </c>
       <c r="W28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-9.0090090090090086E-2</v>
       </c>
       <c r="X28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-0.10398613518197573</v>
       </c>
       <c r="Y28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-5.4635761589403975E-2</v>
       </c>
       <c r="Z28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-0.1092436974789916</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-1.6528925619834711E-2</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-1.6750418760469012E-3</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-8.6355785837651123E-3</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-5.1948051948051951E-2</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-9.8540145985401464E-2</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-7.4866310160427801E-2</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="198"/>
+        <f t="shared" si="196"/>
         <v>-6.9026548672566371E-2</v>
       </c>
       <c r="AH28" s="8">
@@ -6351,20 +6340,20 @@
         <v>-0.17343173431734318</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" ref="AI28:AL28" si="199">(AI4-AI7)/AI4</f>
+        <f t="shared" ref="AI28:AL28" si="197">(AI4-AI7)/AI4</f>
         <v>-0.22932330827067668</v>
       </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="199"/>
+        <f t="shared" si="197"/>
         <v>-9.3406593406593408E-2</v>
       </c>
       <c r="AK28" s="8">
-        <f t="shared" si="199"/>
-        <v>-8.0000000000000085E-2</v>
+        <f t="shared" si="197"/>
+        <v>-0.10694183864915573</v>
       </c>
       <c r="AL28" s="8">
-        <f t="shared" si="199"/>
-        <v>-0.14999999999999991</v>
+        <f t="shared" si="197"/>
+        <v>-0.14999999999999986</v>
       </c>
       <c r="AM28" s="8"/>
       <c r="AN28" s="8"/>
@@ -6374,24 +6363,24 @@
       <c r="AT28" s="8"/>
       <c r="AU28" s="8"/>
       <c r="AV28" s="8">
-        <f t="shared" ref="AV28:AY28" si="200">(AV4-AV7)/AV4</f>
+        <f t="shared" ref="AV28:AY28" si="198">(AV4-AV7)/AV4</f>
         <v>-7.1934604904632146E-2</v>
       </c>
       <c r="AW28" s="8">
-        <f t="shared" si="200"/>
+        <f t="shared" si="198"/>
         <v>-8.9232089232089237E-2</v>
       </c>
       <c r="AX28" s="8">
-        <f t="shared" si="200"/>
+        <f t="shared" si="198"/>
         <v>-1.896551724137931E-2</v>
       </c>
       <c r="AY28" s="8">
-        <f t="shared" si="200"/>
+        <f t="shared" si="198"/>
         <v>-0.10333935018050541</v>
       </c>
       <c r="AZ28" s="8">
-        <f t="shared" ref="AZ28" si="201">(AZ4-AZ7)/AZ4</f>
-        <v>-0.13695601688470763</v>
+        <f t="shared" ref="AZ28" si="199">(AZ4-AZ7)/AZ4</f>
+        <v>-0.14461605294291627</v>
       </c>
       <c r="BA28" s="8"/>
       <c r="BB28" s="8"/>
@@ -6406,463 +6395,463 @@
     </row>
     <row r="29" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" s="8">
         <f>C9/C5</f>
         <v>0.7284105131414268</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" ref="D29:R29" si="202">D9/D5</f>
+        <f t="shared" ref="D29:R29" si="200">D9/D5</f>
         <v>0.74000776096235932</v>
       </c>
       <c r="E29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.73565346168085899</v>
       </c>
       <c r="F29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.74240837696335082</v>
       </c>
       <c r="G29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.74484364604125086</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.74123742761353251</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.73791273584905659</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.7374410213710797</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.75541878512175542</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.75806855141356022</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.74872590294704189</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.74850546279117702</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.74224049331963005</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.74548631333721604</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.75</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="202"/>
+        <f t="shared" si="200"/>
         <v>0.74574522949974209</v>
       </c>
       <c r="S29" s="8">
-        <f t="shared" ref="S29:AL29" si="203">S9/S5</f>
+        <f t="shared" ref="S29:AL29" si="201">S9/S5</f>
         <v>0.73922522220358877</v>
       </c>
       <c r="T29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.74558359621451109</v>
       </c>
       <c r="U29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.73131283695177041</v>
       </c>
       <c r="V29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.72508872508872513</v>
       </c>
       <c r="W29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.72405883146673866</v>
       </c>
       <c r="X29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.72448186528497405</v>
       </c>
       <c r="Y29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.73357151971417633</v>
       </c>
       <c r="Z29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.74952290076335881</v>
       </c>
       <c r="AA29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.74233054444040258</v>
       </c>
       <c r="AB29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.75438800418458674</v>
       </c>
       <c r="AC29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.75286697247706424</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.76870894799181655</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.7632760319719698</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.76847184986595174</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.77710715798390517</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.77814470129090363</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.76955946688371146</v>
       </c>
       <c r="AJ29" s="8">
-        <f t="shared" si="203"/>
+        <f t="shared" si="201"/>
         <v>0.78096912856584599</v>
       </c>
       <c r="AK29" s="8">
-        <f t="shared" si="203"/>
-        <v>0.77976648238702595</v>
+        <f t="shared" si="201"/>
+        <v>0.78019300126718005</v>
       </c>
       <c r="AL29" s="8">
-        <f t="shared" si="203"/>
-        <v>0.77967428674886197</v>
+        <f t="shared" si="201"/>
+        <v>0.7809407657932983</v>
       </c>
       <c r="AM29" s="8"/>
       <c r="AN29" s="8"/>
       <c r="AO29" s="8"/>
       <c r="AP29" s="8"/>
       <c r="AR29" s="8">
-        <f t="shared" ref="AR29:BE29" si="204">AR9/AR5</f>
+        <f t="shared" ref="AR29:BE29" si="202">AR9/AR5</f>
         <v>0.7369070208728653</v>
       </c>
       <c r="AS29" s="8">
-        <f t="shared" si="204"/>
+        <f t="shared" si="202"/>
         <v>0.74017467248908297</v>
       </c>
       <c r="AT29" s="8">
-        <f t="shared" si="204"/>
+        <f t="shared" si="202"/>
         <v>0.75231021172066903</v>
       </c>
       <c r="AU29" s="8">
-        <f t="shared" si="204"/>
+        <f t="shared" si="202"/>
         <v>0.74411820063993972</v>
       </c>
       <c r="AV29" s="8">
-        <f t="shared" si="204"/>
+        <f t="shared" si="202"/>
         <v>0.75</v>
       </c>
       <c r="AW29" s="8">
-        <f t="shared" si="204"/>
+        <f t="shared" si="202"/>
         <v>0.73335034447563152</v>
       </c>
       <c r="AX29" s="8">
-        <f t="shared" si="204"/>
+        <f t="shared" si="202"/>
         <v>0.75497030725535763</v>
       </c>
       <c r="AY29" s="8">
-        <f t="shared" si="204"/>
+        <f t="shared" si="202"/>
         <v>0.77192241720543608</v>
       </c>
       <c r="AZ29" s="8">
-        <f t="shared" si="204"/>
-        <v>0.77265022517532311</v>
+        <f t="shared" si="202"/>
+        <v>0.77143473151981523</v>
       </c>
       <c r="BA29" s="8">
-        <f t="shared" si="204"/>
-        <v>0.78</v>
+        <f t="shared" si="202"/>
+        <v>0.77</v>
       </c>
       <c r="BB29" s="8">
-        <f t="shared" si="204"/>
-        <v>0.78</v>
+        <f t="shared" si="202"/>
+        <v>0.76999999999999991</v>
       </c>
       <c r="BC29" s="8">
-        <f t="shared" si="204"/>
-        <v>0.77999999999999992</v>
+        <f t="shared" si="202"/>
+        <v>0.76999999999999991</v>
       </c>
       <c r="BD29" s="8">
-        <f t="shared" si="204"/>
-        <v>0.78</v>
+        <f t="shared" si="202"/>
+        <v>0.77</v>
       </c>
       <c r="BE29" s="8">
-        <f t="shared" si="204"/>
-        <v>0.78</v>
+        <f t="shared" si="202"/>
+        <v>0.77000000000000013</v>
       </c>
       <c r="BF29" s="8">
-        <f t="shared" ref="BF29:BJ29" si="205">BF9/BF5</f>
-        <v>0.78000000000000014</v>
+        <f t="shared" ref="BF29:BJ29" si="203">BF9/BF5</f>
+        <v>0.77</v>
       </c>
       <c r="BG29" s="8">
-        <f t="shared" si="205"/>
-        <v>0.77999999999999992</v>
+        <f t="shared" si="203"/>
+        <v>0.77</v>
       </c>
       <c r="BH29" s="8">
-        <f t="shared" si="205"/>
-        <v>0.78</v>
+        <f t="shared" si="203"/>
+        <v>0.76999999999999991</v>
       </c>
       <c r="BI29" s="8">
-        <f t="shared" si="205"/>
-        <v>0.78</v>
+        <f t="shared" si="203"/>
+        <v>0.77</v>
       </c>
       <c r="BJ29" s="8">
-        <f t="shared" si="205"/>
-        <v>0.78</v>
+        <f t="shared" si="203"/>
+        <v>0.77</v>
       </c>
     </row>
     <row r="30" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="8">
         <f>C15/C5</f>
         <v>1.6687526074259491E-3</v>
       </c>
       <c r="D30" s="8">
-        <f t="shared" ref="D30:R30" si="206">D15/D5</f>
+        <f t="shared" ref="D30:R30" si="204">D15/D5</f>
         <v>3.2596041909196738E-2</v>
       </c>
       <c r="E30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>5.7386153276564232E-2</v>
       </c>
       <c r="F30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>7.3647469458987785E-2</v>
       </c>
       <c r="G30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>6.35395874916833E-2</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>3.505028954587016E-2</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>2.7122641509433963E-2</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>3.8023868998057174E-2</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>5.6194808670056197E-2</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>1.451088316237178E-2</v>
       </c>
       <c r="M30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>1.4402836250830933E-2</v>
       </c>
       <c r="N30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>-7.4211502782931356E-3</v>
       </c>
       <c r="O30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>-2.8776978417266189E-2</v>
       </c>
       <c r="P30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>3.4556396816152204E-2</v>
       </c>
       <c r="Q30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>4.8579073629821001E-2</v>
       </c>
       <c r="R30" s="8">
-        <f t="shared" si="206"/>
+        <f t="shared" si="204"/>
         <v>3.3178614406051229E-2</v>
       </c>
       <c r="S30" s="8">
-        <f t="shared" ref="S30:AL30" si="207">S15/S5</f>
+        <f t="shared" ref="S30:AL30" si="205">S15/S5</f>
         <v>5.9366090893845383E-2</v>
       </c>
       <c r="T30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>5.2365930599369087E-2</v>
       </c>
       <c r="U30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>5.5369371994754479E-3</v>
       </c>
       <c r="V30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>-2.4024024024024024E-2</v>
       </c>
       <c r="W30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>2.698691134799622E-3</v>
       </c>
       <c r="X30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="Y30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>5.8695929564884522E-2</v>
       </c>
       <c r="Z30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>4.2581106870229007E-2</v>
       </c>
       <c r="AA30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>4.9957560324966656E-2</v>
       </c>
       <c r="AB30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.17156805765430663</v>
       </c>
       <c r="AC30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.17213302752293577</v>
       </c>
       <c r="AD30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.17465274038979217</v>
       </c>
       <c r="AE30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.18712361765027921</v>
       </c>
       <c r="AF30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.1912064343163539</v>
       </c>
       <c r="AG30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.20044472681067343</v>
       </c>
       <c r="AH30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.18212748924246974</v>
       </c>
       <c r="AI30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.19757859395665886</v>
       </c>
       <c r="AJ30" s="8">
-        <f t="shared" si="207"/>
+        <f t="shared" si="205"/>
         <v>0.2278233685033216</v>
       </c>
       <c r="AK30" s="8">
-        <f t="shared" si="207"/>
-        <v>0.21488437782646755</v>
+        <f t="shared" si="205"/>
+        <v>0.21327614777268739</v>
       </c>
       <c r="AL30" s="8">
-        <f t="shared" si="207"/>
-        <v>0.19922847019556314</v>
+        <f t="shared" si="205"/>
+        <v>0.2333371636580959</v>
       </c>
       <c r="AM30" s="8"/>
       <c r="AN30" s="8"/>
       <c r="AO30" s="8"/>
       <c r="AP30" s="8"/>
       <c r="AR30" s="8">
-        <f t="shared" ref="AR30:BE30" si="208">AR15/AR5</f>
+        <f t="shared" ref="AR30:BE30" si="206">AR15/AR5</f>
         <v>4.3074003795066415E-2</v>
       </c>
       <c r="AS30" s="8">
-        <f t="shared" si="208"/>
+        <f t="shared" si="206"/>
         <v>4.0280078301460624E-2</v>
       </c>
       <c r="AT30" s="8">
-        <f t="shared" si="208"/>
+        <f t="shared" si="206"/>
         <v>1.7370452684524505E-2</v>
       </c>
       <c r="AU30" s="8">
-        <f t="shared" si="208"/>
+        <f t="shared" si="206"/>
         <v>2.1409749670619236E-2</v>
       </c>
       <c r="AV30" s="8">
-        <f t="shared" si="208"/>
+        <f t="shared" si="206"/>
         <v>3.5897629473048469E-2</v>
       </c>
       <c r="AW30" s="8">
-        <f t="shared" si="208"/>
+        <f t="shared" si="206"/>
         <v>3.2852768563409032E-2</v>
       </c>
       <c r="AX30" s="8">
-        <f t="shared" si="208"/>
+        <f t="shared" si="206"/>
         <v>0.14375878589666352</v>
       </c>
       <c r="AY30" s="8">
-        <f t="shared" si="208"/>
+        <f t="shared" si="206"/>
         <v>0.19013062409288825</v>
       </c>
       <c r="AZ30" s="8">
-        <f t="shared" si="208"/>
-        <v>0.19232167085317689</v>
+        <f t="shared" si="206"/>
+        <v>0.19517926395427296</v>
       </c>
       <c r="BA30" s="8">
-        <f t="shared" si="208"/>
-        <v>0.22288340708775037</v>
+        <f t="shared" si="206"/>
+        <v>0.20886004348090503</v>
       </c>
       <c r="BB30" s="8">
-        <f t="shared" si="208"/>
-        <v>0.23636653457996953</v>
+        <f t="shared" si="206"/>
+        <v>0.22235270776635074</v>
       </c>
       <c r="BC30" s="8">
-        <f t="shared" si="208"/>
-        <v>0.23805237997351739</v>
+        <f t="shared" si="206"/>
+        <v>0.22404180204795479</v>
       </c>
       <c r="BD30" s="8">
-        <f t="shared" si="208"/>
-        <v>0.24067820597713691</v>
+        <f t="shared" si="206"/>
+        <v>0.22662735712663371</v>
       </c>
       <c r="BE30" s="8">
-        <f t="shared" si="208"/>
-        <v>0.24303618200708041</v>
+        <f t="shared" si="206"/>
+        <v>0.22893625343859053</v>
       </c>
       <c r="BF30" s="8">
-        <f t="shared" ref="BF30:BJ30" si="209">BF15/BF5</f>
-        <v>0.24458972997180639</v>
+        <f t="shared" ref="BF30:BJ30" si="207">BF15/BF5</f>
+        <v>0.23046975731283434</v>
       </c>
       <c r="BG30" s="8">
-        <f t="shared" si="209"/>
-        <v>0.24607200829376613</v>
+        <f t="shared" si="207"/>
+        <v>0.23193006084151382</v>
       </c>
       <c r="BH30" s="8">
-        <f t="shared" si="209"/>
-        <v>0.24751228448493887</v>
+        <f t="shared" si="207"/>
+        <v>0.2333475349268451</v>
       </c>
       <c r="BI30" s="8">
-        <f t="shared" si="209"/>
-        <v>0.24892497463973945</v>
+        <f t="shared" si="207"/>
+        <v>0.23473713537306226</v>
       </c>
       <c r="BJ30" s="8">
-        <f t="shared" si="209"/>
-        <v>0.25031721406676893</v>
+        <f t="shared" si="207"/>
+        <v>0.23610626089610262</v>
       </c>
       <c r="BL30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="BM30" s="8">
         <v>-0.01</v>
@@ -6870,139 +6859,139 @@
     </row>
     <row r="31" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8">
-        <f t="shared" ref="G31:R31" si="210">G10/C10-1</f>
+        <f t="shared" ref="G31:R31" si="208">G10/C10-1</f>
         <v>0.12765957446808507</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.19638242894056845</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.22081218274111669</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.30808080808080818</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.30660377358490565</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.31101511879049681</v>
       </c>
       <c r="M31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.60914760914760913</v>
       </c>
       <c r="N31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.60424710424710426</v>
       </c>
       <c r="O31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.55054151624548742</v>
       </c>
       <c r="P31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.47940691927512358</v>
       </c>
       <c r="Q31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.1653746770025839</v>
       </c>
       <c r="R31" s="8">
-        <f t="shared" si="210"/>
+        <f t="shared" si="208"/>
         <v>0.12996389891696758</v>
       </c>
       <c r="S31" s="8">
-        <f t="shared" ref="S31" si="211">S10/O10-1</f>
+        <f t="shared" ref="S31" si="209">S10/O10-1</f>
         <v>0.1071012805587892</v>
       </c>
       <c r="T31" s="8">
-        <f t="shared" ref="T31" si="212">T10/P10-1</f>
+        <f t="shared" ref="T31" si="210">T10/P10-1</f>
         <v>0.13585746102449892</v>
       </c>
       <c r="U31" s="8">
-        <f t="shared" ref="U31" si="213">U10/Q10-1</f>
+        <f t="shared" ref="U31" si="211">U10/Q10-1</f>
         <v>0.33370288248337032</v>
       </c>
       <c r="V31" s="8">
-        <f t="shared" ref="V31" si="214">V10/R10-1</f>
+        <f t="shared" ref="V31" si="212">V10/R10-1</f>
         <v>0.37486687965921184</v>
       </c>
       <c r="W31" s="8">
-        <f t="shared" ref="W31" si="215">W10/S10-1</f>
+        <f t="shared" ref="W31" si="213">W10/S10-1</f>
         <v>0.3859095688748686</v>
       </c>
       <c r="X31" s="8">
-        <f t="shared" ref="X31" si="216">X10/T10-1</f>
+        <f t="shared" ref="X31" si="214">X10/T10-1</f>
         <v>0.30294117647058827</v>
       </c>
       <c r="Y31" s="8">
-        <f t="shared" ref="Y31" si="217">Y10/U10-1</f>
+        <f t="shared" ref="Y31" si="215">Y10/U10-1</f>
         <v>6.4006650041562807E-2</v>
       </c>
       <c r="Z31" s="8">
-        <f t="shared" ref="Z31" si="218">Z10/V10-1</f>
+        <f t="shared" ref="Z31" si="216">Z10/V10-1</f>
         <v>-0.12625871417505807</v>
       </c>
       <c r="AA31" s="8">
-        <f t="shared" ref="AA31" si="219">AA10/W10-1</f>
+        <f t="shared" ref="AA31" si="217">AA10/W10-1</f>
         <v>-8.4218512898330822E-2</v>
       </c>
       <c r="AB31" s="8">
-        <f t="shared" ref="AB31" si="220">AB10/X10-1</f>
+        <f t="shared" ref="AB31" si="218">AB10/X10-1</f>
         <v>-8.2016553799849512E-2</v>
       </c>
       <c r="AC31" s="8">
-        <f t="shared" ref="AC31" si="221">AC10/Y10-1</f>
+        <f t="shared" ref="AC31" si="219">AC10/Y10-1</f>
         <v>-5.9374999999999956E-2</v>
       </c>
       <c r="AD31" s="8">
-        <f t="shared" ref="AD31" si="222">AD10/Z10-1</f>
+        <f t="shared" ref="AD31" si="220">AD10/Z10-1</f>
         <v>0.13031914893617014</v>
       </c>
       <c r="AE31" s="8">
-        <f t="shared" ref="AE31" si="223">AE10/AA10-1</f>
+        <f t="shared" ref="AE31" si="221">AE10/AA10-1</f>
         <v>0.13338856669428334</v>
       </c>
       <c r="AF31" s="8">
-        <f t="shared" ref="AF31" si="224">AF10/AB10-1</f>
+        <f t="shared" ref="AF31" si="222">AF10/AB10-1</f>
         <v>0.1057377049180328</v>
       </c>
       <c r="AG31" s="8">
-        <f t="shared" ref="AG31" si="225">AG10/AC10-1</f>
+        <f t="shared" ref="AG31" si="223">AG10/AC10-1</f>
         <v>0.12624584717607967</v>
       </c>
       <c r="AH31" s="8">
-        <f t="shared" ref="AH31" si="226">AH10/AD10-1</f>
+        <f t="shared" ref="AH31" si="224">AH10/AD10-1</f>
         <v>0.11372549019607847</v>
       </c>
       <c r="AI31" s="8">
-        <f t="shared" ref="AI31" si="227">AI10/AE10-1</f>
+        <f t="shared" ref="AI31" si="225">AI10/AE10-1</f>
         <v>6.7251461988304007E-2</v>
       </c>
       <c r="AJ31" s="8">
-        <f t="shared" ref="AJ31" si="228">AJ10/AF10-1</f>
+        <f t="shared" ref="AJ31" si="226">AJ10/AF10-1</f>
         <v>9.7850259451445432E-2</v>
       </c>
       <c r="AK31" s="8">
-        <f t="shared" ref="AK31" si="229">AK10/AG10-1</f>
-        <v>0.1100000000000001</v>
+        <f t="shared" ref="AK31" si="227">AK10/AG10-1</f>
+        <v>5.6784660766961759E-2</v>
       </c>
       <c r="AL31" s="8">
-        <f t="shared" ref="AL31" si="230">AL10/AH10-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AL31" si="228">AL10/AH10-1</f>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM31" s="8"/>
       <c r="AN31" s="8"/>
@@ -7010,79 +6999,79 @@
       <c r="AP31" s="8"/>
       <c r="AR31" s="8"/>
       <c r="AS31" s="8">
-        <f t="shared" ref="AS31:BE31" si="231">AS10/AR10-1</f>
+        <f t="shared" ref="AS31:BE31" si="229">AS10/AR10-1</f>
         <v>0.21442369607211842</v>
       </c>
       <c r="AT31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>0.46659597030752908</v>
       </c>
       <c r="AU31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>0.30079537237888654</v>
       </c>
       <c r="AV31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>0.24096720400222349</v>
       </c>
       <c r="AW31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>0.13213885778275469</v>
       </c>
       <c r="AX31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>-2.9475766567754746E-2</v>
       </c>
       <c r="AY31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>0.11964940888707698</v>
       </c>
       <c r="AZ31" s="8">
-        <f t="shared" si="231"/>
-        <v>8.6029492080829995E-2</v>
+        <f t="shared" si="229"/>
+        <v>6.7722555980338717E-2</v>
       </c>
       <c r="BA31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BB31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BC31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BD31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE31" s="8">
-        <f t="shared" si="231"/>
+        <f t="shared" si="229"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF31" s="8">
-        <f t="shared" ref="BF31" si="232">BF10/BE10-1</f>
+        <f t="shared" ref="BF31" si="230">BF10/BE10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG31" s="8">
-        <f t="shared" ref="BG31" si="233">BG10/BF10-1</f>
+        <f t="shared" ref="BG31" si="231">BG10/BF10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH31" s="8">
-        <f t="shared" ref="BH31" si="234">BH10/BG10-1</f>
+        <f t="shared" ref="BH31" si="232">BH10/BG10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI31" s="8">
-        <f t="shared" ref="BI31" si="235">BI10/BH10-1</f>
+        <f t="shared" ref="BI31" si="233">BI10/BH10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BJ31" s="8">
-        <f t="shared" ref="BJ31" si="236">BJ10/BI10-1</f>
+        <f t="shared" ref="BJ31" si="234">BJ10/BI10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BL31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BM31" s="8">
         <v>0.06</v>
@@ -7090,150 +7079,150 @@
     </row>
     <row r="32" spans="2:196" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="8">
         <f>C11/C5</f>
         <v>0.46141009595327492</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" ref="D32:R32" si="237">D11/D5</f>
+        <f t="shared" ref="D32:R32" si="235">D11/D5</f>
         <v>0.4474194800155219</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.43206219918548688</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.43455497382198954</v>
       </c>
       <c r="G32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.44211576846307388</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.45839683023468453</v>
       </c>
       <c r="I32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.46816037735849059</v>
       </c>
       <c r="J32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.45600888148764918</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.45410757291945408</v>
       </c>
       <c r="L32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.49787340505379035</v>
       </c>
       <c r="M32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.45712386439175717</v>
       </c>
       <c r="N32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.48361162646876932</v>
       </c>
       <c r="O32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.49126413155190135</v>
       </c>
       <c r="P32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.44166181324014753</v>
       </c>
       <c r="Q32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.43864181583317957</v>
       </c>
       <c r="R32" s="8">
-        <f t="shared" si="237"/>
+        <f t="shared" si="235"/>
         <v>0.45246690734055356</v>
       </c>
       <c r="S32" s="8">
-        <f t="shared" ref="S32:AL32" si="238">S11/S5</f>
+        <f t="shared" ref="S32:AL32" si="236">S11/S5</f>
         <v>0.42663089049136343</v>
       </c>
       <c r="T32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.43154574132492113</v>
       </c>
       <c r="U32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.45330030598863469</v>
       </c>
       <c r="V32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.47283647283647284</v>
       </c>
       <c r="W32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.45499932532721632</v>
       </c>
       <c r="X32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.44352331606217615</v>
       </c>
       <c r="Y32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.42682148781421464</v>
       </c>
       <c r="Z32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.4037452290076336</v>
       </c>
       <c r="AA32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.38244210015763308</v>
       </c>
       <c r="AB32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.36185051726142042</v>
       </c>
       <c r="AC32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.36387614678899083</v>
       </c>
       <c r="AD32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.37008721869279637</v>
       </c>
       <c r="AE32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.35464797985327934</v>
       </c>
       <c r="AF32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.34573726541554961</v>
       </c>
       <c r="AG32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.35186361711139347</v>
       </c>
       <c r="AH32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.34734314019813872</v>
       </c>
       <c r="AI32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.34886560179061959</v>
       </c>
       <c r="AJ32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.33636186010160218</v>
       </c>
       <c r="AK32" s="8">
-        <f t="shared" si="238"/>
-        <v>0.34</v>
+        <f t="shared" si="236"/>
+        <v>0.33687493907788285</v>
       </c>
       <c r="AL32" s="8">
-        <f t="shared" si="238"/>
+        <f t="shared" si="236"/>
         <v>0.34</v>
       </c>
       <c r="AM32" s="8"/>
@@ -7241,224 +7230,224 @@
       <c r="AO32" s="8"/>
       <c r="AP32" s="8"/>
       <c r="AR32" s="8">
-        <f t="shared" ref="AR32:BE32" si="239">AR11/AR5</f>
+        <f t="shared" ref="AR32:BE32" si="237">AR11/AR5</f>
         <v>0.44316888045540798</v>
       </c>
       <c r="AS32" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="237"/>
         <v>0.45655774732720977</v>
       </c>
       <c r="AT32" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="237"/>
         <v>0.47350567317814951</v>
       </c>
       <c r="AU32" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="237"/>
         <v>0.45520421607378131</v>
       </c>
       <c r="AV32" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="237"/>
         <v>0.44749358296844333</v>
       </c>
       <c r="AW32" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="237"/>
         <v>0.43142383261035977</v>
       </c>
       <c r="AX32" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="237"/>
         <v>0.36942364517887366</v>
       </c>
       <c r="AY32" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="237"/>
         <v>0.34983507058978758</v>
       </c>
       <c r="AZ32" s="8">
-        <f t="shared" si="239"/>
-        <v>0.34880799229250631</v>
+        <f t="shared" si="237"/>
+        <v>0.3505907086861163</v>
       </c>
       <c r="BA32" s="8">
-        <f t="shared" si="239"/>
+        <f t="shared" si="237"/>
+        <v>0.34</v>
+      </c>
+      <c r="BB32" s="8">
+        <f t="shared" si="237"/>
         <v>0.33</v>
       </c>
-      <c r="BB32" s="8">
-        <f t="shared" si="239"/>
-        <v>0.32</v>
-      </c>
       <c r="BC32" s="8">
-        <f t="shared" si="239"/>
-        <v>0.32</v>
+        <f t="shared" si="237"/>
+        <v>0.33</v>
       </c>
       <c r="BD32" s="8">
-        <f t="shared" si="239"/>
-        <v>0.32</v>
+        <f t="shared" si="237"/>
+        <v>0.33</v>
       </c>
       <c r="BE32" s="8">
-        <f t="shared" si="239"/>
-        <v>0.32</v>
+        <f t="shared" si="237"/>
+        <v>0.33</v>
       </c>
       <c r="BF32" s="8">
-        <f t="shared" ref="BF32:BJ32" si="240">BF11/BF5</f>
-        <v>0.32</v>
+        <f t="shared" ref="BF32:BJ32" si="238">BF11/BF5</f>
+        <v>0.33</v>
       </c>
       <c r="BG32" s="8">
-        <f t="shared" si="240"/>
-        <v>0.32</v>
+        <f t="shared" si="238"/>
+        <v>0.33</v>
       </c>
       <c r="BH32" s="8">
-        <f t="shared" si="240"/>
-        <v>0.32</v>
+        <f t="shared" si="238"/>
+        <v>0.33000000000000007</v>
       </c>
       <c r="BI32" s="8">
-        <f t="shared" si="240"/>
-        <v>0.31999999999999995</v>
+        <f t="shared" si="238"/>
+        <v>0.33</v>
       </c>
       <c r="BJ32" s="8">
-        <f t="shared" si="240"/>
-        <v>0.32</v>
+        <f t="shared" si="238"/>
+        <v>0.33</v>
       </c>
       <c r="BL32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="BM32" s="5">
         <f>NPV(BM31,AZ20:GN20)</f>
-        <v>153823.13440534327</v>
+        <v>149568.05772935235</v>
       </c>
     </row>
     <row r="33" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8">
-        <f t="shared" ref="G33:R33" si="241">G12/C12-1</f>
+        <f t="shared" ref="G33:R33" si="239">G12/C12-1</f>
         <v>0.13461538461538458</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.23674911660777376</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.26199261992619927</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.30545454545454542</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.22711864406779658</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>7.1428571428571397E-2</v>
       </c>
       <c r="M33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.39473684210526305</v>
       </c>
       <c r="N33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.36490250696378834</v>
       </c>
       <c r="O33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.38674033149171261</v>
       </c>
       <c r="P33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.30400000000000005</v>
       </c>
       <c r="Q33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>9.4339622641509413E-2</v>
       </c>
       <c r="R33" s="8">
-        <f t="shared" si="241"/>
+        <f t="shared" si="239"/>
         <v>0.17142857142857149</v>
       </c>
       <c r="S33" s="8">
-        <f t="shared" ref="S33" si="242">S12/O12-1</f>
+        <f t="shared" ref="S33" si="240">S12/O12-1</f>
         <v>0.11354581673306763</v>
       </c>
       <c r="T33" s="8">
-        <f t="shared" ref="T33" si="243">T12/P12-1</f>
+        <f t="shared" ref="T33" si="241">T12/P12-1</f>
         <v>0.30674846625766872</v>
       </c>
       <c r="U33" s="8">
-        <f t="shared" ref="U33" si="244">U12/Q12-1</f>
+        <f t="shared" ref="U33" si="242">U12/Q12-1</f>
         <v>0.27777777777777768</v>
       </c>
       <c r="V33" s="8">
-        <f t="shared" ref="V33" si="245">V12/R12-1</f>
+        <f t="shared" ref="V33" si="243">V12/R12-1</f>
         <v>0.27700348432055755</v>
       </c>
       <c r="W33" s="8">
-        <f t="shared" ref="W33" si="246">W12/S12-1</f>
+        <f t="shared" ref="W33" si="244">W12/S12-1</f>
         <v>0.17352415026833623</v>
       </c>
       <c r="X33" s="8">
-        <f t="shared" ref="X33" si="247">X12/T12-1</f>
+        <f t="shared" ref="X33" si="245">X12/T12-1</f>
         <v>1.2519561815336422E-2</v>
       </c>
       <c r="Y33" s="8">
-        <f t="shared" ref="Y33" si="248">Y12/U12-1</f>
+        <f t="shared" ref="Y33" si="246">Y12/U12-1</f>
         <v>-4.4977511244377322E-3</v>
       </c>
       <c r="Z33" s="8">
-        <f t="shared" ref="Z33" si="249">Z12/V12-1</f>
+        <f t="shared" ref="Z33" si="247">Z12/V12-1</f>
         <v>-0.20054570259208726</v>
       </c>
       <c r="AA33" s="8">
-        <f t="shared" ref="AA33" si="250">AA12/W12-1</f>
+        <f t="shared" ref="AA33" si="248">AA12/W12-1</f>
         <v>-2.7439024390243927E-2</v>
       </c>
       <c r="AB33" s="8">
-        <f t="shared" ref="AB33" si="251">AB12/X12-1</f>
+        <f t="shared" ref="AB33" si="249">AB12/X12-1</f>
         <v>-2.3183925811437356E-2</v>
       </c>
       <c r="AC33" s="8">
-        <f t="shared" ref="AC33" si="252">AC12/Y12-1</f>
+        <f t="shared" ref="AC33" si="250">AC12/Y12-1</f>
         <v>-4.8192771084337394E-2</v>
       </c>
       <c r="AD33" s="8">
-        <f t="shared" ref="AD33" si="253">AD12/Z12-1</f>
+        <f t="shared" ref="AD33" si="251">AD12/Z12-1</f>
         <v>7.8498293515358419E-2</v>
       </c>
       <c r="AE33" s="8">
-        <f t="shared" ref="AE33" si="254">AE12/AA12-1</f>
+        <f t="shared" ref="AE33" si="252">AE12/AA12-1</f>
         <v>1.4106583072100332E-2</v>
       </c>
       <c r="AF33" s="8">
-        <f t="shared" ref="AF33" si="255">AF12/AB12-1</f>
+        <f t="shared" ref="AF33" si="253">AF12/AB12-1</f>
         <v>0.125</v>
       </c>
       <c r="AG33" s="8">
-        <f t="shared" ref="AG33" si="256">AG12/AC12-1</f>
+        <f t="shared" ref="AG33" si="254">AG12/AC12-1</f>
         <v>0.125</v>
       </c>
       <c r="AH33" s="8">
-        <f t="shared" ref="AH33" si="257">AH12/AD12-1</f>
+        <f t="shared" ref="AH33" si="255">AH12/AD12-1</f>
         <v>0.21360759493670889</v>
       </c>
       <c r="AI33" s="8">
-        <f t="shared" ref="AI33" si="258">AI12/AE12-1</f>
+        <f t="shared" ref="AI33" si="256">AI12/AE12-1</f>
         <v>7.727975270479126E-2</v>
       </c>
       <c r="AJ33" s="8">
-        <f t="shared" ref="AJ33" si="259">AJ12/AF12-1</f>
+        <f t="shared" ref="AJ33" si="257">AJ12/AF12-1</f>
         <v>3.234880450070321E-2</v>
       </c>
       <c r="AK33" s="8">
-        <f t="shared" ref="AK33" si="260">AK12/AG12-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AK33" si="258">AK12/AG12-1</f>
+        <v>-6.1884669479606136E-2</v>
       </c>
       <c r="AL33" s="8">
-        <f t="shared" ref="AL33" si="261">AL12/AH12-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AL33" si="259">AL12/AH12-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AM33" s="8"/>
       <c r="AN33" s="8"/>
@@ -7466,231 +7455,231 @@
       <c r="AP33" s="8"/>
       <c r="AR33" s="8"/>
       <c r="AS33" s="8">
-        <f t="shared" ref="AS33:BE33" si="262">AS12/AR12-1</f>
+        <f t="shared" ref="AS33:BE33" si="260">AS12/AR12-1</f>
         <v>0.23599632690541772</v>
       </c>
       <c r="AT33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>0.26597325408618122</v>
       </c>
       <c r="AU33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>0.22476525821596249</v>
       </c>
       <c r="AV33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>0.24484906564446574</v>
       </c>
       <c r="AW33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>-1.7321016166281789E-2</v>
       </c>
       <c r="AX33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>-7.4422248335291874E-3</v>
       </c>
       <c r="AY33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>0.11917916337805834</v>
       </c>
       <c r="AZ33" s="8">
-        <f t="shared" si="262"/>
-        <v>5.6812411847672717E-2</v>
+        <f t="shared" si="260"/>
+        <v>4.8166431593794634E-3</v>
       </c>
       <c r="BA33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE33" s="8">
-        <f t="shared" si="262"/>
+        <f t="shared" si="260"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF33" s="8">
-        <f t="shared" ref="BF33" si="263">BF12/BE12-1</f>
+        <f t="shared" ref="BF33" si="261">BF12/BE12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG33" s="8">
-        <f t="shared" ref="BG33" si="264">BG12/BF12-1</f>
+        <f t="shared" ref="BG33" si="262">BG12/BF12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH33" s="8">
-        <f t="shared" ref="BH33" si="265">BH12/BG12-1</f>
+        <f t="shared" ref="BH33" si="263">BH12/BG12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BI33" s="8">
-        <f t="shared" ref="BI33" si="266">BI12/BH12-1</f>
+        <f t="shared" ref="BI33" si="264">BI12/BH12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ33" s="8">
-        <f t="shared" ref="BJ33" si="267">BJ12/BI12-1</f>
+        <f t="shared" ref="BJ33" si="265">BJ12/BI12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BL33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="BM33" s="5">
         <f>Main!D8</f>
-        <v>12021</v>
+        <v>9295</v>
       </c>
     </row>
     <row r="34" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" s="8">
         <f>C19/C18</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" ref="D34:R34" si="268">D19/D18</f>
+        <f t="shared" ref="D34:R34" si="266">D19/D18</f>
         <v>0.26984126984126983</v>
       </c>
       <c r="E34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>0.26712328767123289</v>
       </c>
       <c r="F34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>6.7873303167420809E-2</v>
       </c>
       <c r="G34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>0.10649350649350649</v>
       </c>
       <c r="H34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>-0.2943722943722944</v>
       </c>
       <c r="I34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>0.1796875</v>
       </c>
       <c r="J34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>-0.5146443514644351</v>
       </c>
       <c r="K34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>0.18672199170124482</v>
       </c>
       <c r="L34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>0.4451219512195122</v>
       </c>
       <c r="M34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>2.703125</v>
       </c>
       <c r="N34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>-61</v>
       </c>
       <c r="O34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>-1.1063829787234043</v>
       </c>
       <c r="P34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>-2.1287246722288438</v>
       </c>
       <c r="Q34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>0.13108396354469654</v>
       </c>
       <c r="R34" s="8">
-        <f t="shared" si="268"/>
+        <f t="shared" si="266"/>
         <v>0.37176470588235294</v>
       </c>
       <c r="S34" s="8">
-        <f t="shared" ref="S34:AL34" si="269">S19/S18</f>
+        <f t="shared" ref="S34:AL34" si="267">S19/S18</f>
         <v>0.22350993377483444</v>
       </c>
       <c r="T34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.35230024213075062</v>
       </c>
       <c r="U34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>-0.56521739130434778</v>
       </c>
       <c r="V34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.85786802030456855</v>
       </c>
       <c r="W34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>1.9655172413793103</v>
       </c>
       <c r="X34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.62430939226519333</v>
       </c>
       <c r="Y34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.55789473684210522</v>
       </c>
       <c r="Z34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>3.9696969696969697</v>
       </c>
       <c r="AA34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.38957055214723929</v>
       </c>
       <c r="AB34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.15080428954423591</v>
       </c>
       <c r="AC34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.17686617350369871</v>
       </c>
       <c r="AD34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.1209726443768997</v>
       </c>
       <c r="AE34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.17889662560257097</v>
       </c>
       <c r="AF34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.22210125204137179</v>
       </c>
       <c r="AG34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.12542955326460481</v>
       </c>
       <c r="AH34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.14084507042253522</v>
       </c>
       <c r="AI34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.21935157041540021</v>
       </c>
       <c r="AJ34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.21571072319201995</v>
       </c>
       <c r="AK34" s="8">
-        <f t="shared" si="269"/>
-        <v>0.18</v>
+        <f t="shared" si="267"/>
+        <v>0.16958598726114649</v>
       </c>
       <c r="AL34" s="8">
-        <f t="shared" si="269"/>
+        <f t="shared" si="267"/>
         <v>0.18</v>
       </c>
       <c r="AM34" s="8"/>
@@ -7698,345 +7687,345 @@
       <c r="AO34" s="8"/>
       <c r="AP34" s="8"/>
       <c r="AR34" s="8">
-        <f t="shared" ref="AR34:BE34" si="270">AR19/AR18</f>
+        <f t="shared" ref="AR34:BE34" si="268">AR19/AR18</f>
         <v>0.14285714285714285</v>
       </c>
       <c r="AS34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>-0.12919633774160733</v>
       </c>
       <c r="AT34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>0.82152974504249288</v>
       </c>
       <c r="AU34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>-0.59000390472471687</v>
       </c>
       <c r="AV34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>4.5478036175710591E-2</v>
       </c>
       <c r="AW34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>0.68484848484848482</v>
       </c>
       <c r="AX34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>0.16444444444444445</v>
       </c>
       <c r="AY34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>0.16684592632428072</v>
       </c>
       <c r="AZ34" s="8">
-        <f t="shared" si="270"/>
-        <v>0.220769776877733</v>
+        <f t="shared" si="268"/>
+        <v>0.22237784669524349</v>
       </c>
       <c r="BA34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>0.18</v>
       </c>
       <c r="BB34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>0.18</v>
       </c>
       <c r="BC34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
         <v>0.18</v>
       </c>
       <c r="BD34" s="8">
-        <f t="shared" si="270"/>
+        <f t="shared" si="268"/>
+        <v>0.18</v>
+      </c>
+      <c r="BE34" s="8">
+        <f t="shared" si="268"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="BF34" s="8">
+        <f t="shared" ref="BF34:BJ34" si="269">BF19/BF18</f>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="BG34" s="8">
+        <f t="shared" si="269"/>
         <v>0.17999999999999997</v>
       </c>
-      <c r="BE34" s="8">
-        <f t="shared" si="270"/>
+      <c r="BH34" s="8">
+        <f t="shared" si="269"/>
         <v>0.17999999999999997</v>
       </c>
-      <c r="BF34" s="8">
-        <f t="shared" ref="BF34:BJ34" si="271">BF19/BF18</f>
+      <c r="BI34" s="8">
+        <f t="shared" si="269"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="BJ34" s="8">
+        <f t="shared" si="269"/>
         <v>0.18</v>
       </c>
-      <c r="BG34" s="8">
-        <f t="shared" si="271"/>
-        <v>0.17999999999999997</v>
-      </c>
-      <c r="BH34" s="8">
-        <f t="shared" si="271"/>
-        <v>0.18</v>
-      </c>
-      <c r="BI34" s="8">
-        <f t="shared" si="271"/>
-        <v>0.18</v>
-      </c>
-      <c r="BJ34" s="8">
-        <f t="shared" si="271"/>
-        <v>0.18</v>
-      </c>
       <c r="BL34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="BM34" s="5">
         <f>BM32+BM33</f>
-        <v>165844.13440534327</v>
+        <v>158863.05772935235</v>
       </c>
     </row>
     <row r="35" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C35" s="8">
         <f>C20/C5</f>
         <v>4.1718815185648727E-4</v>
       </c>
       <c r="D35" s="8">
-        <f t="shared" ref="D35:AL35" si="272">D20/D5</f>
+        <f t="shared" ref="D35:AL35" si="270">D20/D5</f>
         <v>1.7850213426464881E-2</v>
       </c>
       <c r="E35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>3.9614957423176604E-2</v>
       </c>
       <c r="F35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>7.1902268760907509E-2</v>
       </c>
       <c r="G35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.11443779108449767</v>
       </c>
       <c r="H35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>9.1130752819262417E-2</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>3.0955188679245283E-2</v>
       </c>
       <c r="J35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.10047182903136276</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.1048969761841049</v>
       </c>
       <c r="L35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>2.276707530647986E-2</v>
       </c>
       <c r="M35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>-2.415244848216264E-2</v>
       </c>
       <c r="N35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>-5.1123479694908269E-2</v>
       </c>
       <c r="O35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>2.0349434737923947E-2</v>
       </c>
       <c r="P35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.50960978450786254</v>
       </c>
       <c r="Q35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.20672633327182138</v>
       </c>
       <c r="R35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>4.5899948427024238E-2</v>
       </c>
       <c r="S35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>7.8651685393258425E-2</v>
       </c>
       <c r="T35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>8.4384858044164041E-2</v>
       </c>
       <c r="U35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>6.8191752877750256E-2</v>
       </c>
       <c r="V35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>-3.8220038220038218E-3</v>
       </c>
       <c r="W35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>3.778167588719471E-3</v>
       </c>
       <c r="X35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>8.8082901554404139E-3</v>
       </c>
       <c r="Y35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>2.6795967844838585E-2</v>
       </c>
       <c r="Z35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>-1.1688931297709924E-2</v>
       </c>
       <c r="AA35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>2.4129986661816417E-2</v>
       </c>
       <c r="AB35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.14727420667209112</v>
       </c>
       <c r="AC35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.14036697247706423</v>
       </c>
       <c r="AD35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.15570151825131906</v>
       </c>
       <c r="AE35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.16785284134457462</v>
       </c>
       <c r="AF35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.15324396782841823</v>
       </c>
       <c r="AG35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.16168996188055909</v>
       </c>
       <c r="AH35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.17091964375062543</v>
       </c>
       <c r="AI35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.15678095431885239</v>
       </c>
       <c r="AJ35" s="8">
-        <f t="shared" si="272"/>
+        <f t="shared" si="270"/>
         <v>0.18434935521688159</v>
       </c>
       <c r="AK35" s="8">
-        <f t="shared" si="272"/>
-        <v>0.18120250542923608</v>
+        <f t="shared" si="270"/>
+        <v>0.20333365825129154</v>
       </c>
       <c r="AL35" s="8">
-        <f t="shared" si="272"/>
-        <v>0.16835196562098098</v>
+        <f t="shared" si="270"/>
+        <v>0.19614801407168952</v>
       </c>
       <c r="AR35" s="8">
-        <f t="shared" ref="AR35:BJ35" si="273">AR20/AR5</f>
+        <f t="shared" ref="AR35:BJ35" si="271">AR20/AR5</f>
         <v>3.4155597722960153E-2</v>
       </c>
       <c r="AS35" s="8">
-        <f t="shared" si="273"/>
+        <f t="shared" si="271"/>
         <v>8.3571751242282791E-2</v>
       </c>
       <c r="AT35" s="8">
-        <f t="shared" si="273"/>
+        <f t="shared" si="271"/>
         <v>7.3692829570710027E-3</v>
       </c>
       <c r="AU35" s="8">
-        <f t="shared" si="273"/>
+        <f t="shared" si="271"/>
         <v>0.19160549595332205</v>
       </c>
       <c r="AV35" s="8">
-        <f t="shared" si="273"/>
+        <f t="shared" si="271"/>
         <v>6.9719160501283406E-2</v>
       </c>
       <c r="AW35" s="8">
-        <f t="shared" si="273"/>
+        <f t="shared" si="271"/>
         <v>6.6343454963000764E-3</v>
       </c>
       <c r="AX35" s="8">
-        <f t="shared" si="273"/>
+        <f t="shared" si="271"/>
         <v>0.11865622400091803</v>
       </c>
       <c r="AY35" s="8">
-        <f t="shared" si="273"/>
+        <f t="shared" si="271"/>
         <v>0.16353080881382767</v>
       </c>
       <c r="AZ35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.15439833078989376</v>
+        <f t="shared" si="271"/>
+        <v>0.16135450701665732</v>
       </c>
       <c r="BA35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.18710703396520426</v>
+        <f t="shared" si="271"/>
+        <v>0.18083675159538459</v>
       </c>
       <c r="BB35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.19780505375538388</v>
+        <f t="shared" si="271"/>
+        <v>0.19149448989181173</v>
       </c>
       <c r="BC35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.19888948878374668</v>
+        <f t="shared" si="271"/>
+        <v>0.1925836382394284</v>
       </c>
       <c r="BD35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.20076206470038849</v>
+        <f t="shared" si="271"/>
+        <v>0.19442512185598429</v>
       </c>
       <c r="BE35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.20243134935160581</v>
+        <f t="shared" si="271"/>
+        <v>0.19605597857788404</v>
       </c>
       <c r="BF35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.20348475748515343</v>
+        <f t="shared" si="271"/>
+        <v>0.19714552763838616</v>
       </c>
       <c r="BG35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.20448988145983729</v>
+        <f t="shared" si="271"/>
+        <v>0.19818564010230694</v>
       </c>
       <c r="BH35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.20547021635435242</v>
+        <f t="shared" si="271"/>
+        <v>0.19920072420435125</v>
       </c>
       <c r="BI35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.20643710374199237</v>
+        <f t="shared" si="271"/>
+        <v>0.20020257233441494</v>
       </c>
       <c r="BJ35" s="8">
-        <f t="shared" si="273"/>
-        <v>0.20739593839939366</v>
+        <f t="shared" si="271"/>
+        <v>0.20119680340502485</v>
       </c>
       <c r="BL35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="BM35" s="11">
         <f>BM34/BE21</f>
-        <v>174.20602353502446</v>
+        <v>167.57706511535059</v>
       </c>
     </row>
     <row r="36" spans="2:65" x14ac:dyDescent="0.3">
       <c r="BL36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="BM36" s="11">
         <f>Main!D3</f>
-        <v>252.92</v>
+        <v>213.02</v>
       </c>
     </row>
     <row r="37" spans="2:65" x14ac:dyDescent="0.3">
       <c r="BL37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="BM37" s="10">
         <f>BM35/BM36-1</f>
-        <v>-0.31122084637425085</v>
+        <v>-0.21332708142263368</v>
       </c>
     </row>
     <row r="38" spans="2:65" x14ac:dyDescent="0.3">
       <c r="BL38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="BM38" s="6" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
